--- a/repair/back/doc/estimate/diagnosis.xlsx
+++ b/repair/back/doc/estimate/diagnosis.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="Polaris Office Sheet" lastEdited="7" lowestEdited="6" rupBuild=""/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="731" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="731" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="갑지" sheetId="21" r:id="rId1"/>
@@ -1975,7 +1975,7 @@
     <numFmt numFmtId="243" formatCode="@\ &quot;정&quot;&quot;기&quot;&quot;안&quot;&quot;전&quot;&quot;점&quot;&quot;검&quot;&quot;(상반기)&quot;\ &quot;용&quot;&quot;역&quot;"/>
     <numFmt numFmtId="244" formatCode="0_);[Red]\(0\)"/>
   </numFmts>
-  <fonts count="172">
+  <fonts count="159">
     <font>
       <sz val="11.0"/>
       <name val="돋움"/>
@@ -2274,11 +2274,6 @@
       <color rgb="FF000000"/>
     </font>
     <font>
-      <sz val="1.0"/>
-      <name val="Courier"/>
-      <color rgb="FF000000"/>
-    </font>
-    <font>
       <sz val="11.0"/>
       <name val="돋움체"/>
       <color rgb="FF000000"/>
@@ -2351,11 +2346,6 @@
       <color rgb="FF000000"/>
     </font>
     <font>
-      <sz val="10.0"/>
-      <name val="바탕"/>
-      <color rgb="FF000000"/>
-    </font>
-    <font>
       <sz val="11.0"/>
       <name val="한컴 솔잎 B"/>
       <color rgb="FF000000"/>
@@ -2411,16 +2401,6 @@
       <color rgb="FF000000"/>
     </font>
     <font>
-      <sz val="10.0"/>
-      <name val="돋움"/>
-      <color rgb="FF000000"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <name val="한컴 솔잎 B"/>
-      <color rgb="FF000000"/>
-    </font>
-    <font>
       <b/>
       <sz val="11.0"/>
       <name val="한컴 솔잎 B"/>
@@ -2467,11 +2447,6 @@
       <color rgb="FF000000"/>
     </font>
     <font>
-      <sz val="12.0"/>
-      <name val="돋움"/>
-      <color rgb="FF000000"/>
-    </font>
-    <font>
       <b/>
       <sz val="17.0"/>
       <name val="돋움"/>
@@ -2479,24 +2454,7 @@
     </font>
     <font>
       <b/>
-      <sz val="14.0"/>
-      <name val="돋움"/>
-      <color rgb="FF000000"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11.0"/>
-      <name val="돋움"/>
-      <color rgb="FF000000"/>
-    </font>
-    <font>
-      <b/>
       <sz val="12.0"/>
-      <name val="돋움"/>
-      <color rgb="FF000000"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
       <name val="돋움"/>
       <color rgb="FF000000"/>
     </font>
@@ -2530,12 +2488,6 @@
     </font>
     <font>
       <sz val="14.0"/>
-      <name val="돋움"/>
-      <color rgb="FF000000"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12.0"/>
       <name val="돋움"/>
       <color rgb="FF000000"/>
     </font>
@@ -2750,16 +2702,6 @@
       <color rgb="FF000000"/>
     </font>
     <font>
-      <sz val="10.0"/>
-      <name val="돋움"/>
-      <color rgb="FF000000"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <name val="돋움"/>
-      <color rgb="FF000000"/>
-    </font>
-    <font>
       <b/>
       <sz val="12.0"/>
       <name val="맑은 고딕"/>
@@ -2778,12 +2720,6 @@
     </font>
     <font>
       <b/>
-      <sz val="14.0"/>
-      <name val="맑은 고딕"/>
-      <color rgb="FF000000"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11.0"/>
       <name val="맑은 고딕"/>
       <color rgb="FF000000"/>
@@ -2795,16 +2731,6 @@
       <color theme="1"/>
     </font>
     <font>
-      <sz val="12.0"/>
-      <name val="맑은 고딕"/>
-      <color rgb="FF000000"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <name val="맑은 고딕"/>
-      <color rgb="FF000000"/>
-    </font>
-    <font>
       <sz val="13.0"/>
       <name val="맑은 고딕"/>
       <color rgb="FF000000"/>
@@ -2813,12 +2739,6 @@
       <b/>
       <u/>
       <sz val="20.0"/>
-      <name val="맑은 고딕"/>
-      <color rgb="FF000000"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12.0"/>
       <name val="맑은 고딕"/>
       <color rgb="FF000000"/>
     </font>
@@ -2859,11 +2779,6 @@
       <color rgb="FF000000"/>
     </font>
     <font>
-      <sz val="13.0"/>
-      <name val="맑은 고딕"/>
-      <color rgb="FF000000"/>
-    </font>
-    <font>
       <sz val="2.0"/>
       <name val="맑은 고딕"/>
       <color rgb="FF000000"/>
@@ -2900,12 +2815,27 @@
     </font>
     <font>
       <b/>
+      <sz val="24.0"/>
+      <name val="바탕"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="16.0"/>
+      <name val="돋움"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10.0"/>
+      <name val="돋움"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
       <sz val="11.0"/>
-      <name val="맑은 고딕"/>
+      <name val="돋움"/>
       <color rgb="FF000000"/>
     </font>
   </fonts>
-  <fills count="43">
+  <fills count="42">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2978,12 +2908,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.150000"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
@@ -3162,7 +3086,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="101">
+  <borders count="100">
     <border>
       <left/>
       <right/>
@@ -3979,14 +3903,6 @@
       </left>
       <right/>
       <top/>
-      <bottom/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
@@ -4214,7 +4130,6 @@
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -4223,7 +4138,6 @@
       <bottom style="thick">
         <color theme="4"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -4232,7 +4146,6 @@
       <bottom style="thick">
         <color rgb="FFACCCEA"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -4241,7 +4154,6 @@
       <bottom style="medium">
         <color theme="4" tint="0.399980"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -4256,7 +4168,6 @@
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -4271,7 +4182,6 @@
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="double">
@@ -4286,7 +4196,6 @@
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -4295,7 +4204,6 @@
       <bottom style="double">
         <color rgb="FFFF8001"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -4306,7 +4214,6 @@
       <bottom style="double">
         <color theme="4"/>
       </bottom>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="3167">
@@ -12225,7 +12132,7 @@
     <xf numFmtId="2" fontId="16" fillId="0" borderId="3">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="87" fillId="9" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="0" fontId="83" fillId="9" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="197" fontId="19" fillId="0" borderId="0">
@@ -12664,7 +12571,7 @@
     <xf numFmtId="10" fontId="55" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="222" fontId="56" fillId="0" borderId="0">
+    <xf numFmtId="222" fontId="31" fillId="0" borderId="0">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -12686,34 +12593,34 @@
     <xf numFmtId="226" fontId="19" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="227" fontId="58" fillId="0" borderId="14" applyAlignment="0" applyFill="0" applyFont="0" applyProtection="0">
+    <xf numFmtId="227" fontId="57" fillId="0" borderId="14" applyAlignment="0" applyFill="0" applyFont="0" applyProtection="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="190" fontId="60" fillId="0" borderId="11">
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="190" fontId="59" fillId="0" borderId="11">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyBorder="0" applyFill="0" applyFont="0" applyNumberFormat="0" applyProtection="0">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="61" fillId="0" borderId="15">
+    <xf numFmtId="179" fontId="60" fillId="0" borderId="15">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="228" fontId="55" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="190" fontId="62" fillId="0" borderId="11">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="229" fontId="63" fillId="0" borderId="0">
+    <xf numFmtId="190" fontId="61" fillId="0" borderId="11">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="229" fontId="62" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
@@ -13502,43 +13409,43 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="16">
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="16">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="230" fontId="32" fillId="0" borderId="2" applyBorder="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="31" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="31" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="231" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="4" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="67" fillId="0" borderId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="31" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="31" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="231" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="4" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
@@ -13553,20 +13460,20 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="88" fillId="10" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="10" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="222" fontId="56" fillId="0" borderId="0">
+    <xf numFmtId="222" fontId="31" fillId="0" borderId="0">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="222" fontId="56" fillId="0" borderId="0">
+    <xf numFmtId="222" fontId="31" fillId="0" borderId="0">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -13594,7 +13501,7 @@
     <xf numFmtId="38" fontId="19" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="228" fontId="57" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+    <xf numFmtId="228" fontId="56" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="235" fontId="7" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
@@ -13603,7 +13510,7 @@
     <xf numFmtId="236" fontId="7" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="237" fontId="57" fillId="0" borderId="2">
+    <xf numFmtId="237" fontId="56" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="238" fontId="7" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
@@ -13615,11 +13522,11 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="222" fontId="56" fillId="0" borderId="0">
+    <xf numFmtId="222" fontId="31" fillId="0" borderId="0">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="222" fontId="56" fillId="0" borderId="0">
+    <xf numFmtId="222" fontId="31" fillId="0" borderId="0">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -13630,17 +13537,17 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="222" fontId="56" fillId="0" borderId="0">
+    <xf numFmtId="222" fontId="31" fillId="0" borderId="0">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="15">
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="15">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="15">
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="15">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="15">
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="15">
       <alignment vertical="center" textRotation="255"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="18">
@@ -13664,7 +13571,7 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" applyFill="0" applyProtection="0">
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" applyFill="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -13691,10 +13598,10 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="61" fillId="0" borderId="2" applyAlignment="0" applyFill="0" applyFont="0" applyProtection="0">
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="60" fillId="0" borderId="2" applyAlignment="0" applyFill="0" applyFont="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
@@ -13724,137 +13631,137 @@
     <xf numFmtId="5" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="120" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="121" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="92" applyAlignment="0" applyFont="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="122" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="123" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="124" fillId="0" borderId="93" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="125" fillId="0" borderId="94" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="126" fillId="0" borderId="95" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="126" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="127" fillId="14" borderId="96" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="128" fillId="15" borderId="97" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="129" fillId="15" borderId="96" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="130" fillId="16" borderId="98" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="131" fillId="0" borderId="99" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="132" fillId="0" borderId="100" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="133" fillId="10" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="134" fillId="17" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="135" fillId="18" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="136" fillId="19" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="137" fillId="20" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="137" fillId="21" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="136" fillId="22" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="136" fillId="23" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="137" fillId="24" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="137" fillId="25" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="136" fillId="26" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="136" fillId="27" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="137" fillId="28" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="137" fillId="29" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="136" fillId="30" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="136" fillId="31" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="137" fillId="32" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="137" fillId="33" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="136" fillId="34" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="136" fillId="35" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="137" fillId="36" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="137" fillId="37" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="136" fillId="38" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="136" fillId="39" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="137" fillId="40" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="137" fillId="41" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="136" fillId="42" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="138" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="0" fontId="111" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="91" applyAlignment="0" applyFont="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="114" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="115" fillId="0" borderId="92" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="116" fillId="0" borderId="93" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="117" fillId="0" borderId="94" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="117" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="118" fillId="13" borderId="95" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="119" fillId="14" borderId="96" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="120" fillId="14" borderId="95" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="121" fillId="15" borderId="97" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="98" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="0" borderId="99" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="10" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="16" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="126" fillId="17" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="18" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="128" fillId="19" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="128" fillId="20" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="21" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="22" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="128" fillId="23" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="128" fillId="24" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="25" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="26" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="128" fillId="27" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="128" fillId="28" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="29" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="30" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="128" fillId="31" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="128" fillId="32" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="33" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="34" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="128" fillId="35" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="128" fillId="36" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="37" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="38" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="128" fillId="39" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="128" fillId="40" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="41" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="129" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="359">
+  <cellXfs count="358">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3104">
       <alignment vertical="center"/>
@@ -13872,82 +13779,82 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="85" fillId="2" borderId="2" xfId="2792" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="81" fillId="2" borderId="2" xfId="2792" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="38" fontId="85" fillId="2" borderId="2" xfId="2792" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="38" fontId="81" fillId="2" borderId="2" xfId="2792" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="84" fillId="0" borderId="34" xfId="2637" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="34" xfId="2637" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="84" fillId="2" borderId="36" xfId="2637" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="70" fillId="2" borderId="36" xfId="2637" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="76" fillId="0" borderId="38" xfId="2792" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="74" fillId="0" borderId="38" xfId="2792" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="177" fontId="76" fillId="0" borderId="38" xfId="2792" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="74" fillId="0" borderId="38" xfId="2792" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="177" fontId="76" fillId="0" borderId="40" xfId="2792" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="74" fillId="0" borderId="40" xfId="2792" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="38" fontId="76" fillId="0" borderId="42" xfId="2792" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="38" fontId="74" fillId="0" borderId="42" xfId="2792" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="38" fontId="76" fillId="0" borderId="11" xfId="2792" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="38" fontId="74" fillId="0" borderId="11" xfId="2792" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="84" fillId="8" borderId="52" xfId="2637" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="70" fillId="8" borderId="52" xfId="2637" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="177" fontId="76" fillId="0" borderId="28" xfId="2792" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="74" fillId="0" borderId="28" xfId="2792" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="99" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="91" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="99" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="91" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -13956,26 +13863,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="96" fillId="0" borderId="77" xfId="2637" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="76" xfId="2637" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="77" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="76" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="24" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="183" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="104" fillId="0" borderId="79" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="96" fillId="0" borderId="78" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="80" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="79" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="80" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="82" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="79" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="81" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="183" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -13994,10 +13901,10 @@
     <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="85" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="85" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="84" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="84" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -14012,19 +13919,19 @@
     <xf numFmtId="225" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="85" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="84" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="85" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="84" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="85" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="84" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="85" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="85" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="84" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="84" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
@@ -14039,22 +13946,22 @@
     <xf numFmtId="0" fontId="53" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="3113">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="61" fillId="0" borderId="2" xfId="3114">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="2" xfId="3113" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="61" fillId="0" borderId="17" xfId="3114" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="17" xfId="3113" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="61" fillId="0" borderId="0" xfId="3114" applyBorder="1">
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="3113">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="60" fillId="0" borderId="2" xfId="3114">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="2" xfId="3113" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="60" fillId="0" borderId="17" xfId="3114" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="17" xfId="3113" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="60" fillId="0" borderId="0" xfId="3114" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3113">
@@ -14066,10 +13973,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3113" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="110" fillId="0" borderId="0" xfId="3113">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="110" fillId="0" borderId="8" xfId="3113" applyBorder="1">
+    <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="3113">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="101" fillId="0" borderId="8" xfId="3113" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3113" applyBorder="1">
@@ -14081,19 +13988,19 @@
     <xf numFmtId="0" fontId="6" fillId="12" borderId="0" xfId="3113" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="110" fillId="12" borderId="0" xfId="3113" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="91" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="101" fillId="12" borderId="0" xfId="3113" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="88" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="84" fillId="0" borderId="33" xfId="2637" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="33" xfId="2637" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="243" fontId="79" fillId="0" borderId="8" xfId="3102" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="243" fontId="77" fillId="0" borderId="8" xfId="3102" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="3102" applyAlignment="1">
@@ -14102,169 +14009,169 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3102" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="72" fillId="2" borderId="36" xfId="3102" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="70" fillId="2" borderId="36" xfId="3102" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="49" fontId="72" fillId="0" borderId="35" xfId="3102" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="183" fontId="76" fillId="0" borderId="37" xfId="3102" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="70" fillId="0" borderId="35" xfId="3102" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="183" fontId="74" fillId="0" borderId="37" xfId="3102" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="38" xfId="3102" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="38" xfId="3102" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="29" xfId="3102" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="29" xfId="3102" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="49" fontId="72" fillId="0" borderId="31" xfId="3102" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="183" fontId="76" fillId="0" borderId="39" xfId="3102" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="70" fillId="0" borderId="31" xfId="3102" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="183" fontId="74" fillId="0" borderId="39" xfId="3102" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="28" xfId="3102" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="28" xfId="3102" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="40" xfId="3102" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="40" xfId="3102" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="73" fillId="0" borderId="31" xfId="3102" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="71" fillId="0" borderId="31" xfId="3102" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="39" xfId="3102" quotePrefix="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="39" xfId="3102" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="72" fillId="2" borderId="2" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="2" borderId="2" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="70" fillId="2" borderId="2" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="2" borderId="2" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="72" fillId="2" borderId="2" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="70" fillId="2" borderId="2" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="77" fillId="2" borderId="32" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="75" fillId="2" borderId="32" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="72" fillId="2" borderId="11" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="2" borderId="11" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="70" fillId="2" borderId="11" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="2" borderId="11" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="72" fillId="2" borderId="11" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="70" fillId="2" borderId="11" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="41" xfId="3102" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="41" xfId="3102" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="42" xfId="3102" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="42" xfId="3102" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="42" xfId="3102" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="42" xfId="3102" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="42" xfId="3102" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="42" xfId="3102" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="43" xfId="3102" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="43" xfId="3102" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="44" xfId="3102" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="44" xfId="3102" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="38" xfId="3102" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="76" fillId="0" borderId="38" xfId="3102" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="38" xfId="3102" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="74" fillId="0" borderId="38" xfId="3102" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="30" xfId="3102" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="30" xfId="3102" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="47" xfId="3102" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="45" xfId="3102" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="45" xfId="3102" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="28" xfId="3102" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="76" fillId="0" borderId="28" xfId="3102" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="28" xfId="3102" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="74" fillId="0" borderId="28" xfId="3102" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="76" fillId="0" borderId="28" xfId="3102" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="74" fillId="0" borderId="28" xfId="3102" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="244" fontId="76" fillId="0" borderId="39" xfId="3102" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="244" fontId="74" fillId="0" borderId="39" xfId="3102" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="244" fontId="76" fillId="0" borderId="28" xfId="3102" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="244" fontId="74" fillId="0" borderId="28" xfId="3102" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="48" xfId="3102" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="48" xfId="3102" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="3102" applyAlignment="1">
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="3102" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="46" xfId="3102" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="76" fillId="0" borderId="40" xfId="3102" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="46" xfId="3102" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="74" fillId="0" borderId="40" xfId="3102" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="244" fontId="76" fillId="0" borderId="40" xfId="3102" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="244" fontId="74" fillId="0" borderId="40" xfId="3102" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="38" fontId="76" fillId="0" borderId="40" xfId="3102" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="38" fontId="74" fillId="0" borderId="40" xfId="3102" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="76" fillId="2" borderId="2" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="74" fillId="2" borderId="2" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="85" fillId="2" borderId="2" xfId="3102" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="81" fillId="2" borderId="2" xfId="3102" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="76" fillId="2" borderId="32" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="74" fillId="2" borderId="32" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="177" fontId="72" fillId="0" borderId="2" xfId="3102" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="70" fillId="0" borderId="2" xfId="3102" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="32" xfId="3102" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="32" xfId="3102" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="32" xfId="3102" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="32" xfId="3102" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="177" fontId="72" fillId="8" borderId="2" xfId="3102" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="70" fillId="8" borderId="2" xfId="3102" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="76" fillId="8" borderId="32" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="74" fillId="8" borderId="32" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="177" fontId="72" fillId="0" borderId="2" xfId="3102" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="70" fillId="0" borderId="2" xfId="3102" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="177" fontId="73" fillId="8" borderId="8" xfId="3102" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="71" fillId="8" borderId="8" xfId="3102" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="73" fillId="8" borderId="51" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="71" fillId="8" borderId="51" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="75" fillId="2" borderId="23" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="73" fillId="2" borderId="23" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="3102" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="75" fillId="2" borderId="25" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="3102" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="2" borderId="25" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="75" fillId="2" borderId="27" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="73" fillId="2" borderId="27" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="3102"/>
@@ -14274,652 +14181,649 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="3102" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="50" xfId="3102" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="8" borderId="50" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="8" borderId="8" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" xfId="3113" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="0" xfId="3113">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="2" borderId="49" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="2" borderId="50" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="2" borderId="50" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="74" fillId="0" borderId="28" xfId="2792" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="83" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="84" xfId="2792" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="85" xfId="2792" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="84" xfId="2792" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="85" xfId="2792" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="69" fillId="0" borderId="8" xfId="2792" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="69" fillId="0" borderId="27" xfId="2792" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="83" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="84" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="97" fillId="0" borderId="84" xfId="2792" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="97" fillId="0" borderId="85" xfId="2792" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="38" fontId="53" fillId="0" borderId="84" xfId="2792" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="38" fontId="53" fillId="0" borderId="85" xfId="2792" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="2792" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="25" xfId="2792" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="187" fontId="0" fillId="0" borderId="0" xfId="2792" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="187" fontId="0" fillId="0" borderId="25" xfId="2792" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="84" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="97" fillId="0" borderId="84" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="53" fillId="0" borderId="84" xfId="2792" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="53" fillId="0" borderId="85" xfId="2792" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="90" fillId="0" borderId="0" xfId="2792" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="38" fontId="90" fillId="0" borderId="25" xfId="2792" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="16" xfId="2792" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="82" xfId="2792" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="187" fontId="53" fillId="0" borderId="0" xfId="2792" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="187" fontId="53" fillId="0" borderId="25" xfId="2792" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="79" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="79" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="79" xfId="2792" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="80" xfId="2792" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="75" xfId="2637" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="76" xfId="2637" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="76" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="53" fillId="0" borderId="76" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="53" fillId="0" borderId="77" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="72" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="73" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="74" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="68" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="69" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="70" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="71" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="65" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="66" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="67" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="58" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="109" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="64" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="109" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="109" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="182" fontId="109" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="182" fontId="109" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="63" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="0" borderId="63" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="11" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="107" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="11" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="107" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="109" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="109" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="109" fillId="0" borderId="63" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="109" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="109" fillId="0" borderId="52" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="0" borderId="62" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="99" fillId="0" borderId="0" xfId="3113" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3113" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="0" xfId="3113" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="102" fillId="0" borderId="0" xfId="3113" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="3113" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="3113" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="98" fillId="0" borderId="0" xfId="3113" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="104" fillId="0" borderId="0" xfId="3113" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="2" borderId="21" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="2" borderId="22" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="2" borderId="24" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="2" borderId="0" xfId="3102" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="2" borderId="26" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="2" borderId="8" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="22" xfId="3102" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="3102" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="3102" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="8" xfId="3102" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="8" borderId="90" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="8" borderId="50" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="8" borderId="49" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="8" borderId="7" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="90" xfId="3102" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="72" fillId="0" borderId="50" xfId="3102" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="72" fillId="8" borderId="50" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="49" xfId="3102" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="72" fillId="8" borderId="8" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="7" xfId="3102" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" xfId="3113" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="117" fillId="0" borderId="0" xfId="3113">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="2" borderId="49" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="2" borderId="50" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="71" fillId="8" borderId="88" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="76" fillId="2" borderId="50" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="76" fillId="0" borderId="28" xfId="2792" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="84" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="71" fillId="8" borderId="89" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="85" xfId="2792" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="86" xfId="2792" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="85" xfId="2792" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="86" xfId="2792" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="70" fillId="8" borderId="72" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="8" borderId="73" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="8" borderId="89" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="7" borderId="88" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="7" borderId="89" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="71" fillId="7" borderId="72" xfId="3102" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="182" fontId="71" fillId="7" borderId="73" xfId="3102" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="182" fontId="71" fillId="7" borderId="74" xfId="3102" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="86" xfId="3102" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="6" xfId="3102" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="54" xfId="3102" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="86" xfId="2637" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="87" xfId="2637" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="2" borderId="59" xfId="2637" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="70" fillId="2" borderId="60" xfId="2637" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="70" fillId="0" borderId="8" xfId="2792" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="70" fillId="0" borderId="27" xfId="2792" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="105" fillId="0" borderId="84" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="70" fillId="2" borderId="90" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="105" fillId="0" borderId="85" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="70" fillId="2" borderId="50" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="106" fillId="0" borderId="85" xfId="2792" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="106" fillId="0" borderId="86" xfId="2792" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="38" fontId="53" fillId="0" borderId="85" xfId="2792" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="38" fontId="53" fillId="0" borderId="86" xfId="2792" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="2792" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="25" xfId="2792" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="187" fontId="0" fillId="0" borderId="0" xfId="2792" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="187" fontId="0" fillId="0" borderId="25" xfId="2792" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="85" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="106" fillId="0" borderId="85" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="53" fillId="0" borderId="85" xfId="2792" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="53" fillId="0" borderId="86" xfId="2792" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="105" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="105" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="105" fillId="0" borderId="0" xfId="2792" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="38" fontId="105" fillId="0" borderId="25" xfId="2792" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="16" xfId="2792" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="83" xfId="2792" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="106" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="187" fontId="53" fillId="0" borderId="0" xfId="2792" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="187" fontId="53" fillId="0" borderId="25" xfId="2792" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="80" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="80" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="80" xfId="2792" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="81" xfId="2792" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="76" xfId="2637" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="77" xfId="2637" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="77" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="53" fillId="0" borderId="77" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="53" fillId="0" borderId="78" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="98" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="98" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="98" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="98" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="98" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="98" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="98" fillId="0" borderId="63" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="98" fillId="0" borderId="73" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="98" fillId="0" borderId="74" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="98" fillId="0" borderId="75" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="91" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="98" fillId="0" borderId="68" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="98" fillId="0" borderId="69" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="98" fillId="0" borderId="70" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="98" fillId="0" borderId="71" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="98" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="98" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="98" fillId="0" borderId="72" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="98" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="98" fillId="0" borderId="62" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="96" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="95" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="95" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="95" fillId="0" borderId="65" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="95" fillId="0" borderId="66" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="95" fillId="0" borderId="67" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="98" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="98" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="58" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="118" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="93" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="93" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="95" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="95" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="95" fillId="0" borderId="64" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="95" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="95" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="95" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="118" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="118" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="182" fontId="118" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="182" fontId="118" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="96" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="96" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="96" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="63" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="96" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="63" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="11" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="116" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="11" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="116" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="118" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="118" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="118" fillId="0" borderId="63" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="95" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="95" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="96" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="118" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="118" fillId="0" borderId="52" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="62" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="108" fillId="0" borderId="0" xfId="3113" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3113" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="117" fillId="0" borderId="0" xfId="3113" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="111" fillId="0" borderId="0" xfId="3113" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="3113" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="3113" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="107" fillId="0" borderId="0" xfId="3113" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="113" fillId="0" borderId="0" xfId="3113" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="75" fillId="2" borderId="21" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="75" fillId="2" borderId="22" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="75" fillId="2" borderId="24" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="75" fillId="2" borderId="0" xfId="3102" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="75" fillId="2" borderId="26" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="75" fillId="2" borderId="8" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="0" borderId="22" xfId="3102" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="3102" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="3102" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="8" xfId="3102" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="8" borderId="91" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="8" borderId="50" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="8" borderId="49" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="8" borderId="7" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="91" xfId="3102" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="50" xfId="3102" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="49" xfId="3102" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="7" xfId="3102" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="8" borderId="89" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="8" borderId="90" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="8" borderId="73" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="8" borderId="74" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="8" borderId="90" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="7" borderId="89" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="7" borderId="90" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="73" fillId="7" borderId="73" xfId="3102" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="182" fontId="73" fillId="7" borderId="74" xfId="3102" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="182" fontId="73" fillId="7" borderId="75" xfId="3102" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="87" xfId="3102" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="6" xfId="3102" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="54" xfId="3102" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="84" fillId="0" borderId="87" xfId="2637" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="84" fillId="0" borderId="88" xfId="2637" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="84" fillId="2" borderId="59" xfId="2637" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="84" fillId="2" borderId="60" xfId="2637" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="2" borderId="91" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="72" fillId="2" borderId="90" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="72" fillId="2" borderId="50" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="74" fillId="2" borderId="91" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="90" xfId="3102" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="74" fillId="2" borderId="50" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="50" xfId="3102" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="91" xfId="3102" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="50" xfId="3102" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="49" xfId="3102" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="49" xfId="3102" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="7" xfId="3102" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="7" xfId="3102" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="50" xfId="3102" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="50" xfId="3102" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="86" fillId="8" borderId="0" xfId="3102" quotePrefix="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="82" fillId="8" borderId="0" xfId="3102" quotePrefix="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="8" xfId="3102" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="8" xfId="3102" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="73" fillId="8" borderId="87" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="71" fillId="8" borderId="86" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="73" fillId="8" borderId="88" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="71" fillId="8" borderId="87" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="73" fillId="8" borderId="56" xfId="3102" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="71" fillId="8" borderId="56" xfId="3102" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="182" fontId="73" fillId="8" borderId="6" xfId="3102" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="71" fillId="8" borderId="6" xfId="3102" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="182" fontId="73" fillId="8" borderId="54" xfId="3102" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="71" fillId="8" borderId="54" xfId="3102" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="73" fillId="7" borderId="59" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="71" fillId="7" borderId="59" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="73" fillId="7" borderId="60" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="71" fillId="7" borderId="60" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="73" fillId="7" borderId="65" xfId="3102" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="71" fillId="7" borderId="65" xfId="3102" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="182" fontId="73" fillId="7" borderId="66" xfId="3102" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="71" fillId="7" borderId="66" xfId="3102" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="182" fontId="73" fillId="7" borderId="67" xfId="3102" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="71" fillId="7" borderId="67" xfId="3102" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
@@ -18257,7 +18161,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="0" y="8636635"/>
-            <a:ext cx="3175" cy="0"/>
+            <a:ext cx="0" cy="0"/>
           </a:xfrm>
           <a:prstGeom prst="rect"/>
           <a:noFill/>
@@ -18305,7 +18209,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="0" y="8636635"/>
-            <a:ext cx="3175" cy="0"/>
+            <a:ext cx="0" cy="0"/>
           </a:xfrm>
           <a:prstGeom prst="rect"/>
           <a:noFill/>
@@ -18353,7 +18257,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="0" y="8636635"/>
-            <a:ext cx="3175" cy="0"/>
+            <a:ext cx="0" cy="0"/>
           </a:xfrm>
           <a:prstGeom prst="rect"/>
           <a:noFill/>
@@ -18414,7 +18318,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="0" y="8636635"/>
-            <a:ext cx="3175" cy="0"/>
+            <a:ext cx="0" cy="0"/>
           </a:xfrm>
           <a:prstGeom prst="rect"/>
           <a:noFill/>
@@ -19098,7 +19002,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AF1591"/>
+  <dimension ref="A1:AC1591"/>
   <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="13.500000"/>
   <cols>
     <col min="1" max="2" style="66" width="3.33833334" customWidth="1" outlineLevel="0"/>
@@ -19108,39 +19012,39 @@
     <col min="257" max="16384" style="64" width="8.78277800" customWidth="1" outlineLevel="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:32" s="70" customFormat="1" ht="42.000000" customHeight="1">
-      <c r="B1" s="298" t="s">
+    <row r="1" spans="2:29" s="70" customFormat="1" ht="42.000000" customHeight="1">
+      <c r="B1" s="297" t="s">
         <v>126</v>
       </c>
-      <c r="C1" s="298"/>
-      <c r="D1" s="298"/>
-      <c r="E1" s="298"/>
-      <c r="F1" s="298"/>
-      <c r="G1" s="298"/>
-      <c r="H1" s="298"/>
-      <c r="I1" s="298"/>
-      <c r="J1" s="298"/>
-      <c r="K1" s="298"/>
-      <c r="L1" s="298"/>
-      <c r="M1" s="298"/>
-      <c r="N1" s="298"/>
-      <c r="O1" s="298"/>
-      <c r="P1" s="298"/>
-      <c r="Q1" s="298"/>
-      <c r="R1" s="298"/>
-      <c r="S1" s="298"/>
-      <c r="T1" s="298"/>
-      <c r="U1" s="298"/>
-      <c r="V1" s="298"/>
-      <c r="W1" s="298"/>
-      <c r="X1" s="298"/>
-      <c r="Y1" s="298"/>
-      <c r="Z1" s="298"/>
-      <c r="AA1" s="298"/>
-      <c r="AB1" s="298"/>
-      <c r="AC1" s="298"/>
-    </row>
-    <row r="2" spans="2:32" s="70" customFormat="1" ht="12.000000" customHeight="1">
+      <c r="C1" s="297"/>
+      <c r="D1" s="297"/>
+      <c r="E1" s="297"/>
+      <c r="F1" s="297"/>
+      <c r="G1" s="297"/>
+      <c r="H1" s="297"/>
+      <c r="I1" s="297"/>
+      <c r="J1" s="297"/>
+      <c r="K1" s="297"/>
+      <c r="L1" s="297"/>
+      <c r="M1" s="297"/>
+      <c r="N1" s="297"/>
+      <c r="O1" s="297"/>
+      <c r="P1" s="297"/>
+      <c r="Q1" s="297"/>
+      <c r="R1" s="297"/>
+      <c r="S1" s="297"/>
+      <c r="T1" s="297"/>
+      <c r="U1" s="297"/>
+      <c r="V1" s="297"/>
+      <c r="W1" s="297"/>
+      <c r="X1" s="297"/>
+      <c r="Y1" s="297"/>
+      <c r="Z1" s="297"/>
+      <c r="AA1" s="297"/>
+      <c r="AB1" s="297"/>
+      <c r="AC1" s="297"/>
+    </row>
+    <row r="2" spans="2:29" s="70" customFormat="1" ht="12.000000" customHeight="1">
       <c r="B2" s="71"/>
       <c r="C2" s="71"/>
       <c r="D2" s="71"/>
@@ -19170,39 +19074,39 @@
       <c r="AB2" s="73"/>
       <c r="AC2" s="73"/>
     </row>
-    <row r="3" spans="2:32" s="70" customFormat="1" ht="18.000000" customHeight="1">
-      <c r="B3" s="299" t="s">
+    <row r="3" spans="2:29" s="70" customFormat="1" ht="18.000000" customHeight="1">
+      <c r="B3" s="298" t="s">
         <v>191</v>
       </c>
-      <c r="C3" s="299"/>
-      <c r="D3" s="299"/>
-      <c r="E3" s="299"/>
-      <c r="F3" s="299"/>
-      <c r="G3" s="299"/>
-      <c r="H3" s="299"/>
-      <c r="I3" s="299"/>
-      <c r="J3" s="299"/>
-      <c r="K3" s="299"/>
-      <c r="L3" s="299"/>
-      <c r="M3" s="299"/>
-      <c r="N3" s="299"/>
-      <c r="O3" s="299"/>
-      <c r="P3" s="299"/>
-      <c r="Q3" s="299"/>
-      <c r="R3" s="299"/>
-      <c r="S3" s="299"/>
-      <c r="T3" s="299"/>
-      <c r="U3" s="299"/>
-      <c r="V3" s="299"/>
-      <c r="W3" s="299"/>
-      <c r="X3" s="299"/>
-      <c r="Y3" s="299"/>
-      <c r="Z3" s="299"/>
-      <c r="AA3" s="299"/>
-      <c r="AB3" s="299"/>
-      <c r="AC3" s="299"/>
-    </row>
-    <row r="4" spans="2:32" s="70" customFormat="1" ht="7.500000" customHeight="1">
+      <c r="C3" s="298"/>
+      <c r="D3" s="298"/>
+      <c r="E3" s="298"/>
+      <c r="F3" s="298"/>
+      <c r="G3" s="298"/>
+      <c r="H3" s="298"/>
+      <c r="I3" s="298"/>
+      <c r="J3" s="298"/>
+      <c r="K3" s="298"/>
+      <c r="L3" s="298"/>
+      <c r="M3" s="298"/>
+      <c r="N3" s="298"/>
+      <c r="O3" s="298"/>
+      <c r="P3" s="298"/>
+      <c r="Q3" s="298"/>
+      <c r="R3" s="298"/>
+      <c r="S3" s="298"/>
+      <c r="T3" s="298"/>
+      <c r="U3" s="298"/>
+      <c r="V3" s="298"/>
+      <c r="W3" s="298"/>
+      <c r="X3" s="298"/>
+      <c r="Y3" s="298"/>
+      <c r="Z3" s="298"/>
+      <c r="AA3" s="298"/>
+      <c r="AB3" s="298"/>
+      <c r="AC3" s="298"/>
+    </row>
+    <row r="4" spans="2:29" s="70" customFormat="1" ht="7.500000" customHeight="1">
       <c r="B4" s="147"/>
       <c r="C4" s="147"/>
       <c r="D4" s="147"/>
@@ -19232,7 +19136,7 @@
       <c r="AB4" s="147"/>
       <c r="AC4" s="147"/>
     </row>
-    <row r="5" spans="2:32" s="70" customFormat="1" ht="5.000000" customHeight="1">
+    <row r="5" spans="2:29" s="70" customFormat="1" ht="5.000000" customHeight="1">
       <c r="B5" s="71"/>
       <c r="C5" s="71"/>
       <c r="D5" s="71"/>
@@ -19262,13 +19166,13 @@
       <c r="AB5" s="73"/>
       <c r="AC5" s="73"/>
     </row>
-    <row r="6" spans="2:32" s="70" customFormat="1" ht="20.000000" customHeight="1">
-      <c r="B6" s="295" t="s">
+    <row r="6" spans="2:29" s="70" customFormat="1" ht="20.000000" customHeight="1">
+      <c r="B6" s="294" t="s">
         <v>125</v>
       </c>
-      <c r="C6" s="295"/>
-      <c r="D6" s="295"/>
-      <c r="E6" s="295"/>
+      <c r="C6" s="294"/>
+      <c r="D6" s="294"/>
+      <c r="E6" s="294"/>
       <c r="F6" s="71" t="s">
         <v>124</v>
       </c>
@@ -19296,146 +19200,122 @@
       <c r="AB6" s="73"/>
       <c r="AC6" s="73"/>
     </row>
-    <row r="7" spans="2:32" s="70" customFormat="1" ht="20.000000" customHeight="1">
-      <c r="B7" s="295" t="s">
+    <row r="7" spans="2:29" s="70" customFormat="1" ht="20.000000" customHeight="1">
+      <c r="B7" s="294" t="s">
         <v>123</v>
       </c>
-      <c r="C7" s="295"/>
-      <c r="D7" s="295"/>
-      <c r="E7" s="295"/>
-      <c r="F7" s="300">
+      <c r="C7" s="294"/>
+      <c r="D7" s="294"/>
+      <c r="E7" s="294"/>
+      <c r="F7" s="299">
         <v>46072</v>
       </c>
-      <c r="G7" s="300"/>
-      <c r="H7" s="300"/>
-      <c r="I7" s="300"/>
-      <c r="J7" s="300"/>
-      <c r="K7" s="300"/>
-      <c r="L7" s="300"/>
-      <c r="M7" s="300"/>
-      <c r="N7" s="300"/>
-      <c r="O7" s="300"/>
-      <c r="P7" s="300"/>
-      <c r="Q7" s="300"/>
-      <c r="R7" s="300"/>
-      <c r="S7" s="300"/>
-      <c r="T7" s="300"/>
-      <c r="U7" s="300"/>
-      <c r="V7" s="300"/>
-      <c r="W7" s="300"/>
-      <c r="X7" s="300"/>
-      <c r="Y7" s="300"/>
-      <c r="Z7" s="300"/>
-      <c r="AA7" s="300"/>
-      <c r="AB7" s="300"/>
-      <c r="AC7" s="300"/>
-    </row>
-    <row r="8" spans="2:32" s="70" customFormat="1" ht="20.000000" customHeight="1">
-      <c r="B8" s="295" t="s">
+      <c r="G7" s="299"/>
+      <c r="H7" s="299"/>
+      <c r="I7" s="299"/>
+      <c r="J7" s="299"/>
+      <c r="K7" s="299"/>
+      <c r="L7" s="299"/>
+      <c r="M7" s="299"/>
+      <c r="N7" s="299"/>
+      <c r="O7" s="299"/>
+      <c r="P7" s="299"/>
+      <c r="Q7" s="299"/>
+      <c r="R7" s="299"/>
+      <c r="S7" s="299"/>
+      <c r="T7" s="299"/>
+      <c r="U7" s="299"/>
+      <c r="V7" s="299"/>
+      <c r="W7" s="299"/>
+      <c r="X7" s="299"/>
+      <c r="Y7" s="299"/>
+      <c r="Z7" s="299"/>
+      <c r="AA7" s="299"/>
+      <c r="AB7" s="299"/>
+      <c r="AC7" s="299"/>
+    </row>
+    <row r="8" spans="2:29" s="70" customFormat="1" ht="20.000000" customHeight="1">
+      <c r="B8" s="294" t="s">
         <v>122</v>
       </c>
-      <c r="C8" s="295"/>
-      <c r="D8" s="295"/>
-      <c r="E8" s="295"/>
-      <c r="F8" s="297" t="s">
+      <c r="C8" s="294"/>
+      <c r="D8" s="294"/>
+      <c r="E8" s="294"/>
+      <c r="F8" s="296" t="s">
         <v>189</v>
       </c>
-      <c r="G8" s="297"/>
-      <c r="H8" s="297"/>
-      <c r="I8" s="297"/>
-      <c r="J8" s="297"/>
-      <c r="K8" s="297"/>
-      <c r="L8" s="297"/>
-      <c r="M8" s="297"/>
-      <c r="N8" s="297"/>
-      <c r="O8" s="297"/>
-      <c r="P8" s="297"/>
-      <c r="Q8" s="297"/>
-      <c r="R8" s="297"/>
-      <c r="S8" s="297"/>
-      <c r="T8" s="297"/>
-      <c r="U8" s="297"/>
-      <c r="V8" s="297"/>
-      <c r="W8" s="297"/>
-      <c r="X8" s="297"/>
-      <c r="Y8" s="297"/>
-      <c r="Z8" s="297"/>
-      <c r="AA8" s="297"/>
-      <c r="AB8" s="297"/>
-      <c r="AC8" s="297"/>
-    </row>
-    <row r="9" spans="2:32" s="70" customFormat="1" ht="20.000000" customHeight="1">
-      <c r="B9" s="295" t="s">
+      <c r="G8" s="296"/>
+      <c r="H8" s="296"/>
+      <c r="I8" s="296"/>
+      <c r="J8" s="296"/>
+      <c r="K8" s="296"/>
+      <c r="L8" s="296"/>
+      <c r="M8" s="296"/>
+      <c r="N8" s="296"/>
+      <c r="O8" s="296"/>
+      <c r="P8" s="296"/>
+      <c r="Q8" s="296"/>
+      <c r="R8" s="296"/>
+      <c r="S8" s="296"/>
+      <c r="T8" s="296"/>
+      <c r="U8" s="296"/>
+      <c r="V8" s="296"/>
+      <c r="W8" s="296"/>
+      <c r="X8" s="296"/>
+      <c r="Y8" s="296"/>
+      <c r="Z8" s="296"/>
+      <c r="AA8" s="296"/>
+      <c r="AB8" s="296"/>
+      <c r="AC8" s="296"/>
+    </row>
+    <row r="9" spans="2:29" s="70" customFormat="1" ht="20.000000" customHeight="1">
+      <c r="B9" s="294" t="s">
         <v>121</v>
       </c>
-      <c r="C9" s="295"/>
-      <c r="D9" s="295"/>
-      <c r="E9" s="295"/>
+      <c r="C9" s="294"/>
+      <c r="D9" s="294"/>
+      <c r="E9" s="294"/>
       <c r="F9" s="148" t="s">
         <v>120</v>
       </c>
       <c r="G9" s="148"/>
       <c r="H9" s="148"/>
-      <c r="I9" s="70"/>
-      <c r="J9" s="70"/>
-      <c r="K9" s="70"/>
-      <c r="L9" s="70"/>
-      <c r="M9" s="70"/>
-      <c r="N9" s="70"/>
-      <c r="O9" s="70"/>
-      <c r="P9" s="70"/>
-      <c r="Q9" s="70"/>
-      <c r="R9" s="70"/>
-      <c r="S9" s="70"/>
-      <c r="T9" s="70"/>
-      <c r="U9" s="70"/>
-      <c r="V9" s="70"/>
-      <c r="W9" s="70"/>
-      <c r="X9" s="70"/>
-      <c r="Y9" s="70"/>
-      <c r="Z9" s="70"/>
-      <c r="AA9" s="70"/>
-      <c r="AB9" s="70"/>
-      <c r="AC9" s="70"/>
-      <c r="AD9" s="70"/>
-      <c r="AE9" s="70"/>
-      <c r="AF9" s="70"/>
-    </row>
-    <row r="10" spans="2:32" s="70" customFormat="1" ht="20.000000" customHeight="1">
-      <c r="B10" s="295" t="s">
+    </row>
+    <row r="10" spans="2:29" s="70" customFormat="1" ht="20.000000" customHeight="1">
+      <c r="B10" s="294" t="s">
         <v>119</v>
       </c>
-      <c r="C10" s="295"/>
-      <c r="D10" s="295"/>
-      <c r="E10" s="295"/>
-      <c r="F10" s="297" t="s">
+      <c r="C10" s="294"/>
+      <c r="D10" s="294"/>
+      <c r="E10" s="294"/>
+      <c r="F10" s="296" t="s">
         <v>197</v>
       </c>
-      <c r="G10" s="297"/>
-      <c r="H10" s="297"/>
-      <c r="I10" s="297"/>
-      <c r="J10" s="297"/>
-      <c r="K10" s="297"/>
-      <c r="L10" s="297"/>
-      <c r="M10" s="297"/>
-      <c r="N10" s="297"/>
-      <c r="O10" s="297"/>
-      <c r="P10" s="297"/>
-      <c r="Q10" s="297"/>
-      <c r="R10" s="297"/>
-      <c r="S10" s="297"/>
-      <c r="T10" s="297"/>
-      <c r="U10" s="297"/>
-      <c r="V10" s="297"/>
-      <c r="W10" s="297"/>
-      <c r="X10" s="297"/>
-      <c r="Y10" s="297"/>
-      <c r="Z10" s="297"/>
-      <c r="AA10" s="297"/>
-      <c r="AB10" s="297"/>
-      <c r="AC10" s="297"/>
-    </row>
-    <row r="11" spans="2:32" s="70" customFormat="1" ht="13.500000" hidden="1" customHeight="1">
+      <c r="G10" s="296"/>
+      <c r="H10" s="296"/>
+      <c r="I10" s="296"/>
+      <c r="J10" s="296"/>
+      <c r="K10" s="296"/>
+      <c r="L10" s="296"/>
+      <c r="M10" s="296"/>
+      <c r="N10" s="296"/>
+      <c r="O10" s="296"/>
+      <c r="P10" s="296"/>
+      <c r="Q10" s="296"/>
+      <c r="R10" s="296"/>
+      <c r="S10" s="296"/>
+      <c r="T10" s="296"/>
+      <c r="U10" s="296"/>
+      <c r="V10" s="296"/>
+      <c r="W10" s="296"/>
+      <c r="X10" s="296"/>
+      <c r="Y10" s="296"/>
+      <c r="Z10" s="296"/>
+      <c r="AA10" s="296"/>
+      <c r="AB10" s="296"/>
+      <c r="AC10" s="296"/>
+    </row>
+    <row r="11" spans="2:29" s="70" customFormat="1" ht="13.500000" hidden="1" customHeight="1">
       <c r="B11" s="75"/>
       <c r="C11" s="75"/>
       <c r="D11" s="75"/>
@@ -19465,7 +19345,7 @@
       <c r="AB11" s="74"/>
       <c r="AC11" s="74"/>
     </row>
-    <row r="12" spans="2:32" s="70" customFormat="1" ht="7.500000" customHeight="1">
+    <row r="12" spans="2:29" s="70" customFormat="1" ht="7.500000" customHeight="1">
       <c r="B12" s="77"/>
       <c r="C12" s="77"/>
       <c r="D12" s="77"/>
@@ -19495,7 +19375,7 @@
       <c r="AB12" s="78"/>
       <c r="AC12" s="78"/>
     </row>
-    <row r="13" spans="2:32" s="70" customFormat="1" ht="5.000000" customHeight="1">
+    <row r="13" spans="2:29" s="70" customFormat="1" ht="5.000000" customHeight="1">
       <c r="B13" s="71"/>
       <c r="C13" s="71"/>
       <c r="D13" s="71"/>
@@ -19525,39 +19405,39 @@
       <c r="AB13" s="73"/>
       <c r="AC13" s="73"/>
     </row>
-    <row r="14" spans="2:32" s="70" customFormat="1" ht="20.000000" customHeight="1">
-      <c r="B14" s="296" t="s">
+    <row r="14" spans="2:29" s="70" customFormat="1" ht="20.000000" customHeight="1">
+      <c r="B14" s="295" t="s">
         <v>228</v>
       </c>
-      <c r="C14" s="296"/>
-      <c r="D14" s="296"/>
-      <c r="E14" s="296"/>
-      <c r="F14" s="296"/>
-      <c r="G14" s="296"/>
-      <c r="H14" s="296"/>
-      <c r="I14" s="296"/>
-      <c r="J14" s="296"/>
-      <c r="K14" s="296"/>
-      <c r="L14" s="296"/>
-      <c r="M14" s="296"/>
-      <c r="N14" s="296"/>
-      <c r="O14" s="296"/>
-      <c r="P14" s="296"/>
-      <c r="Q14" s="296"/>
-      <c r="R14" s="296"/>
-      <c r="S14" s="296"/>
-      <c r="T14" s="296"/>
-      <c r="U14" s="296"/>
-      <c r="V14" s="296"/>
-      <c r="W14" s="296"/>
-      <c r="X14" s="296"/>
-      <c r="Y14" s="296"/>
-      <c r="Z14" s="296"/>
-      <c r="AA14" s="296"/>
-      <c r="AB14" s="296"/>
-      <c r="AC14" s="296"/>
-    </row>
-    <row r="15" spans="2:32" s="70" customFormat="1" ht="10.000000" customHeight="1">
+      <c r="C14" s="295"/>
+      <c r="D14" s="295"/>
+      <c r="E14" s="295"/>
+      <c r="F14" s="295"/>
+      <c r="G14" s="295"/>
+      <c r="H14" s="295"/>
+      <c r="I14" s="295"/>
+      <c r="J14" s="295"/>
+      <c r="K14" s="295"/>
+      <c r="L14" s="295"/>
+      <c r="M14" s="295"/>
+      <c r="N14" s="295"/>
+      <c r="O14" s="295"/>
+      <c r="P14" s="295"/>
+      <c r="Q14" s="295"/>
+      <c r="R14" s="295"/>
+      <c r="S14" s="295"/>
+      <c r="T14" s="295"/>
+      <c r="U14" s="295"/>
+      <c r="V14" s="295"/>
+      <c r="W14" s="295"/>
+      <c r="X14" s="295"/>
+      <c r="Y14" s="295"/>
+      <c r="Z14" s="295"/>
+      <c r="AA14" s="295"/>
+      <c r="AB14" s="295"/>
+      <c r="AC14" s="295"/>
+    </row>
+    <row r="15" spans="2:29" s="70" customFormat="1" ht="10.000000" customHeight="1">
       <c r="B15" s="71"/>
       <c r="C15" s="71"/>
       <c r="D15" s="71"/>
@@ -19587,7 +19467,7 @@
       <c r="AB15" s="73"/>
       <c r="AC15" s="73"/>
     </row>
-    <row r="16" spans="2:32" s="70" customFormat="1" ht="70.500000" customHeight="1">
+    <row r="16" spans="2:29" s="70" customFormat="1" ht="70.500000" customHeight="1">
       <c r="B16" s="76" t="s">
         <v>229</v>
       </c>
@@ -19712,204 +19592,204 @@
       <c r="AC19" s="73"/>
     </row>
     <row r="20" spans="2:29" s="70" customFormat="1" ht="20.000000" customHeight="1">
-      <c r="B20" s="296" t="s">
+      <c r="B20" s="295" t="s">
         <v>231</v>
       </c>
-      <c r="C20" s="296"/>
-      <c r="D20" s="296"/>
-      <c r="E20" s="296"/>
-      <c r="F20" s="296"/>
-      <c r="G20" s="296"/>
-      <c r="H20" s="296"/>
-      <c r="I20" s="296"/>
-      <c r="J20" s="296"/>
-      <c r="K20" s="296"/>
-      <c r="L20" s="296"/>
-      <c r="M20" s="296"/>
-      <c r="N20" s="296"/>
-      <c r="O20" s="296"/>
-      <c r="P20" s="296"/>
-      <c r="Q20" s="296"/>
-      <c r="R20" s="296"/>
-      <c r="S20" s="296"/>
-      <c r="T20" s="296"/>
-      <c r="U20" s="296"/>
-      <c r="V20" s="296"/>
-      <c r="W20" s="296"/>
-      <c r="X20" s="296"/>
-      <c r="Y20" s="296"/>
-      <c r="Z20" s="296"/>
-      <c r="AA20" s="296"/>
-      <c r="AB20" s="296"/>
-      <c r="AC20" s="296"/>
+      <c r="C20" s="295"/>
+      <c r="D20" s="295"/>
+      <c r="E20" s="295"/>
+      <c r="F20" s="295"/>
+      <c r="G20" s="295"/>
+      <c r="H20" s="295"/>
+      <c r="I20" s="295"/>
+      <c r="J20" s="295"/>
+      <c r="K20" s="295"/>
+      <c r="L20" s="295"/>
+      <c r="M20" s="295"/>
+      <c r="N20" s="295"/>
+      <c r="O20" s="295"/>
+      <c r="P20" s="295"/>
+      <c r="Q20" s="295"/>
+      <c r="R20" s="295"/>
+      <c r="S20" s="295"/>
+      <c r="T20" s="295"/>
+      <c r="U20" s="295"/>
+      <c r="V20" s="295"/>
+      <c r="W20" s="295"/>
+      <c r="X20" s="295"/>
+      <c r="Y20" s="295"/>
+      <c r="Z20" s="295"/>
+      <c r="AA20" s="295"/>
+      <c r="AB20" s="295"/>
+      <c r="AC20" s="295"/>
     </row>
     <row r="21" spans="2:29" s="70" customFormat="1" ht="20.000000" customHeight="1">
       <c r="B21" s="71"/>
       <c r="C21" s="71"/>
       <c r="D21" s="71"/>
       <c r="E21" s="71"/>
-      <c r="F21" s="296" t="s">
+      <c r="F21" s="295" t="s">
         <v>235</v>
       </c>
-      <c r="G21" s="296"/>
-      <c r="H21" s="296"/>
-      <c r="I21" s="296"/>
-      <c r="J21" s="296"/>
-      <c r="K21" s="296"/>
-      <c r="L21" s="297" t="s">
+      <c r="G21" s="295"/>
+      <c r="H21" s="295"/>
+      <c r="I21" s="295"/>
+      <c r="J21" s="295"/>
+      <c r="K21" s="295"/>
+      <c r="L21" s="296" t="s">
         <v>189</v>
       </c>
-      <c r="M21" s="297"/>
-      <c r="N21" s="297"/>
-      <c r="O21" s="297"/>
-      <c r="P21" s="297"/>
-      <c r="Q21" s="297"/>
-      <c r="R21" s="297"/>
-      <c r="S21" s="297"/>
-      <c r="T21" s="297"/>
-      <c r="U21" s="297"/>
-      <c r="V21" s="297"/>
-      <c r="W21" s="297"/>
-      <c r="X21" s="297"/>
-      <c r="Y21" s="297"/>
-      <c r="Z21" s="297"/>
-      <c r="AA21" s="297"/>
-      <c r="AB21" s="297"/>
-      <c r="AC21" s="297"/>
+      <c r="M21" s="296"/>
+      <c r="N21" s="296"/>
+      <c r="O21" s="296"/>
+      <c r="P21" s="296"/>
+      <c r="Q21" s="296"/>
+      <c r="R21" s="296"/>
+      <c r="S21" s="296"/>
+      <c r="T21" s="296"/>
+      <c r="U21" s="296"/>
+      <c r="V21" s="296"/>
+      <c r="W21" s="296"/>
+      <c r="X21" s="296"/>
+      <c r="Y21" s="296"/>
+      <c r="Z21" s="296"/>
+      <c r="AA21" s="296"/>
+      <c r="AB21" s="296"/>
+      <c r="AC21" s="296"/>
     </row>
     <row r="22" spans="2:29" s="70" customFormat="1" ht="20.000000" customHeight="1">
       <c r="B22" s="71"/>
       <c r="C22" s="71"/>
       <c r="D22" s="71"/>
       <c r="E22" s="71"/>
-      <c r="F22" s="296" t="s">
+      <c r="F22" s="295" t="s">
         <v>245</v>
       </c>
-      <c r="G22" s="296"/>
-      <c r="H22" s="296"/>
-      <c r="I22" s="296"/>
-      <c r="J22" s="296"/>
-      <c r="K22" s="296"/>
-      <c r="L22" s="297" t="s">
+      <c r="G22" s="295"/>
+      <c r="H22" s="295"/>
+      <c r="I22" s="295"/>
+      <c r="J22" s="295"/>
+      <c r="K22" s="295"/>
+      <c r="L22" s="296" t="s">
         <v>128</v>
       </c>
-      <c r="M22" s="297"/>
-      <c r="N22" s="297"/>
-      <c r="O22" s="297"/>
-      <c r="P22" s="297"/>
-      <c r="Q22" s="297"/>
-      <c r="R22" s="297"/>
-      <c r="S22" s="297"/>
-      <c r="T22" s="297"/>
-      <c r="U22" s="297"/>
-      <c r="V22" s="297"/>
-      <c r="W22" s="297"/>
-      <c r="X22" s="297"/>
-      <c r="Y22" s="297"/>
-      <c r="Z22" s="297"/>
-      <c r="AA22" s="297"/>
-      <c r="AB22" s="297"/>
-      <c r="AC22" s="297"/>
+      <c r="M22" s="296"/>
+      <c r="N22" s="296"/>
+      <c r="O22" s="296"/>
+      <c r="P22" s="296"/>
+      <c r="Q22" s="296"/>
+      <c r="R22" s="296"/>
+      <c r="S22" s="296"/>
+      <c r="T22" s="296"/>
+      <c r="U22" s="296"/>
+      <c r="V22" s="296"/>
+      <c r="W22" s="296"/>
+      <c r="X22" s="296"/>
+      <c r="Y22" s="296"/>
+      <c r="Z22" s="296"/>
+      <c r="AA22" s="296"/>
+      <c r="AB22" s="296"/>
+      <c r="AC22" s="296"/>
     </row>
     <row r="23" spans="2:29" s="70" customFormat="1" ht="20.000000" customHeight="1">
       <c r="B23" s="71"/>
       <c r="C23" s="71"/>
       <c r="D23" s="71"/>
       <c r="E23" s="71"/>
-      <c r="F23" s="296" t="s">
+      <c r="F23" s="295" t="s">
         <v>246</v>
       </c>
-      <c r="G23" s="296"/>
-      <c r="H23" s="296"/>
-      <c r="I23" s="296"/>
-      <c r="J23" s="296"/>
-      <c r="K23" s="296"/>
-      <c r="L23" s="297" t="s">
+      <c r="G23" s="295"/>
+      <c r="H23" s="295"/>
+      <c r="I23" s="295"/>
+      <c r="J23" s="295"/>
+      <c r="K23" s="295"/>
+      <c r="L23" s="296" t="s">
         <v>127</v>
       </c>
-      <c r="M23" s="297"/>
-      <c r="N23" s="297"/>
-      <c r="O23" s="297"/>
-      <c r="P23" s="297"/>
-      <c r="Q23" s="297"/>
-      <c r="R23" s="297"/>
-      <c r="S23" s="297"/>
-      <c r="T23" s="297"/>
-      <c r="U23" s="297"/>
-      <c r="V23" s="297"/>
-      <c r="W23" s="297"/>
-      <c r="X23" s="297"/>
-      <c r="Y23" s="297"/>
-      <c r="Z23" s="297"/>
-      <c r="AA23" s="297"/>
-      <c r="AB23" s="297"/>
-      <c r="AC23" s="297"/>
+      <c r="M23" s="296"/>
+      <c r="N23" s="296"/>
+      <c r="O23" s="296"/>
+      <c r="P23" s="296"/>
+      <c r="Q23" s="296"/>
+      <c r="R23" s="296"/>
+      <c r="S23" s="296"/>
+      <c r="T23" s="296"/>
+      <c r="U23" s="296"/>
+      <c r="V23" s="296"/>
+      <c r="W23" s="296"/>
+      <c r="X23" s="296"/>
+      <c r="Y23" s="296"/>
+      <c r="Z23" s="296"/>
+      <c r="AA23" s="296"/>
+      <c r="AB23" s="296"/>
+      <c r="AC23" s="296"/>
     </row>
     <row r="24" spans="2:29" s="70" customFormat="1" ht="20.000000" customHeight="1">
       <c r="B24" s="71"/>
       <c r="C24" s="71"/>
       <c r="D24" s="71"/>
       <c r="E24" s="71"/>
-      <c r="F24" s="296" t="s">
+      <c r="F24" s="295" t="s">
         <v>210</v>
       </c>
-      <c r="G24" s="296"/>
-      <c r="H24" s="296"/>
-      <c r="I24" s="296"/>
-      <c r="J24" s="296"/>
-      <c r="K24" s="296"/>
-      <c r="L24" s="297" t="s">
+      <c r="G24" s="295"/>
+      <c r="H24" s="295"/>
+      <c r="I24" s="295"/>
+      <c r="J24" s="295"/>
+      <c r="K24" s="295"/>
+      <c r="L24" s="296" t="s">
         <v>129</v>
       </c>
-      <c r="M24" s="297"/>
-      <c r="N24" s="297"/>
-      <c r="O24" s="297"/>
-      <c r="P24" s="297"/>
-      <c r="Q24" s="297"/>
-      <c r="R24" s="297"/>
-      <c r="S24" s="297"/>
-      <c r="T24" s="297"/>
-      <c r="U24" s="297"/>
-      <c r="V24" s="297"/>
-      <c r="W24" s="297"/>
-      <c r="X24" s="297"/>
-      <c r="Y24" s="297"/>
-      <c r="Z24" s="297"/>
-      <c r="AA24" s="297"/>
-      <c r="AB24" s="297"/>
-      <c r="AC24" s="297"/>
+      <c r="M24" s="296"/>
+      <c r="N24" s="296"/>
+      <c r="O24" s="296"/>
+      <c r="P24" s="296"/>
+      <c r="Q24" s="296"/>
+      <c r="R24" s="296"/>
+      <c r="S24" s="296"/>
+      <c r="T24" s="296"/>
+      <c r="U24" s="296"/>
+      <c r="V24" s="296"/>
+      <c r="W24" s="296"/>
+      <c r="X24" s="296"/>
+      <c r="Y24" s="296"/>
+      <c r="Z24" s="296"/>
+      <c r="AA24" s="296"/>
+      <c r="AB24" s="296"/>
+      <c r="AC24" s="296"/>
     </row>
     <row r="25" spans="2:29" s="70" customFormat="1" ht="20.000000" customHeight="1">
       <c r="B25" s="71"/>
       <c r="C25" s="71"/>
       <c r="D25" s="71"/>
       <c r="E25" s="71"/>
-      <c r="F25" s="296" t="s">
+      <c r="F25" s="295" t="s">
         <v>211</v>
       </c>
-      <c r="G25" s="296"/>
-      <c r="H25" s="296"/>
-      <c r="I25" s="296"/>
-      <c r="J25" s="296"/>
-      <c r="K25" s="296"/>
-      <c r="L25" s="297"/>
-      <c r="M25" s="297"/>
-      <c r="N25" s="297"/>
-      <c r="O25" s="297"/>
-      <c r="P25" s="297"/>
-      <c r="Q25" s="297"/>
-      <c r="R25" s="297"/>
-      <c r="S25" s="297"/>
-      <c r="T25" s="297"/>
-      <c r="U25" s="297"/>
-      <c r="V25" s="297"/>
-      <c r="W25" s="297"/>
-      <c r="X25" s="297"/>
-      <c r="Y25" s="297"/>
-      <c r="Z25" s="297"/>
-      <c r="AA25" s="297"/>
-      <c r="AB25" s="297"/>
-      <c r="AC25" s="297"/>
+      <c r="G25" s="295"/>
+      <c r="H25" s="295"/>
+      <c r="I25" s="295"/>
+      <c r="J25" s="295"/>
+      <c r="K25" s="295"/>
+      <c r="L25" s="296"/>
+      <c r="M25" s="296"/>
+      <c r="N25" s="296"/>
+      <c r="O25" s="296"/>
+      <c r="P25" s="296"/>
+      <c r="Q25" s="296"/>
+      <c r="R25" s="296"/>
+      <c r="S25" s="296"/>
+      <c r="T25" s="296"/>
+      <c r="U25" s="296"/>
+      <c r="V25" s="296"/>
+      <c r="W25" s="296"/>
+      <c r="X25" s="296"/>
+      <c r="Y25" s="296"/>
+      <c r="Z25" s="296"/>
+      <c r="AA25" s="296"/>
+      <c r="AB25" s="296"/>
+      <c r="AC25" s="296"/>
     </row>
     <row r="26" spans="2:29" s="70" customFormat="1" ht="10.000000" customHeight="1">
       <c r="B26" s="71"/>
@@ -19942,100 +19822,100 @@
       <c r="AC26" s="73"/>
     </row>
     <row r="27" spans="2:29" s="70" customFormat="1" ht="20.000000" customHeight="1">
-      <c r="B27" s="296" t="s">
+      <c r="B27" s="295" t="s">
         <v>232</v>
       </c>
-      <c r="C27" s="296"/>
-      <c r="D27" s="296"/>
-      <c r="E27" s="296"/>
-      <c r="F27" s="296"/>
-      <c r="G27" s="296"/>
-      <c r="H27" s="296"/>
-      <c r="I27" s="296"/>
-      <c r="J27" s="296"/>
-      <c r="K27" s="296"/>
-      <c r="L27" s="296"/>
-      <c r="M27" s="296"/>
-      <c r="N27" s="296"/>
-      <c r="O27" s="296"/>
-      <c r="P27" s="296"/>
-      <c r="Q27" s="296"/>
-      <c r="R27" s="296"/>
-      <c r="S27" s="296"/>
-      <c r="T27" s="296"/>
-      <c r="U27" s="296"/>
-      <c r="V27" s="296"/>
-      <c r="W27" s="296"/>
-      <c r="X27" s="296"/>
-      <c r="Y27" s="296"/>
-      <c r="Z27" s="296"/>
-      <c r="AA27" s="296"/>
-      <c r="AB27" s="296"/>
-      <c r="AC27" s="296"/>
+      <c r="C27" s="295"/>
+      <c r="D27" s="295"/>
+      <c r="E27" s="295"/>
+      <c r="F27" s="295"/>
+      <c r="G27" s="295"/>
+      <c r="H27" s="295"/>
+      <c r="I27" s="295"/>
+      <c r="J27" s="295"/>
+      <c r="K27" s="295"/>
+      <c r="L27" s="295"/>
+      <c r="M27" s="295"/>
+      <c r="N27" s="295"/>
+      <c r="O27" s="295"/>
+      <c r="P27" s="295"/>
+      <c r="Q27" s="295"/>
+      <c r="R27" s="295"/>
+      <c r="S27" s="295"/>
+      <c r="T27" s="295"/>
+      <c r="U27" s="295"/>
+      <c r="V27" s="295"/>
+      <c r="W27" s="295"/>
+      <c r="X27" s="295"/>
+      <c r="Y27" s="295"/>
+      <c r="Z27" s="295"/>
+      <c r="AA27" s="295"/>
+      <c r="AB27" s="295"/>
+      <c r="AC27" s="295"/>
     </row>
     <row r="28" spans="2:29" s="70" customFormat="1" ht="20.000000" customHeight="1">
       <c r="B28" s="71"/>
       <c r="C28" s="71"/>
       <c r="D28" s="71"/>
       <c r="E28" s="71"/>
-      <c r="F28" s="296" t="s">
+      <c r="F28" s="295" t="s">
         <v>195</v>
       </c>
-      <c r="G28" s="296"/>
-      <c r="H28" s="296"/>
-      <c r="I28" s="296"/>
-      <c r="J28" s="296"/>
-      <c r="K28" s="296"/>
-      <c r="L28" s="296"/>
-      <c r="M28" s="296"/>
-      <c r="N28" s="296"/>
-      <c r="O28" s="296"/>
-      <c r="P28" s="296"/>
-      <c r="Q28" s="296"/>
-      <c r="R28" s="296"/>
-      <c r="S28" s="296"/>
-      <c r="T28" s="296"/>
-      <c r="U28" s="296"/>
-      <c r="V28" s="296"/>
-      <c r="W28" s="296"/>
-      <c r="X28" s="296"/>
-      <c r="Y28" s="296"/>
-      <c r="Z28" s="296"/>
-      <c r="AA28" s="296"/>
-      <c r="AB28" s="296"/>
-      <c r="AC28" s="296"/>
+      <c r="G28" s="295"/>
+      <c r="H28" s="295"/>
+      <c r="I28" s="295"/>
+      <c r="J28" s="295"/>
+      <c r="K28" s="295"/>
+      <c r="L28" s="295"/>
+      <c r="M28" s="295"/>
+      <c r="N28" s="295"/>
+      <c r="O28" s="295"/>
+      <c r="P28" s="295"/>
+      <c r="Q28" s="295"/>
+      <c r="R28" s="295"/>
+      <c r="S28" s="295"/>
+      <c r="T28" s="295"/>
+      <c r="U28" s="295"/>
+      <c r="V28" s="295"/>
+      <c r="W28" s="295"/>
+      <c r="X28" s="295"/>
+      <c r="Y28" s="295"/>
+      <c r="Z28" s="295"/>
+      <c r="AA28" s="295"/>
+      <c r="AB28" s="295"/>
+      <c r="AC28" s="295"/>
     </row>
     <row r="29" spans="2:29" s="70" customFormat="1" ht="20.000000" customHeight="1">
       <c r="B29" s="71"/>
       <c r="C29" s="71"/>
       <c r="D29" s="71"/>
       <c r="E29" s="71"/>
-      <c r="F29" s="296" t="s">
+      <c r="F29" s="295" t="s">
         <v>190</v>
       </c>
-      <c r="G29" s="296"/>
-      <c r="H29" s="296"/>
-      <c r="I29" s="296"/>
-      <c r="J29" s="296"/>
-      <c r="K29" s="296"/>
-      <c r="L29" s="296"/>
-      <c r="M29" s="296"/>
-      <c r="N29" s="296"/>
-      <c r="O29" s="296"/>
-      <c r="P29" s="296"/>
-      <c r="Q29" s="296"/>
-      <c r="R29" s="296"/>
-      <c r="S29" s="296"/>
-      <c r="T29" s="296"/>
-      <c r="U29" s="296"/>
-      <c r="V29" s="296"/>
-      <c r="W29" s="296"/>
-      <c r="X29" s="296"/>
-      <c r="Y29" s="296"/>
-      <c r="Z29" s="296"/>
-      <c r="AA29" s="296"/>
-      <c r="AB29" s="296"/>
-      <c r="AC29" s="296"/>
+      <c r="G29" s="295"/>
+      <c r="H29" s="295"/>
+      <c r="I29" s="295"/>
+      <c r="J29" s="295"/>
+      <c r="K29" s="295"/>
+      <c r="L29" s="295"/>
+      <c r="M29" s="295"/>
+      <c r="N29" s="295"/>
+      <c r="O29" s="295"/>
+      <c r="P29" s="295"/>
+      <c r="Q29" s="295"/>
+      <c r="R29" s="295"/>
+      <c r="S29" s="295"/>
+      <c r="T29" s="295"/>
+      <c r="U29" s="295"/>
+      <c r="V29" s="295"/>
+      <c r="W29" s="295"/>
+      <c r="X29" s="295"/>
+      <c r="Y29" s="295"/>
+      <c r="Z29" s="295"/>
+      <c r="AA29" s="295"/>
+      <c r="AB29" s="295"/>
+      <c r="AC29" s="295"/>
     </row>
     <row r="30" spans="2:29" s="70" customFormat="1" ht="10.000000" customHeight="1">
       <c r="B30" s="71"/>
@@ -20068,39 +19948,39 @@
       <c r="AC30" s="73"/>
     </row>
     <row r="31" spans="2:29" s="70" customFormat="1" ht="20.000000" customHeight="1">
-      <c r="B31" s="302" t="s">
+      <c r="B31" s="301" t="s">
         <v>234</v>
       </c>
-      <c r="C31" s="302"/>
-      <c r="D31" s="302"/>
-      <c r="E31" s="302"/>
-      <c r="F31" s="302"/>
-      <c r="G31" s="302"/>
-      <c r="H31" s="302"/>
-      <c r="I31" s="302"/>
-      <c r="J31" s="302"/>
-      <c r="K31" s="302"/>
-      <c r="L31" s="302" t="str">
+      <c r="C31" s="301"/>
+      <c r="D31" s="301"/>
+      <c r="E31" s="301"/>
+      <c r="F31" s="301"/>
+      <c r="G31" s="301"/>
+      <c r="H31" s="301"/>
+      <c r="I31" s="301"/>
+      <c r="J31" s="301"/>
+      <c r="K31" s="301"/>
+      <c r="L31" s="301" t="str">
         <f>대가산출!D3</f>
         <v>일금이백오십만원정 (₩2,500,000) - VAT별도</v>
       </c>
-      <c r="M31" s="302"/>
-      <c r="N31" s="302"/>
-      <c r="O31" s="302"/>
-      <c r="P31" s="302"/>
-      <c r="Q31" s="302"/>
-      <c r="R31" s="302"/>
-      <c r="S31" s="302"/>
-      <c r="T31" s="302"/>
-      <c r="U31" s="302"/>
-      <c r="V31" s="302"/>
-      <c r="W31" s="302"/>
-      <c r="X31" s="302"/>
-      <c r="Y31" s="302"/>
-      <c r="Z31" s="302"/>
-      <c r="AA31" s="302"/>
-      <c r="AB31" s="302"/>
-      <c r="AC31" s="302"/>
+      <c r="M31" s="301"/>
+      <c r="N31" s="301"/>
+      <c r="O31" s="301"/>
+      <c r="P31" s="301"/>
+      <c r="Q31" s="301"/>
+      <c r="R31" s="301"/>
+      <c r="S31" s="301"/>
+      <c r="T31" s="301"/>
+      <c r="U31" s="301"/>
+      <c r="V31" s="301"/>
+      <c r="W31" s="301"/>
+      <c r="X31" s="301"/>
+      <c r="Y31" s="301"/>
+      <c r="Z31" s="301"/>
+      <c r="AA31" s="301"/>
+      <c r="AB31" s="301"/>
+      <c r="AC31" s="301"/>
     </row>
     <row r="32" spans="2:29" s="70" customFormat="1" ht="10.000000" customHeight="1">
       <c r="B32" s="71"/>
@@ -20133,18 +20013,18 @@
       <c r="AC32" s="73"/>
     </row>
     <row r="33" spans="1:29" s="70" customFormat="1" ht="20.000000" customHeight="1">
-      <c r="B33" s="296" t="s">
+      <c r="B33" s="295" t="s">
         <v>233</v>
       </c>
-      <c r="C33" s="296"/>
-      <c r="D33" s="296"/>
-      <c r="E33" s="296"/>
-      <c r="F33" s="296"/>
-      <c r="G33" s="296"/>
-      <c r="H33" s="296"/>
-      <c r="I33" s="296"/>
-      <c r="J33" s="296"/>
-      <c r="K33" s="296"/>
+      <c r="C33" s="295"/>
+      <c r="D33" s="295"/>
+      <c r="E33" s="295"/>
+      <c r="F33" s="295"/>
+      <c r="G33" s="295"/>
+      <c r="H33" s="295"/>
+      <c r="I33" s="295"/>
+      <c r="J33" s="295"/>
+      <c r="K33" s="295"/>
       <c r="L33" s="71"/>
       <c r="M33" s="71"/>
       <c r="N33" s="71"/>
@@ -20227,36 +20107,36 @@
       <c r="AC35" s="76"/>
     </row>
     <row r="36" spans="1:29" s="70" customFormat="1" ht="19.500000" customHeight="1">
-      <c r="B36" s="296" t="s">
+      <c r="B36" s="295" t="s">
         <v>203</v>
       </c>
-      <c r="C36" s="296"/>
-      <c r="D36" s="296"/>
-      <c r="E36" s="296"/>
-      <c r="F36" s="296"/>
-      <c r="G36" s="296"/>
-      <c r="H36" s="296"/>
-      <c r="I36" s="296"/>
-      <c r="J36" s="296"/>
-      <c r="K36" s="296"/>
-      <c r="L36" s="296"/>
-      <c r="M36" s="296"/>
-      <c r="N36" s="296"/>
-      <c r="O36" s="296"/>
-      <c r="P36" s="296"/>
-      <c r="Q36" s="296"/>
-      <c r="R36" s="296"/>
-      <c r="S36" s="296"/>
-      <c r="T36" s="296"/>
-      <c r="U36" s="296"/>
-      <c r="V36" s="296"/>
-      <c r="W36" s="296"/>
-      <c r="X36" s="296"/>
-      <c r="Y36" s="296"/>
-      <c r="Z36" s="296"/>
-      <c r="AA36" s="296"/>
-      <c r="AB36" s="296"/>
-      <c r="AC36" s="296"/>
+      <c r="C36" s="295"/>
+      <c r="D36" s="295"/>
+      <c r="E36" s="295"/>
+      <c r="F36" s="295"/>
+      <c r="G36" s="295"/>
+      <c r="H36" s="295"/>
+      <c r="I36" s="295"/>
+      <c r="J36" s="295"/>
+      <c r="K36" s="295"/>
+      <c r="L36" s="295"/>
+      <c r="M36" s="295"/>
+      <c r="N36" s="295"/>
+      <c r="O36" s="295"/>
+      <c r="P36" s="295"/>
+      <c r="Q36" s="295"/>
+      <c r="R36" s="295"/>
+      <c r="S36" s="295"/>
+      <c r="T36" s="295"/>
+      <c r="U36" s="295"/>
+      <c r="V36" s="295"/>
+      <c r="W36" s="295"/>
+      <c r="X36" s="295"/>
+      <c r="Y36" s="295"/>
+      <c r="Z36" s="295"/>
+      <c r="AA36" s="295"/>
+      <c r="AB36" s="295"/>
+      <c r="AC36" s="295"/>
     </row>
     <row r="37" spans="1:29" s="70" customFormat="1" ht="19.500000" customHeight="1">
       <c r="B37" s="71"/>
@@ -20274,36 +20154,36 @@
       <c r="N37" s="71"/>
     </row>
     <row r="38" spans="1:29" s="70" customFormat="1" ht="46.500000" customHeight="1">
-      <c r="B38" s="301" t="s">
+      <c r="B38" s="300" t="s">
         <v>118</v>
       </c>
-      <c r="C38" s="301"/>
-      <c r="D38" s="301"/>
-      <c r="E38" s="301"/>
-      <c r="F38" s="301"/>
-      <c r="G38" s="301"/>
-      <c r="H38" s="301"/>
-      <c r="I38" s="301"/>
-      <c r="J38" s="301"/>
-      <c r="K38" s="301"/>
-      <c r="L38" s="301"/>
-      <c r="M38" s="301"/>
-      <c r="N38" s="301"/>
-      <c r="O38" s="301"/>
-      <c r="P38" s="301"/>
-      <c r="Q38" s="301"/>
-      <c r="R38" s="301"/>
-      <c r="S38" s="301"/>
-      <c r="T38" s="301"/>
-      <c r="U38" s="301"/>
-      <c r="V38" s="301"/>
-      <c r="W38" s="301"/>
-      <c r="X38" s="301"/>
-      <c r="Y38" s="301"/>
-      <c r="Z38" s="301"/>
-      <c r="AA38" s="301"/>
-      <c r="AB38" s="301"/>
-      <c r="AC38" s="301"/>
+      <c r="C38" s="300"/>
+      <c r="D38" s="300"/>
+      <c r="E38" s="300"/>
+      <c r="F38" s="300"/>
+      <c r="G38" s="300"/>
+      <c r="H38" s="300"/>
+      <c r="I38" s="300"/>
+      <c r="J38" s="300"/>
+      <c r="K38" s="300"/>
+      <c r="L38" s="300"/>
+      <c r="M38" s="300"/>
+      <c r="N38" s="300"/>
+      <c r="O38" s="300"/>
+      <c r="P38" s="300"/>
+      <c r="Q38" s="300"/>
+      <c r="R38" s="300"/>
+      <c r="S38" s="300"/>
+      <c r="T38" s="300"/>
+      <c r="U38" s="300"/>
+      <c r="V38" s="300"/>
+      <c r="W38" s="300"/>
+      <c r="X38" s="300"/>
+      <c r="Y38" s="300"/>
+      <c r="Z38" s="300"/>
+      <c r="AA38" s="300"/>
+      <c r="AB38" s="300"/>
+      <c r="AC38" s="300"/>
     </row>
     <row r="39" spans="1:29">
       <c r="A39" s="64"/>
@@ -37406,10 +37286,10 @@
     <mergeCell ref="B20:AC20"/>
     <mergeCell ref="F21:K21"/>
     <mergeCell ref="L21:AC21"/>
+    <mergeCell ref="F22:K22"/>
+    <mergeCell ref="L22:AC22"/>
     <mergeCell ref="F23:K23"/>
     <mergeCell ref="L23:AC23"/>
-    <mergeCell ref="F22:K22"/>
-    <mergeCell ref="L22:AC22"/>
     <mergeCell ref="F24:K24"/>
     <mergeCell ref="L24:AC24"/>
     <mergeCell ref="F25:K25"/>
@@ -37449,16 +37329,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:9" s="1" customFormat="1" ht="39.000000" customHeight="1">
-      <c r="B1" s="347" t="s">
+      <c r="B1" s="346" t="s">
         <v>113</v>
       </c>
-      <c r="C1" s="347"/>
-      <c r="D1" s="347"/>
-      <c r="E1" s="347"/>
-      <c r="F1" s="347"/>
-      <c r="G1" s="347"/>
-      <c r="H1" s="347"/>
-      <c r="I1" s="347"/>
+      <c r="C1" s="346"/>
+      <c r="D1" s="346"/>
+      <c r="E1" s="346"/>
+      <c r="F1" s="346"/>
+      <c r="G1" s="346"/>
+      <c r="H1" s="346"/>
+      <c r="I1" s="346"/>
     </row>
     <row r="2" spans="2:9" s="1" customFormat="1" ht="18.000000" customHeight="1">
       <c r="B2" s="82"/>
@@ -37467,71 +37347,71 @@
       <c r="E2" s="82"/>
       <c r="F2" s="82"/>
       <c r="G2" s="82"/>
-      <c r="H2" s="348"/>
-      <c r="I2" s="348"/>
+      <c r="H2" s="347"/>
+      <c r="I2" s="347"/>
     </row>
     <row r="3" spans="2:9" s="83" customFormat="1" ht="34.500000" customHeight="1">
-      <c r="B3" s="349" t="s">
+      <c r="B3" s="348" t="s">
         <v>131</v>
       </c>
-      <c r="C3" s="350"/>
-      <c r="D3" s="351" t="str">
+      <c r="C3" s="349"/>
+      <c r="D3" s="350" t="str">
         <f>"일금"&amp;NUMBERSTRING(H30,1)&amp;"원정 ("&amp;DOLLAR(H30,0)&amp;") - VAT별도"</f>
         <v>일금이백오십만원정 (₩2,500,000) - VAT별도</v>
       </c>
-      <c r="E3" s="352"/>
-      <c r="F3" s="352"/>
-      <c r="G3" s="352"/>
-      <c r="H3" s="352"/>
-      <c r="I3" s="353"/>
+      <c r="E3" s="351"/>
+      <c r="F3" s="351"/>
+      <c r="G3" s="351"/>
+      <c r="H3" s="351"/>
+      <c r="I3" s="352"/>
     </row>
     <row r="4" spans="2:9" s="83" customFormat="1" ht="38.250000" hidden="1" customHeight="1">
-      <c r="B4" s="354" t="s">
+      <c r="B4" s="353" t="s">
         <v>132</v>
       </c>
-      <c r="C4" s="355"/>
-      <c r="D4" s="356" t="str">
+      <c r="C4" s="354"/>
+      <c r="D4" s="355" t="str">
         <f>"일금 "&amp;NUMBERSTRING(H30,1)&amp;"원정"&amp;TEXT(H30,"(￦ #,##0)")&amp;" "</f>
         <v xml:space="preserve">일금 이백오십만원정(₩ 2,500,000) </v>
       </c>
-      <c r="E4" s="357"/>
-      <c r="F4" s="357"/>
-      <c r="G4" s="357"/>
-      <c r="H4" s="357"/>
-      <c r="I4" s="358"/>
+      <c r="E4" s="356"/>
+      <c r="F4" s="356"/>
+      <c r="G4" s="356"/>
+      <c r="H4" s="356"/>
+      <c r="I4" s="357"/>
     </row>
     <row r="5" spans="2:9" s="83" customFormat="1" ht="38.250000" hidden="1" customHeight="1">
-      <c r="B5" s="326" t="s">
+      <c r="B5" s="325" t="s">
         <v>133</v>
       </c>
-      <c r="C5" s="327"/>
-      <c r="D5" s="328" t="e">
+      <c r="C5" s="326"/>
+      <c r="D5" s="327">
         <f>"일금 "&amp;NUMBERSTRING(H31,1)&amp;"원정"&amp;TEXT(H31,"(￦ #,##0)")&amp;" "</f>
-        <v>일금 #VALUE!원정</v>
+        <v/>
       </c>
-      <c r="E5" s="329"/>
-      <c r="F5" s="329"/>
-      <c r="G5" s="329"/>
-      <c r="H5" s="329"/>
-      <c r="I5" s="330"/>
+      <c r="E5" s="328"/>
+      <c r="F5" s="328"/>
+      <c r="G5" s="328"/>
+      <c r="H5" s="328"/>
+      <c r="I5" s="329"/>
     </row>
     <row r="6" spans="2:9" s="83" customFormat="1" ht="31.500000" customHeight="1">
-      <c r="B6" s="331" t="s">
+      <c r="B6" s="330" t="s">
         <v>134</v>
       </c>
-      <c r="C6" s="332"/>
-      <c r="D6" s="332"/>
-      <c r="E6" s="332"/>
-      <c r="F6" s="332"/>
-      <c r="G6" s="332"/>
-      <c r="H6" s="332"/>
-      <c r="I6" s="333"/>
+      <c r="C6" s="331"/>
+      <c r="D6" s="331"/>
+      <c r="E6" s="331"/>
+      <c r="F6" s="331"/>
+      <c r="G6" s="331"/>
+      <c r="H6" s="331"/>
+      <c r="I6" s="332"/>
     </row>
     <row r="7" spans="2:9" s="84" customFormat="1" ht="30.000000" customHeight="1">
-      <c r="B7" s="334" t="s">
+      <c r="B7" s="333" t="s">
         <v>135</v>
       </c>
-      <c r="C7" s="335"/>
+      <c r="C7" s="334"/>
       <c r="D7" s="81" t="s">
         <v>136</v>
       </c>
@@ -37552,10 +37432,10 @@
       </c>
     </row>
     <row r="8" spans="2:9" s="84" customFormat="1" ht="28.000000" customHeight="1">
-      <c r="B8" s="336" t="s">
+      <c r="B8" s="335" t="s">
         <v>204</v>
       </c>
-      <c r="C8" s="337"/>
+      <c r="C8" s="336"/>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
       <c r="F8" s="10"/>
@@ -37741,10 +37621,10 @@
       <c r="I16" s="89"/>
     </row>
     <row r="17" spans="2:13" s="84" customFormat="1" ht="28.000000" customHeight="1">
-      <c r="B17" s="338" t="s">
+      <c r="B17" s="337" t="s">
         <v>147</v>
       </c>
-      <c r="C17" s="339"/>
+      <c r="C17" s="338"/>
       <c r="D17" s="96"/>
       <c r="E17" s="98" t="s">
         <v>148</v>
@@ -37762,10 +37642,10 @@
       </c>
     </row>
     <row r="18" spans="2:13" s="84" customFormat="1" ht="28.000000" customHeight="1">
-      <c r="B18" s="338" t="s">
+      <c r="B18" s="337" t="s">
         <v>149</v>
       </c>
-      <c r="C18" s="339"/>
+      <c r="C18" s="338"/>
       <c r="D18" s="96"/>
       <c r="E18" s="98" t="s">
         <v>148</v>
@@ -37783,10 +37663,10 @@
       </c>
     </row>
     <row r="19" spans="2:13" s="84" customFormat="1" ht="28.000000" customHeight="1">
-      <c r="B19" s="338" t="s">
+      <c r="B19" s="337" t="s">
         <v>150</v>
       </c>
-      <c r="C19" s="339"/>
+      <c r="C19" s="338"/>
       <c r="D19" s="100"/>
       <c r="E19" s="102"/>
       <c r="F19" s="102"/>
@@ -37916,10 +37796,10 @@
       <c r="I25" s="89"/>
     </row>
     <row r="26" spans="2:13" s="84" customFormat="1" ht="28.000000" customHeight="1">
-      <c r="B26" s="340" t="s">
+      <c r="B26" s="339" t="s">
         <v>207</v>
       </c>
-      <c r="C26" s="341"/>
+      <c r="C26" s="340"/>
       <c r="D26" s="96"/>
       <c r="E26" s="98"/>
       <c r="F26" s="98"/>
@@ -37928,10 +37808,10 @@
       <c r="I26" s="127"/>
     </row>
     <row r="27" spans="2:13" s="84" customFormat="1" ht="28.000000" customHeight="1">
-      <c r="B27" s="340" t="s">
+      <c r="B27" s="339" t="s">
         <v>205</v>
       </c>
-      <c r="C27" s="341"/>
+      <c r="C27" s="340"/>
       <c r="D27" s="149"/>
       <c r="E27" s="98"/>
       <c r="F27" s="150"/>
@@ -37940,15 +37820,15 @@
       <c r="I27" s="127"/>
     </row>
     <row r="28" spans="2:13" s="84" customFormat="1" ht="28.000000" customHeight="1">
-      <c r="B28" s="342" t="s">
+      <c r="B28" s="341" t="s">
         <v>206</v>
       </c>
-      <c r="C28" s="343"/>
-      <c r="D28" s="344" t="s">
+      <c r="C28" s="342"/>
+      <c r="D28" s="343" t="s">
         <v>221</v>
       </c>
-      <c r="E28" s="345"/>
-      <c r="F28" s="346"/>
+      <c r="E28" s="344"/>
+      <c r="F28" s="345"/>
       <c r="G28" s="143"/>
       <c r="H28" s="128">
         <f>(SUM(H8,H17,H18,H19,H26,H27))</f>
@@ -37957,12 +37837,12 @@
       <c r="I28" s="129"/>
     </row>
     <row r="29" spans="2:13" s="84" customFormat="1" ht="18.000000" customHeight="1">
-      <c r="B29" s="317" t="s">
+      <c r="B29" s="316" t="s">
         <v>159</v>
       </c>
-      <c r="C29" s="318"/>
-      <c r="D29" s="319"/>
-      <c r="E29" s="320"/>
+      <c r="C29" s="317"/>
+      <c r="D29" s="318"/>
+      <c r="E29" s="319"/>
       <c r="F29" s="143"/>
       <c r="G29" s="143"/>
       <c r="H29" s="128">
@@ -37971,12 +37851,12 @@
       <c r="I29" s="130"/>
     </row>
     <row r="30" spans="2:13" s="84" customFormat="1" ht="18.000000" customHeight="1">
-      <c r="B30" s="313" t="s">
+      <c r="B30" s="312" t="s">
         <v>160</v>
       </c>
-      <c r="C30" s="314"/>
-      <c r="D30" s="315"/>
-      <c r="E30" s="316"/>
+      <c r="C30" s="313"/>
+      <c r="D30" s="314"/>
+      <c r="E30" s="315"/>
       <c r="F30" s="144"/>
       <c r="G30" s="144"/>
       <c r="H30" s="131">
@@ -37986,12 +37866,12 @@
       <c r="I30" s="132"/>
     </row>
     <row r="31" spans="2:13" s="84" customFormat="1" ht="18.000000" customHeight="1">
-      <c r="B31" s="317" t="s">
+      <c r="B31" s="316" t="s">
         <v>161</v>
       </c>
-      <c r="C31" s="318"/>
-      <c r="D31" s="319"/>
-      <c r="E31" s="320"/>
+      <c r="C31" s="317"/>
+      <c r="D31" s="318"/>
+      <c r="E31" s="319"/>
       <c r="F31" s="143"/>
       <c r="G31" s="143"/>
       <c r="H31" s="133" t="s">
@@ -38000,13 +37880,13 @@
       <c r="I31" s="130"/>
     </row>
     <row r="32" spans="2:13" s="84" customFormat="1" ht="28.000000" customHeight="1">
-      <c r="B32" s="321" t="s">
+      <c r="B32" s="320" t="s">
         <v>163</v>
       </c>
-      <c r="C32" s="322"/>
-      <c r="D32" s="323"/>
-      <c r="E32" s="324"/>
-      <c r="F32" s="325"/>
+      <c r="C32" s="321"/>
+      <c r="D32" s="322"/>
+      <c r="E32" s="323"/>
+      <c r="F32" s="324"/>
       <c r="G32" s="145"/>
       <c r="H32" s="134">
         <f>H30</f>
@@ -38017,69 +37897,69 @@
       </c>
     </row>
     <row r="33" spans="2:9" s="137" customFormat="1" ht="23.000000" customHeight="1">
-      <c r="B33" s="303"/>
-      <c r="C33" s="304"/>
-      <c r="D33" s="309" t="s">
+      <c r="B33" s="302"/>
+      <c r="C33" s="303"/>
+      <c r="D33" s="308" t="s">
         <v>15</v>
       </c>
-      <c r="E33" s="309"/>
-      <c r="F33" s="309"/>
-      <c r="G33" s="309"/>
-      <c r="H33" s="309"/>
+      <c r="E33" s="308"/>
+      <c r="F33" s="308"/>
+      <c r="G33" s="308"/>
+      <c r="H33" s="308"/>
       <c r="I33" s="136"/>
     </row>
     <row r="34" spans="2:9" s="137" customFormat="1" ht="23.000000" customHeight="1">
-      <c r="B34" s="305"/>
-      <c r="C34" s="306"/>
-      <c r="D34" s="310" t="s">
+      <c r="B34" s="304"/>
+      <c r="C34" s="305"/>
+      <c r="D34" s="309" t="s">
         <v>16</v>
       </c>
-      <c r="E34" s="310"/>
-      <c r="F34" s="310"/>
-      <c r="G34" s="310"/>
-      <c r="H34" s="310"/>
+      <c r="E34" s="309"/>
+      <c r="F34" s="309"/>
+      <c r="G34" s="309"/>
+      <c r="H34" s="309"/>
       <c r="I34" s="138" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="35" spans="2:9" s="137" customFormat="1" ht="23.000000" customHeight="1">
-      <c r="B35" s="305"/>
-      <c r="C35" s="306"/>
-      <c r="D35" s="311" t="s">
+      <c r="B35" s="304"/>
+      <c r="C35" s="305"/>
+      <c r="D35" s="310" t="s">
         <v>18</v>
       </c>
-      <c r="E35" s="311"/>
-      <c r="F35" s="311"/>
-      <c r="G35" s="311"/>
-      <c r="H35" s="311"/>
+      <c r="E35" s="310"/>
+      <c r="F35" s="310"/>
+      <c r="G35" s="310"/>
+      <c r="H35" s="310"/>
       <c r="I35" s="138" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="36" spans="2:9" s="137" customFormat="1" ht="23.000000" customHeight="1">
-      <c r="B36" s="305"/>
-      <c r="C36" s="306"/>
-      <c r="D36" s="310" t="s">
+      <c r="B36" s="304"/>
+      <c r="C36" s="305"/>
+      <c r="D36" s="309" t="s">
         <v>20</v>
       </c>
-      <c r="E36" s="310"/>
-      <c r="F36" s="310"/>
-      <c r="G36" s="310"/>
-      <c r="H36" s="310"/>
+      <c r="E36" s="309"/>
+      <c r="F36" s="309"/>
+      <c r="G36" s="309"/>
+      <c r="H36" s="309"/>
       <c r="I36" s="138" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="37" spans="2:9" s="137" customFormat="1" ht="23.000000" customHeight="1">
-      <c r="B37" s="307"/>
-      <c r="C37" s="308"/>
-      <c r="D37" s="312" t="s">
+      <c r="B37" s="306"/>
+      <c r="C37" s="307"/>
+      <c r="D37" s="311" t="s">
         <v>22</v>
       </c>
-      <c r="E37" s="312"/>
-      <c r="F37" s="312"/>
-      <c r="G37" s="312"/>
-      <c r="H37" s="312"/>
+      <c r="E37" s="311"/>
+      <c r="F37" s="311"/>
+      <c r="G37" s="311"/>
+      <c r="H37" s="311"/>
       <c r="I37" s="139" t="s">
         <v>23</v>
       </c>
@@ -38613,99 +38493,99 @@
       <c r="C6" s="18"/>
     </row>
     <row r="7" spans="2:21" ht="4.000000" customHeight="1">
-      <c r="B7" s="272" t="s">
+      <c r="B7" s="271" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="273"/>
-      <c r="D7" s="273"/>
-      <c r="E7" s="273"/>
-      <c r="F7" s="273"/>
-      <c r="G7" s="273"/>
-      <c r="H7" s="273"/>
-      <c r="I7" s="273"/>
-      <c r="J7" s="273"/>
-      <c r="K7" s="273"/>
-      <c r="L7" s="273"/>
-      <c r="M7" s="273"/>
-      <c r="N7" s="273"/>
-      <c r="O7" s="273"/>
-      <c r="P7" s="273"/>
-      <c r="Q7" s="273"/>
-      <c r="R7" s="273"/>
-      <c r="S7" s="273"/>
-      <c r="T7" s="273"/>
-      <c r="U7" s="273"/>
+      <c r="C7" s="272"/>
+      <c r="D7" s="272"/>
+      <c r="E7" s="272"/>
+      <c r="F7" s="272"/>
+      <c r="G7" s="272"/>
+      <c r="H7" s="272"/>
+      <c r="I7" s="272"/>
+      <c r="J7" s="272"/>
+      <c r="K7" s="272"/>
+      <c r="L7" s="272"/>
+      <c r="M7" s="272"/>
+      <c r="N7" s="272"/>
+      <c r="O7" s="272"/>
+      <c r="P7" s="272"/>
+      <c r="Q7" s="272"/>
+      <c r="R7" s="272"/>
+      <c r="S7" s="272"/>
+      <c r="T7" s="272"/>
+      <c r="U7" s="272"/>
     </row>
     <row r="8" spans="2:21" ht="66.000000" customHeight="1">
-      <c r="B8" s="274" t="s">
+      <c r="B8" s="273" t="s">
         <v>165</v>
       </c>
-      <c r="C8" s="274"/>
-      <c r="D8" s="274"/>
-      <c r="E8" s="274"/>
-      <c r="F8" s="274"/>
-      <c r="G8" s="274"/>
-      <c r="H8" s="274"/>
-      <c r="I8" s="274"/>
-      <c r="J8" s="274"/>
-      <c r="K8" s="274"/>
-      <c r="L8" s="274"/>
-      <c r="M8" s="274"/>
-      <c r="N8" s="274"/>
-      <c r="O8" s="274"/>
-      <c r="P8" s="274"/>
-      <c r="Q8" s="274"/>
-      <c r="R8" s="274"/>
-      <c r="S8" s="274"/>
-      <c r="T8" s="274"/>
-      <c r="U8" s="274"/>
+      <c r="C8" s="273"/>
+      <c r="D8" s="273"/>
+      <c r="E8" s="273"/>
+      <c r="F8" s="273"/>
+      <c r="G8" s="273"/>
+      <c r="H8" s="273"/>
+      <c r="I8" s="273"/>
+      <c r="J8" s="273"/>
+      <c r="K8" s="273"/>
+      <c r="L8" s="273"/>
+      <c r="M8" s="273"/>
+      <c r="N8" s="273"/>
+      <c r="O8" s="273"/>
+      <c r="P8" s="273"/>
+      <c r="Q8" s="273"/>
+      <c r="R8" s="273"/>
+      <c r="S8" s="273"/>
+      <c r="T8" s="273"/>
+      <c r="U8" s="273"/>
     </row>
     <row r="9" spans="2:21" ht="44.000000" customHeight="1">
-      <c r="B9" s="275" t="str">
+      <c r="B9" s="274" t="str">
         <f>갑지!L21</f>
         <v>효성뉴서울5차아파트</v>
       </c>
-      <c r="C9" s="275"/>
-      <c r="D9" s="275"/>
-      <c r="E9" s="275"/>
-      <c r="F9" s="275"/>
-      <c r="G9" s="275"/>
-      <c r="H9" s="275"/>
-      <c r="I9" s="275"/>
-      <c r="J9" s="275"/>
-      <c r="K9" s="275"/>
-      <c r="L9" s="275"/>
-      <c r="M9" s="275"/>
-      <c r="N9" s="275"/>
-      <c r="O9" s="275"/>
-      <c r="P9" s="275"/>
-      <c r="Q9" s="275"/>
-      <c r="R9" s="275"/>
-      <c r="S9" s="275"/>
-      <c r="T9" s="275"/>
-      <c r="U9" s="275"/>
+      <c r="C9" s="274"/>
+      <c r="D9" s="274"/>
+      <c r="E9" s="274"/>
+      <c r="F9" s="274"/>
+      <c r="G9" s="274"/>
+      <c r="H9" s="274"/>
+      <c r="I9" s="274"/>
+      <c r="J9" s="274"/>
+      <c r="K9" s="274"/>
+      <c r="L9" s="274"/>
+      <c r="M9" s="274"/>
+      <c r="N9" s="274"/>
+      <c r="O9" s="274"/>
+      <c r="P9" s="274"/>
+      <c r="Q9" s="274"/>
+      <c r="R9" s="274"/>
+      <c r="S9" s="274"/>
+      <c r="T9" s="274"/>
+      <c r="U9" s="274"/>
     </row>
     <row r="10" spans="2:21" ht="4.000000" customHeight="1">
-      <c r="B10" s="276"/>
-      <c r="C10" s="277"/>
-      <c r="D10" s="277"/>
-      <c r="E10" s="277"/>
-      <c r="F10" s="277"/>
-      <c r="G10" s="277"/>
-      <c r="H10" s="277"/>
-      <c r="I10" s="277"/>
-      <c r="J10" s="277"/>
-      <c r="K10" s="277"/>
-      <c r="L10" s="277"/>
-      <c r="M10" s="277"/>
-      <c r="N10" s="277"/>
-      <c r="O10" s="277"/>
-      <c r="P10" s="277"/>
-      <c r="Q10" s="277"/>
-      <c r="R10" s="277"/>
-      <c r="S10" s="277"/>
-      <c r="T10" s="277"/>
-      <c r="U10" s="277"/>
+      <c r="B10" s="275"/>
+      <c r="C10" s="276"/>
+      <c r="D10" s="276"/>
+      <c r="E10" s="276"/>
+      <c r="F10" s="276"/>
+      <c r="G10" s="276"/>
+      <c r="H10" s="276"/>
+      <c r="I10" s="276"/>
+      <c r="J10" s="276"/>
+      <c r="K10" s="276"/>
+      <c r="L10" s="276"/>
+      <c r="M10" s="276"/>
+      <c r="N10" s="276"/>
+      <c r="O10" s="276"/>
+      <c r="P10" s="276"/>
+      <c r="Q10" s="276"/>
+      <c r="R10" s="276"/>
+      <c r="S10" s="276"/>
+      <c r="T10" s="276"/>
+      <c r="U10" s="276"/>
     </row>
     <row r="11" spans="2:21" ht="40.000000" customHeight="1">
       <c r="B11" s="20"/>
@@ -38728,29 +38608,29 @@
       <c r="C15" s="20"/>
     </row>
     <row r="16" spans="2:21" ht="22.500000">
-      <c r="B16" s="278">
+      <c r="B16" s="277">
         <f>갑지!F7</f>
         <v>46072</v>
       </c>
-      <c r="C16" s="278"/>
-      <c r="D16" s="278"/>
-      <c r="E16" s="278"/>
-      <c r="F16" s="278"/>
-      <c r="G16" s="278"/>
-      <c r="H16" s="278"/>
-      <c r="I16" s="278"/>
-      <c r="J16" s="278"/>
-      <c r="K16" s="278"/>
-      <c r="L16" s="278"/>
-      <c r="M16" s="278"/>
-      <c r="N16" s="278"/>
-      <c r="O16" s="278"/>
-      <c r="P16" s="278"/>
-      <c r="Q16" s="278"/>
-      <c r="R16" s="278"/>
-      <c r="S16" s="278"/>
-      <c r="T16" s="278"/>
-      <c r="U16" s="278"/>
+      <c r="C16" s="277"/>
+      <c r="D16" s="277"/>
+      <c r="E16" s="277"/>
+      <c r="F16" s="277"/>
+      <c r="G16" s="277"/>
+      <c r="H16" s="277"/>
+      <c r="I16" s="277"/>
+      <c r="J16" s="277"/>
+      <c r="K16" s="277"/>
+      <c r="L16" s="277"/>
+      <c r="M16" s="277"/>
+      <c r="N16" s="277"/>
+      <c r="O16" s="277"/>
+      <c r="P16" s="277"/>
+      <c r="Q16" s="277"/>
+      <c r="R16" s="277"/>
+      <c r="S16" s="277"/>
+      <c r="T16" s="277"/>
+      <c r="U16" s="277"/>
     </row>
     <row r="17" spans="2:21" ht="40.000000" customHeight="1">
       <c r="B17" s="20"/>
@@ -38773,45 +38653,45 @@
       <c r="C21" s="20"/>
     </row>
     <row r="22" spans="2:21" ht="4.000000" customHeight="1">
-      <c r="B22" s="283" t="s">
+      <c r="B22" s="282" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="283"/>
-      <c r="D22" s="283"/>
-      <c r="E22" s="283"/>
-      <c r="F22" s="283"/>
-      <c r="G22" s="283"/>
-      <c r="H22" s="283"/>
-      <c r="I22" s="283"/>
-      <c r="J22" s="283"/>
-      <c r="K22" s="283"/>
-      <c r="L22" s="283"/>
-      <c r="M22" s="283"/>
-      <c r="N22" s="283"/>
-      <c r="O22" s="283"/>
-      <c r="P22" s="283"/>
-      <c r="Q22" s="283"/>
-      <c r="R22" s="283"/>
-      <c r="S22" s="283"/>
-      <c r="T22" s="283"/>
-      <c r="U22" s="283"/>
+      <c r="C22" s="282"/>
+      <c r="D22" s="282"/>
+      <c r="E22" s="282"/>
+      <c r="F22" s="282"/>
+      <c r="G22" s="282"/>
+      <c r="H22" s="282"/>
+      <c r="I22" s="282"/>
+      <c r="J22" s="282"/>
+      <c r="K22" s="282"/>
+      <c r="L22" s="282"/>
+      <c r="M22" s="282"/>
+      <c r="N22" s="282"/>
+      <c r="O22" s="282"/>
+      <c r="P22" s="282"/>
+      <c r="Q22" s="282"/>
+      <c r="R22" s="282"/>
+      <c r="S22" s="282"/>
+      <c r="T22" s="282"/>
+      <c r="U22" s="282"/>
     </row>
     <row r="23" spans="2:21" ht="53.250000" customHeight="1">
       <c r="D23" s="79"/>
       <c r="E23" s="79"/>
-      <c r="I23" s="282" t="s">
+      <c r="I23" s="281" t="s">
         <v>25</v>
       </c>
-      <c r="J23" s="282"/>
-      <c r="K23" s="282"/>
-      <c r="L23" s="282"/>
-      <c r="M23" s="282"/>
-      <c r="N23" s="282"/>
-      <c r="O23" s="282"/>
-      <c r="P23" s="282"/>
-      <c r="Q23" s="282"/>
-      <c r="R23" s="282"/>
-      <c r="S23" s="282"/>
+      <c r="J23" s="281"/>
+      <c r="K23" s="281"/>
+      <c r="L23" s="281"/>
+      <c r="M23" s="281"/>
+      <c r="N23" s="281"/>
+      <c r="O23" s="281"/>
+      <c r="P23" s="281"/>
+      <c r="Q23" s="281"/>
+      <c r="R23" s="281"/>
+      <c r="S23" s="281"/>
       <c r="T23" s="80"/>
       <c r="U23" s="80"/>
     </row>
@@ -38890,349 +38770,349 @@
       <c r="U27" s="23"/>
     </row>
     <row r="28" spans="2:21" ht="43.500000" customHeight="1">
-      <c r="B28" s="279" t="s">
+      <c r="B28" s="278" t="s">
         <v>166</v>
       </c>
-      <c r="C28" s="280"/>
-      <c r="D28" s="280"/>
-      <c r="E28" s="280"/>
-      <c r="F28" s="280"/>
-      <c r="G28" s="280"/>
-      <c r="H28" s="280"/>
-      <c r="I28" s="280"/>
-      <c r="J28" s="280"/>
-      <c r="K28" s="280"/>
-      <c r="L28" s="280"/>
-      <c r="M28" s="280"/>
-      <c r="N28" s="280"/>
-      <c r="O28" s="280"/>
-      <c r="P28" s="280"/>
-      <c r="Q28" s="280"/>
-      <c r="R28" s="280"/>
-      <c r="S28" s="280"/>
-      <c r="T28" s="280"/>
-      <c r="U28" s="281"/>
+      <c r="C28" s="279"/>
+      <c r="D28" s="279"/>
+      <c r="E28" s="279"/>
+      <c r="F28" s="279"/>
+      <c r="G28" s="279"/>
+      <c r="H28" s="279"/>
+      <c r="I28" s="279"/>
+      <c r="J28" s="279"/>
+      <c r="K28" s="279"/>
+      <c r="L28" s="279"/>
+      <c r="M28" s="279"/>
+      <c r="N28" s="279"/>
+      <c r="O28" s="279"/>
+      <c r="P28" s="279"/>
+      <c r="Q28" s="279"/>
+      <c r="R28" s="279"/>
+      <c r="S28" s="279"/>
+      <c r="T28" s="279"/>
+      <c r="U28" s="280"/>
     </row>
     <row r="29" spans="2:21" ht="24.950000" customHeight="1">
-      <c r="B29" s="287" t="s">
+      <c r="B29" s="286" t="s">
         <v>27</v>
       </c>
-      <c r="C29" s="288"/>
-      <c r="D29" s="289" t="s">
+      <c r="C29" s="287"/>
+      <c r="D29" s="288" t="s">
         <v>28</v>
       </c>
-      <c r="E29" s="289"/>
-      <c r="F29" s="289"/>
-      <c r="G29" s="290" t="str">
+      <c r="E29" s="288"/>
+      <c r="F29" s="288"/>
+      <c r="G29" s="289" t="str">
         <f>B9</f>
         <v>효성뉴서울5차아파트</v>
       </c>
-      <c r="H29" s="290"/>
-      <c r="I29" s="290"/>
-      <c r="J29" s="290"/>
-      <c r="K29" s="290"/>
-      <c r="L29" s="290"/>
-      <c r="M29" s="290"/>
-      <c r="N29" s="290"/>
-      <c r="O29" s="290"/>
-      <c r="P29" s="290"/>
-      <c r="Q29" s="290"/>
-      <c r="R29" s="290"/>
-      <c r="S29" s="290"/>
-      <c r="T29" s="290"/>
-      <c r="U29" s="291"/>
+      <c r="H29" s="289"/>
+      <c r="I29" s="289"/>
+      <c r="J29" s="289"/>
+      <c r="K29" s="289"/>
+      <c r="L29" s="289"/>
+      <c r="M29" s="289"/>
+      <c r="N29" s="289"/>
+      <c r="O29" s="289"/>
+      <c r="P29" s="289"/>
+      <c r="Q29" s="289"/>
+      <c r="R29" s="289"/>
+      <c r="S29" s="289"/>
+      <c r="T29" s="289"/>
+      <c r="U29" s="290"/>
     </row>
     <row r="30" spans="2:21" ht="24.950000" customHeight="1">
-      <c r="B30" s="253"/>
-      <c r="C30" s="254"/>
-      <c r="D30" s="219" t="s">
+      <c r="B30" s="252"/>
+      <c r="C30" s="253"/>
+      <c r="D30" s="218" t="s">
         <v>29</v>
       </c>
-      <c r="E30" s="219"/>
-      <c r="F30" s="219"/>
-      <c r="G30" s="239" t="s">
+      <c r="E30" s="218"/>
+      <c r="F30" s="218"/>
+      <c r="G30" s="238" t="s">
         <v>198</v>
       </c>
-      <c r="H30" s="239"/>
-      <c r="I30" s="239"/>
-      <c r="J30" s="239"/>
-      <c r="K30" s="239"/>
-      <c r="L30" s="239"/>
-      <c r="M30" s="239"/>
-      <c r="N30" s="239"/>
-      <c r="O30" s="239"/>
-      <c r="P30" s="239"/>
-      <c r="Q30" s="239"/>
-      <c r="R30" s="239"/>
-      <c r="S30" s="239"/>
-      <c r="T30" s="239"/>
-      <c r="U30" s="292"/>
+      <c r="H30" s="238"/>
+      <c r="I30" s="238"/>
+      <c r="J30" s="238"/>
+      <c r="K30" s="238"/>
+      <c r="L30" s="238"/>
+      <c r="M30" s="238"/>
+      <c r="N30" s="238"/>
+      <c r="O30" s="238"/>
+      <c r="P30" s="238"/>
+      <c r="Q30" s="238"/>
+      <c r="R30" s="238"/>
+      <c r="S30" s="238"/>
+      <c r="T30" s="238"/>
+      <c r="U30" s="291"/>
     </row>
     <row r="31" spans="2:21" ht="24.950000" customHeight="1">
-      <c r="B31" s="253"/>
-      <c r="C31" s="254"/>
-      <c r="D31" s="219"/>
-      <c r="E31" s="219"/>
-      <c r="F31" s="219"/>
-      <c r="G31" s="239" t="s">
+      <c r="B31" s="252"/>
+      <c r="C31" s="253"/>
+      <c r="D31" s="218"/>
+      <c r="E31" s="218"/>
+      <c r="F31" s="218"/>
+      <c r="G31" s="238" t="s">
         <v>199</v>
       </c>
-      <c r="H31" s="239"/>
-      <c r="I31" s="239"/>
-      <c r="J31" s="239"/>
-      <c r="K31" s="239"/>
-      <c r="L31" s="239"/>
-      <c r="M31" s="239"/>
-      <c r="N31" s="239"/>
-      <c r="O31" s="239"/>
-      <c r="P31" s="239"/>
-      <c r="Q31" s="239"/>
-      <c r="R31" s="239"/>
-      <c r="S31" s="239"/>
-      <c r="T31" s="239"/>
-      <c r="U31" s="292"/>
+      <c r="H31" s="238"/>
+      <c r="I31" s="238"/>
+      <c r="J31" s="238"/>
+      <c r="K31" s="238"/>
+      <c r="L31" s="238"/>
+      <c r="M31" s="238"/>
+      <c r="N31" s="238"/>
+      <c r="O31" s="238"/>
+      <c r="P31" s="238"/>
+      <c r="Q31" s="238"/>
+      <c r="R31" s="238"/>
+      <c r="S31" s="238"/>
+      <c r="T31" s="238"/>
+      <c r="U31" s="291"/>
     </row>
     <row r="32" spans="2:21" ht="24.950000" customHeight="1">
-      <c r="B32" s="253"/>
-      <c r="C32" s="254"/>
-      <c r="D32" s="219"/>
-      <c r="E32" s="219"/>
-      <c r="F32" s="219"/>
-      <c r="G32" s="239" t="s">
+      <c r="B32" s="252"/>
+      <c r="C32" s="253"/>
+      <c r="D32" s="218"/>
+      <c r="E32" s="218"/>
+      <c r="F32" s="218"/>
+      <c r="G32" s="238" t="s">
         <v>200</v>
       </c>
-      <c r="H32" s="239"/>
-      <c r="I32" s="239"/>
-      <c r="J32" s="239"/>
-      <c r="K32" s="239"/>
-      <c r="L32" s="239"/>
-      <c r="M32" s="239"/>
-      <c r="N32" s="239"/>
-      <c r="O32" s="239"/>
-      <c r="P32" s="239"/>
-      <c r="Q32" s="239"/>
-      <c r="R32" s="239"/>
-      <c r="S32" s="239"/>
-      <c r="T32" s="239"/>
-      <c r="U32" s="292"/>
+      <c r="H32" s="238"/>
+      <c r="I32" s="238"/>
+      <c r="J32" s="238"/>
+      <c r="K32" s="238"/>
+      <c r="L32" s="238"/>
+      <c r="M32" s="238"/>
+      <c r="N32" s="238"/>
+      <c r="O32" s="238"/>
+      <c r="P32" s="238"/>
+      <c r="Q32" s="238"/>
+      <c r="R32" s="238"/>
+      <c r="S32" s="238"/>
+      <c r="T32" s="238"/>
+      <c r="U32" s="291"/>
     </row>
     <row r="33" spans="2:21" ht="24.950000" customHeight="1">
-      <c r="B33" s="253"/>
-      <c r="C33" s="254"/>
-      <c r="D33" s="219"/>
-      <c r="E33" s="219"/>
-      <c r="F33" s="219"/>
-      <c r="G33" s="239" t="s">
+      <c r="B33" s="252"/>
+      <c r="C33" s="253"/>
+      <c r="D33" s="218"/>
+      <c r="E33" s="218"/>
+      <c r="F33" s="218"/>
+      <c r="G33" s="238" t="s">
         <v>201</v>
       </c>
-      <c r="H33" s="239"/>
-      <c r="I33" s="239"/>
-      <c r="J33" s="239"/>
-      <c r="K33" s="239"/>
-      <c r="L33" s="239"/>
-      <c r="M33" s="239"/>
-      <c r="N33" s="239"/>
-      <c r="O33" s="239"/>
-      <c r="P33" s="239"/>
-      <c r="Q33" s="239"/>
-      <c r="R33" s="239"/>
-      <c r="S33" s="239"/>
-      <c r="T33" s="239"/>
-      <c r="U33" s="292"/>
+      <c r="H33" s="238"/>
+      <c r="I33" s="238"/>
+      <c r="J33" s="238"/>
+      <c r="K33" s="238"/>
+      <c r="L33" s="238"/>
+      <c r="M33" s="238"/>
+      <c r="N33" s="238"/>
+      <c r="O33" s="238"/>
+      <c r="P33" s="238"/>
+      <c r="Q33" s="238"/>
+      <c r="R33" s="238"/>
+      <c r="S33" s="238"/>
+      <c r="T33" s="238"/>
+      <c r="U33" s="291"/>
     </row>
     <row r="34" spans="2:21" ht="24.950000" customHeight="1">
-      <c r="B34" s="253"/>
-      <c r="C34" s="254"/>
-      <c r="D34" s="219"/>
-      <c r="E34" s="219"/>
-      <c r="F34" s="219"/>
-      <c r="G34" s="293" t="s">
+      <c r="B34" s="252"/>
+      <c r="C34" s="253"/>
+      <c r="D34" s="218"/>
+      <c r="E34" s="218"/>
+      <c r="F34" s="218"/>
+      <c r="G34" s="292" t="s">
         <v>202</v>
       </c>
-      <c r="H34" s="293"/>
-      <c r="I34" s="293"/>
-      <c r="J34" s="293"/>
-      <c r="K34" s="293"/>
-      <c r="L34" s="293"/>
-      <c r="M34" s="293"/>
-      <c r="N34" s="293"/>
-      <c r="O34" s="293"/>
-      <c r="P34" s="293"/>
-      <c r="Q34" s="293"/>
-      <c r="R34" s="293"/>
-      <c r="S34" s="293"/>
-      <c r="T34" s="293"/>
-      <c r="U34" s="294"/>
+      <c r="H34" s="292"/>
+      <c r="I34" s="292"/>
+      <c r="J34" s="292"/>
+      <c r="K34" s="292"/>
+      <c r="L34" s="292"/>
+      <c r="M34" s="292"/>
+      <c r="N34" s="292"/>
+      <c r="O34" s="292"/>
+      <c r="P34" s="292"/>
+      <c r="Q34" s="292"/>
+      <c r="R34" s="292"/>
+      <c r="S34" s="292"/>
+      <c r="T34" s="292"/>
+      <c r="U34" s="293"/>
     </row>
     <row r="35" spans="2:21" ht="24.950000" customHeight="1">
-      <c r="B35" s="253" t="s">
+      <c r="B35" s="252" t="s">
         <v>30</v>
       </c>
-      <c r="C35" s="254"/>
-      <c r="D35" s="219" t="s">
+      <c r="C35" s="253"/>
+      <c r="D35" s="218" t="s">
         <v>31</v>
       </c>
-      <c r="E35" s="219"/>
-      <c r="F35" s="219"/>
-      <c r="G35" s="284" t="str">
+      <c r="E35" s="218"/>
+      <c r="F35" s="218"/>
+      <c r="G35" s="283" t="str">
         <f>G29&amp;" 시설물 구조안전진단 용역"</f>
         <v>효성뉴서울5차아파트 시설물 구조안전진단 용역</v>
       </c>
-      <c r="H35" s="285"/>
-      <c r="I35" s="285"/>
-      <c r="J35" s="285"/>
-      <c r="K35" s="285"/>
-      <c r="L35" s="285"/>
-      <c r="M35" s="285"/>
-      <c r="N35" s="285"/>
-      <c r="O35" s="285"/>
-      <c r="P35" s="285"/>
-      <c r="Q35" s="285"/>
-      <c r="R35" s="285"/>
-      <c r="S35" s="285"/>
-      <c r="T35" s="285"/>
-      <c r="U35" s="286"/>
+      <c r="H35" s="284"/>
+      <c r="I35" s="284"/>
+      <c r="J35" s="284"/>
+      <c r="K35" s="284"/>
+      <c r="L35" s="284"/>
+      <c r="M35" s="284"/>
+      <c r="N35" s="284"/>
+      <c r="O35" s="284"/>
+      <c r="P35" s="284"/>
+      <c r="Q35" s="284"/>
+      <c r="R35" s="284"/>
+      <c r="S35" s="284"/>
+      <c r="T35" s="284"/>
+      <c r="U35" s="285"/>
     </row>
     <row r="36" spans="2:21" ht="24.950000" customHeight="1">
-      <c r="B36" s="253"/>
-      <c r="C36" s="254"/>
-      <c r="D36" s="219" t="s">
+      <c r="B36" s="252"/>
+      <c r="C36" s="253"/>
+      <c r="D36" s="218" t="s">
         <v>32</v>
       </c>
-      <c r="E36" s="219"/>
-      <c r="F36" s="219"/>
-      <c r="G36" s="259" t="str">
+      <c r="E36" s="218"/>
+      <c r="F36" s="218"/>
+      <c r="G36" s="258" t="str">
         <f>갑지!L31</f>
         <v>일금이백오십만원정 (₩2,500,000) - VAT별도</v>
       </c>
-      <c r="H36" s="259"/>
-      <c r="I36" s="259"/>
-      <c r="J36" s="259"/>
-      <c r="K36" s="259"/>
-      <c r="L36" s="259"/>
-      <c r="M36" s="259"/>
-      <c r="N36" s="259"/>
-      <c r="O36" s="259"/>
-      <c r="P36" s="259"/>
-      <c r="Q36" s="259"/>
-      <c r="R36" s="259"/>
-      <c r="S36" s="259"/>
-      <c r="T36" s="259"/>
-      <c r="U36" s="260"/>
+      <c r="H36" s="258"/>
+      <c r="I36" s="258"/>
+      <c r="J36" s="258"/>
+      <c r="K36" s="258"/>
+      <c r="L36" s="258"/>
+      <c r="M36" s="258"/>
+      <c r="N36" s="258"/>
+      <c r="O36" s="258"/>
+      <c r="P36" s="258"/>
+      <c r="Q36" s="258"/>
+      <c r="R36" s="258"/>
+      <c r="S36" s="258"/>
+      <c r="T36" s="258"/>
+      <c r="U36" s="259"/>
     </row>
     <row r="37" spans="2:21" ht="24.950000" customHeight="1">
-      <c r="B37" s="253"/>
-      <c r="C37" s="254"/>
-      <c r="D37" s="219" t="s">
+      <c r="B37" s="252"/>
+      <c r="C37" s="253"/>
+      <c r="D37" s="218" t="s">
         <v>14</v>
       </c>
-      <c r="E37" s="219"/>
-      <c r="F37" s="219"/>
-      <c r="G37" s="261" t="str">
+      <c r="E37" s="218"/>
+      <c r="F37" s="218"/>
+      <c r="G37" s="260" t="str">
         <f>갑지!L31</f>
         <v>일금이백오십만원정 (₩2,500,000) - VAT별도</v>
       </c>
-      <c r="H37" s="261"/>
-      <c r="I37" s="261"/>
-      <c r="J37" s="261"/>
-      <c r="K37" s="261"/>
-      <c r="L37" s="261"/>
-      <c r="M37" s="261"/>
-      <c r="N37" s="261"/>
-      <c r="O37" s="261"/>
-      <c r="P37" s="261"/>
-      <c r="Q37" s="261"/>
-      <c r="R37" s="261"/>
-      <c r="S37" s="261"/>
-      <c r="T37" s="261"/>
-      <c r="U37" s="262"/>
+      <c r="H37" s="260"/>
+      <c r="I37" s="260"/>
+      <c r="J37" s="260"/>
+      <c r="K37" s="260"/>
+      <c r="L37" s="260"/>
+      <c r="M37" s="260"/>
+      <c r="N37" s="260"/>
+      <c r="O37" s="260"/>
+      <c r="P37" s="260"/>
+      <c r="Q37" s="260"/>
+      <c r="R37" s="260"/>
+      <c r="S37" s="260"/>
+      <c r="T37" s="260"/>
+      <c r="U37" s="261"/>
     </row>
     <row r="38" spans="2:21" ht="24.950000" customHeight="1">
-      <c r="B38" s="253"/>
-      <c r="C38" s="254"/>
-      <c r="D38" s="219" t="s">
+      <c r="B38" s="252"/>
+      <c r="C38" s="253"/>
+      <c r="D38" s="218" t="s">
         <v>33</v>
       </c>
-      <c r="E38" s="219"/>
-      <c r="F38" s="219"/>
-      <c r="G38" s="250" t="s">
+      <c r="E38" s="218"/>
+      <c r="F38" s="218"/>
+      <c r="G38" s="249" t="s">
         <v>34</v>
       </c>
-      <c r="H38" s="250"/>
-      <c r="I38" s="250"/>
-      <c r="J38" s="250"/>
-      <c r="K38" s="250"/>
-      <c r="L38" s="250"/>
-      <c r="M38" s="250"/>
-      <c r="N38" s="250"/>
-      <c r="O38" s="250"/>
-      <c r="P38" s="250"/>
-      <c r="Q38" s="250"/>
-      <c r="R38" s="250"/>
-      <c r="S38" s="250"/>
-      <c r="T38" s="250"/>
-      <c r="U38" s="251"/>
+      <c r="H38" s="249"/>
+      <c r="I38" s="249"/>
+      <c r="J38" s="249"/>
+      <c r="K38" s="249"/>
+      <c r="L38" s="249"/>
+      <c r="M38" s="249"/>
+      <c r="N38" s="249"/>
+      <c r="O38" s="249"/>
+      <c r="P38" s="249"/>
+      <c r="Q38" s="249"/>
+      <c r="R38" s="249"/>
+      <c r="S38" s="249"/>
+      <c r="T38" s="249"/>
+      <c r="U38" s="250"/>
     </row>
     <row r="39" spans="2:21" ht="24.950000" customHeight="1">
-      <c r="B39" s="253"/>
-      <c r="C39" s="254"/>
-      <c r="D39" s="219" t="s">
+      <c r="B39" s="252"/>
+      <c r="C39" s="253"/>
+      <c r="D39" s="218" t="s">
         <v>35</v>
       </c>
-      <c r="E39" s="219"/>
-      <c r="F39" s="219"/>
-      <c r="G39" s="250" t="s">
+      <c r="E39" s="218"/>
+      <c r="F39" s="218"/>
+      <c r="G39" s="249" t="s">
         <v>117</v>
       </c>
-      <c r="H39" s="250"/>
-      <c r="I39" s="250"/>
-      <c r="J39" s="250"/>
-      <c r="K39" s="250"/>
-      <c r="L39" s="250"/>
-      <c r="M39" s="250"/>
-      <c r="N39" s="250"/>
-      <c r="O39" s="250"/>
-      <c r="P39" s="250"/>
-      <c r="Q39" s="250"/>
-      <c r="R39" s="250"/>
-      <c r="S39" s="250"/>
-      <c r="T39" s="250"/>
-      <c r="U39" s="251"/>
+      <c r="H39" s="249"/>
+      <c r="I39" s="249"/>
+      <c r="J39" s="249"/>
+      <c r="K39" s="249"/>
+      <c r="L39" s="249"/>
+      <c r="M39" s="249"/>
+      <c r="N39" s="249"/>
+      <c r="O39" s="249"/>
+      <c r="P39" s="249"/>
+      <c r="Q39" s="249"/>
+      <c r="R39" s="249"/>
+      <c r="S39" s="249"/>
+      <c r="T39" s="249"/>
+      <c r="U39" s="250"/>
     </row>
     <row r="40" spans="2:21" ht="24.950000" customHeight="1">
-      <c r="B40" s="253"/>
-      <c r="C40" s="254"/>
-      <c r="D40" s="219" t="s">
+      <c r="B40" s="252"/>
+      <c r="C40" s="253"/>
+      <c r="D40" s="218" t="s">
         <v>36</v>
       </c>
-      <c r="E40" s="219"/>
-      <c r="F40" s="219"/>
-      <c r="G40" s="250" t="str">
+      <c r="E40" s="218"/>
+      <c r="F40" s="218"/>
+      <c r="G40" s="249" t="str">
         <f>갑지!L22</f>
         <v>인천 계양구 아나지로 199 (효성동)</v>
       </c>
-      <c r="H40" s="250"/>
-      <c r="I40" s="250"/>
-      <c r="J40" s="250"/>
-      <c r="K40" s="250"/>
-      <c r="L40" s="250"/>
-      <c r="M40" s="250"/>
-      <c r="N40" s="250"/>
-      <c r="O40" s="250"/>
-      <c r="P40" s="250"/>
-      <c r="Q40" s="250"/>
-      <c r="R40" s="250"/>
-      <c r="S40" s="250"/>
-      <c r="T40" s="250"/>
-      <c r="U40" s="251"/>
+      <c r="H40" s="249"/>
+      <c r="I40" s="249"/>
+      <c r="J40" s="249"/>
+      <c r="K40" s="249"/>
+      <c r="L40" s="249"/>
+      <c r="M40" s="249"/>
+      <c r="N40" s="249"/>
+      <c r="O40" s="249"/>
+      <c r="P40" s="249"/>
+      <c r="Q40" s="249"/>
+      <c r="R40" s="249"/>
+      <c r="S40" s="249"/>
+      <c r="T40" s="249"/>
+      <c r="U40" s="250"/>
     </row>
     <row r="41" spans="2:21" ht="24.950000" customHeight="1">
-      <c r="B41" s="253"/>
-      <c r="C41" s="254"/>
-      <c r="D41" s="219"/>
-      <c r="E41" s="219"/>
-      <c r="F41" s="219"/>
-      <c r="G41" s="270" t="s">
+      <c r="B41" s="252"/>
+      <c r="C41" s="253"/>
+      <c r="D41" s="218"/>
+      <c r="E41" s="218"/>
+      <c r="F41" s="218"/>
+      <c r="G41" s="269" t="s">
         <v>194</v>
       </c>
       <c r="H41" s="153"/>
@@ -39252,69 +39132,69 @@
       <c r="R41" s="153"/>
       <c r="S41" s="153"/>
       <c r="T41" s="153"/>
-      <c r="U41" s="271"/>
+      <c r="U41" s="270"/>
     </row>
     <row r="42" spans="2:21" ht="24.950000" customHeight="1">
-      <c r="B42" s="255"/>
-      <c r="C42" s="256"/>
-      <c r="D42" s="263" t="s">
+      <c r="B42" s="254"/>
+      <c r="C42" s="255"/>
+      <c r="D42" s="262" t="s">
         <v>37</v>
       </c>
-      <c r="E42" s="264"/>
-      <c r="F42" s="265"/>
-      <c r="G42" s="266" t="s">
+      <c r="E42" s="263"/>
+      <c r="F42" s="264"/>
+      <c r="G42" s="265" t="s">
         <v>38</v>
       </c>
-      <c r="H42" s="267"/>
-      <c r="I42" s="267"/>
-      <c r="J42" s="267"/>
-      <c r="K42" s="267"/>
-      <c r="L42" s="267"/>
-      <c r="M42" s="267"/>
-      <c r="N42" s="267"/>
-      <c r="O42" s="267"/>
-      <c r="P42" s="267"/>
-      <c r="Q42" s="267"/>
-      <c r="R42" s="267"/>
-      <c r="S42" s="267"/>
-      <c r="T42" s="267"/>
-      <c r="U42" s="268"/>
+      <c r="H42" s="266"/>
+      <c r="I42" s="266"/>
+      <c r="J42" s="266"/>
+      <c r="K42" s="266"/>
+      <c r="L42" s="266"/>
+      <c r="M42" s="266"/>
+      <c r="N42" s="266"/>
+      <c r="O42" s="266"/>
+      <c r="P42" s="266"/>
+      <c r="Q42" s="266"/>
+      <c r="R42" s="266"/>
+      <c r="S42" s="266"/>
+      <c r="T42" s="266"/>
+      <c r="U42" s="267"/>
     </row>
     <row r="43" spans="2:21" ht="24.950000" customHeight="1">
-      <c r="B43" s="257"/>
-      <c r="C43" s="258"/>
-      <c r="D43" s="269" t="s">
+      <c r="B43" s="256"/>
+      <c r="C43" s="257"/>
+      <c r="D43" s="268" t="s">
         <v>39</v>
       </c>
-      <c r="E43" s="269"/>
-      <c r="F43" s="269"/>
-      <c r="G43" s="237" t="s">
+      <c r="E43" s="268"/>
+      <c r="F43" s="268"/>
+      <c r="G43" s="236" t="s">
         <v>167</v>
       </c>
-      <c r="H43" s="237"/>
-      <c r="I43" s="237"/>
-      <c r="J43" s="237"/>
-      <c r="K43" s="237"/>
-      <c r="L43" s="237"/>
-      <c r="M43" s="237"/>
-      <c r="N43" s="237"/>
-      <c r="O43" s="237"/>
-      <c r="P43" s="237"/>
-      <c r="Q43" s="237"/>
-      <c r="R43" s="237"/>
-      <c r="S43" s="237"/>
-      <c r="T43" s="237"/>
-      <c r="U43" s="238"/>
+      <c r="H43" s="236"/>
+      <c r="I43" s="236"/>
+      <c r="J43" s="236"/>
+      <c r="K43" s="236"/>
+      <c r="L43" s="236"/>
+      <c r="M43" s="236"/>
+      <c r="N43" s="236"/>
+      <c r="O43" s="236"/>
+      <c r="P43" s="236"/>
+      <c r="Q43" s="236"/>
+      <c r="R43" s="236"/>
+      <c r="S43" s="236"/>
+      <c r="T43" s="236"/>
+      <c r="U43" s="237"/>
     </row>
     <row r="44" spans="2:21">
-      <c r="B44" s="245"/>
-      <c r="C44" s="246"/>
-      <c r="D44" s="246"/>
-      <c r="E44" s="246"/>
+      <c r="B44" s="244"/>
+      <c r="C44" s="245"/>
+      <c r="D44" s="245"/>
+      <c r="E44" s="245"/>
       <c r="U44" s="3"/>
     </row>
     <row r="45" spans="2:21" ht="67.500000" customHeight="1">
-      <c r="B45" s="247" t="s">
+      <c r="B45" s="246" t="s">
         <v>40</v>
       </c>
       <c r="C45" s="22"/>
@@ -39335,7 +39215,7 @@
       <c r="R45" s="22"/>
       <c r="S45" s="22"/>
       <c r="T45" s="22"/>
-      <c r="U45" s="244"/>
+      <c r="U45" s="243"/>
     </row>
     <row r="46" spans="2:21">
       <c r="B46" s="24"/>
@@ -39345,7 +39225,7 @@
       <c r="U46" s="3"/>
     </row>
     <row r="47" spans="2:21" ht="24.950000" customHeight="1">
-      <c r="B47" s="243" t="s">
+      <c r="B47" s="242" t="s">
         <v>41</v>
       </c>
       <c r="C47" s="23"/>
@@ -39368,7 +39248,7 @@
       <c r="R47" s="22"/>
       <c r="S47" s="22"/>
       <c r="T47" s="22"/>
-      <c r="U47" s="244"/>
+      <c r="U47" s="243"/>
     </row>
     <row r="48" spans="2:21" ht="24.950000" customHeight="1">
       <c r="B48" s="26"/>
@@ -39392,7 +39272,7 @@
       <c r="R48" s="22"/>
       <c r="S48" s="22"/>
       <c r="T48" s="22"/>
-      <c r="U48" s="244"/>
+      <c r="U48" s="243"/>
     </row>
     <row r="49" spans="2:21" ht="24.950000" customHeight="1">
       <c r="B49" s="26"/>
@@ -39416,206 +39296,206 @@
       <c r="R49" s="22"/>
       <c r="S49" s="22"/>
       <c r="T49" s="22"/>
-      <c r="U49" s="244"/>
+      <c r="U49" s="243"/>
     </row>
     <row r="50" spans="2:21">
-      <c r="B50" s="245"/>
-      <c r="C50" s="246"/>
-      <c r="D50" s="246"/>
-      <c r="E50" s="246"/>
+      <c r="B50" s="244"/>
+      <c r="C50" s="245"/>
+      <c r="D50" s="245"/>
+      <c r="E50" s="245"/>
       <c r="U50" s="3"/>
     </row>
     <row r="51" spans="2:21" ht="24.950000" customHeight="1">
-      <c r="B51" s="247" t="s">
+      <c r="B51" s="246" t="s">
         <v>42</v>
       </c>
       <c r="C51" s="22"/>
       <c r="D51" s="22"/>
-      <c r="E51" s="248" t="s">
+      <c r="E51" s="247" t="s">
         <v>112</v>
       </c>
-      <c r="F51" s="248"/>
-      <c r="G51" s="248"/>
-      <c r="H51" s="248"/>
-      <c r="I51" s="248"/>
-      <c r="J51" s="248"/>
-      <c r="K51" s="248"/>
-      <c r="L51" s="248"/>
-      <c r="M51" s="248"/>
-      <c r="N51" s="248"/>
-      <c r="O51" s="248"/>
-      <c r="P51" s="248"/>
-      <c r="Q51" s="248"/>
-      <c r="R51" s="248"/>
-      <c r="S51" s="248"/>
-      <c r="T51" s="248"/>
-      <c r="U51" s="249"/>
+      <c r="F51" s="247"/>
+      <c r="G51" s="247"/>
+      <c r="H51" s="247"/>
+      <c r="I51" s="247"/>
+      <c r="J51" s="247"/>
+      <c r="K51" s="247"/>
+      <c r="L51" s="247"/>
+      <c r="M51" s="247"/>
+      <c r="N51" s="247"/>
+      <c r="O51" s="247"/>
+      <c r="P51" s="247"/>
+      <c r="Q51" s="247"/>
+      <c r="R51" s="247"/>
+      <c r="S51" s="247"/>
+      <c r="T51" s="247"/>
+      <c r="U51" s="248"/>
     </row>
     <row r="52" spans="2:21" ht="40.500000" customHeight="1">
-      <c r="B52" s="229" t="s">
+      <c r="B52" s="228" t="s">
         <v>43</v>
       </c>
-      <c r="C52" s="230"/>
-      <c r="D52" s="230"/>
-      <c r="E52" s="230"/>
-      <c r="F52" s="230"/>
-      <c r="G52" s="230"/>
-      <c r="H52" s="230"/>
-      <c r="I52" s="230"/>
-      <c r="J52" s="230"/>
-      <c r="K52" s="230"/>
-      <c r="L52" s="230" t="s">
+      <c r="C52" s="229"/>
+      <c r="D52" s="229"/>
+      <c r="E52" s="229"/>
+      <c r="F52" s="229"/>
+      <c r="G52" s="229"/>
+      <c r="H52" s="229"/>
+      <c r="I52" s="229"/>
+      <c r="J52" s="229"/>
+      <c r="K52" s="229"/>
+      <c r="L52" s="229" t="s">
         <v>44</v>
       </c>
-      <c r="M52" s="230"/>
-      <c r="N52" s="230"/>
-      <c r="O52" s="230"/>
-      <c r="P52" s="230"/>
-      <c r="Q52" s="230"/>
-      <c r="R52" s="230"/>
-      <c r="S52" s="230"/>
-      <c r="T52" s="230"/>
-      <c r="U52" s="252"/>
+      <c r="M52" s="229"/>
+      <c r="N52" s="229"/>
+      <c r="O52" s="229"/>
+      <c r="P52" s="229"/>
+      <c r="Q52" s="229"/>
+      <c r="R52" s="229"/>
+      <c r="S52" s="229"/>
+      <c r="T52" s="229"/>
+      <c r="U52" s="251"/>
     </row>
     <row r="53" spans="2:21" ht="40.500000" customHeight="1">
-      <c r="B53" s="229" t="s">
+      <c r="B53" s="228" t="s">
         <v>45</v>
       </c>
-      <c r="C53" s="230"/>
-      <c r="D53" s="230"/>
-      <c r="E53" s="231" t="str">
+      <c r="C53" s="229"/>
+      <c r="D53" s="229"/>
+      <c r="E53" s="230" t="str">
         <f>G29</f>
         <v>효성뉴서울5차아파트</v>
       </c>
-      <c r="F53" s="231"/>
-      <c r="G53" s="231"/>
-      <c r="H53" s="231"/>
-      <c r="I53" s="231"/>
-      <c r="J53" s="231"/>
-      <c r="K53" s="231"/>
-      <c r="L53" s="230" t="s">
+      <c r="F53" s="230"/>
+      <c r="G53" s="230"/>
+      <c r="H53" s="230"/>
+      <c r="I53" s="230"/>
+      <c r="J53" s="230"/>
+      <c r="K53" s="230"/>
+      <c r="L53" s="229" t="s">
         <v>46</v>
       </c>
-      <c r="M53" s="230"/>
-      <c r="N53" s="230"/>
-      <c r="O53" s="241" t="s">
+      <c r="M53" s="229"/>
+      <c r="N53" s="229"/>
+      <c r="O53" s="240" t="s">
         <v>47</v>
       </c>
-      <c r="P53" s="241"/>
-      <c r="Q53" s="241"/>
-      <c r="R53" s="241"/>
-      <c r="S53" s="241"/>
-      <c r="T53" s="241"/>
-      <c r="U53" s="242"/>
+      <c r="P53" s="240"/>
+      <c r="Q53" s="240"/>
+      <c r="R53" s="240"/>
+      <c r="S53" s="240"/>
+      <c r="T53" s="240"/>
+      <c r="U53" s="241"/>
     </row>
     <row r="54" spans="2:21" ht="40.500000" customHeight="1">
-      <c r="B54" s="229" t="s">
+      <c r="B54" s="228" t="s">
         <v>48</v>
       </c>
-      <c r="C54" s="230"/>
-      <c r="D54" s="230"/>
-      <c r="E54" s="231" t="str">
+      <c r="C54" s="229"/>
+      <c r="D54" s="229"/>
+      <c r="E54" s="230" t="str">
         <f>G40</f>
         <v>인천 계양구 아나지로 199 (효성동)</v>
       </c>
-      <c r="F54" s="231"/>
-      <c r="G54" s="231"/>
-      <c r="H54" s="231"/>
-      <c r="I54" s="231"/>
-      <c r="J54" s="231"/>
-      <c r="K54" s="231"/>
-      <c r="L54" s="230" t="s">
+      <c r="F54" s="230"/>
+      <c r="G54" s="230"/>
+      <c r="H54" s="230"/>
+      <c r="I54" s="230"/>
+      <c r="J54" s="230"/>
+      <c r="K54" s="230"/>
+      <c r="L54" s="229" t="s">
         <v>49</v>
       </c>
-      <c r="M54" s="230"/>
-      <c r="N54" s="230"/>
-      <c r="O54" s="232" t="s">
+      <c r="M54" s="229"/>
+      <c r="N54" s="229"/>
+      <c r="O54" s="231" t="s">
         <v>227</v>
       </c>
-      <c r="P54" s="232"/>
-      <c r="Q54" s="232"/>
-      <c r="R54" s="232"/>
-      <c r="S54" s="232"/>
-      <c r="T54" s="232"/>
-      <c r="U54" s="233"/>
+      <c r="P54" s="231"/>
+      <c r="Q54" s="231"/>
+      <c r="R54" s="231"/>
+      <c r="S54" s="231"/>
+      <c r="T54" s="231"/>
+      <c r="U54" s="232"/>
     </row>
     <row r="55" spans="2:21" ht="40.500000" customHeight="1">
-      <c r="B55" s="234" t="s">
+      <c r="B55" s="233" t="s">
         <v>50</v>
       </c>
-      <c r="C55" s="235"/>
-      <c r="D55" s="235"/>
-      <c r="E55" s="236" t="s">
+      <c r="C55" s="234"/>
+      <c r="D55" s="234"/>
+      <c r="E55" s="235" t="s">
         <v>51</v>
       </c>
-      <c r="F55" s="236"/>
-      <c r="G55" s="236"/>
-      <c r="H55" s="236"/>
-      <c r="I55" s="236"/>
-      <c r="J55" s="236"/>
-      <c r="K55" s="236"/>
-      <c r="L55" s="235" t="s">
+      <c r="F55" s="235"/>
+      <c r="G55" s="235"/>
+      <c r="H55" s="235"/>
+      <c r="I55" s="235"/>
+      <c r="J55" s="235"/>
+      <c r="K55" s="235"/>
+      <c r="L55" s="234" t="s">
         <v>52</v>
       </c>
-      <c r="M55" s="235"/>
-      <c r="N55" s="235"/>
-      <c r="O55" s="237" t="s">
+      <c r="M55" s="234"/>
+      <c r="N55" s="234"/>
+      <c r="O55" s="236" t="s">
         <v>53</v>
       </c>
-      <c r="P55" s="237"/>
-      <c r="Q55" s="237"/>
-      <c r="R55" s="237"/>
-      <c r="S55" s="237"/>
-      <c r="T55" s="237"/>
-      <c r="U55" s="238"/>
+      <c r="P55" s="236"/>
+      <c r="Q55" s="236"/>
+      <c r="R55" s="236"/>
+      <c r="S55" s="236"/>
+      <c r="T55" s="236"/>
+      <c r="U55" s="237"/>
     </row>
     <row r="56" spans="2:21" ht="16.500000">
-      <c r="B56" s="227" t="s">
+      <c r="B56" s="226" t="s">
         <v>54</v>
       </c>
-      <c r="C56" s="227"/>
-      <c r="D56" s="227"/>
-      <c r="E56" s="227"/>
-      <c r="F56" s="227"/>
-      <c r="G56" s="227"/>
-      <c r="H56" s="227"/>
-      <c r="I56" s="227"/>
-      <c r="J56" s="227"/>
-      <c r="K56" s="227"/>
-      <c r="L56" s="227"/>
-      <c r="M56" s="227"/>
-      <c r="N56" s="227"/>
-      <c r="O56" s="227"/>
-      <c r="P56" s="227"/>
-      <c r="Q56" s="227"/>
-      <c r="R56" s="227"/>
-      <c r="S56" s="227"/>
-      <c r="T56" s="227"/>
-      <c r="U56" s="227"/>
+      <c r="C56" s="226"/>
+      <c r="D56" s="226"/>
+      <c r="E56" s="226"/>
+      <c r="F56" s="226"/>
+      <c r="G56" s="226"/>
+      <c r="H56" s="226"/>
+      <c r="I56" s="226"/>
+      <c r="J56" s="226"/>
+      <c r="K56" s="226"/>
+      <c r="L56" s="226"/>
+      <c r="M56" s="226"/>
+      <c r="N56" s="226"/>
+      <c r="O56" s="226"/>
+      <c r="P56" s="226"/>
+      <c r="Q56" s="226"/>
+      <c r="R56" s="226"/>
+      <c r="S56" s="226"/>
+      <c r="T56" s="226"/>
+      <c r="U56" s="226"/>
     </row>
     <row r="57" spans="2:21" ht="25.500000">
-      <c r="B57" s="228" t="s">
+      <c r="B57" s="227" t="s">
         <v>171</v>
       </c>
-      <c r="C57" s="228"/>
-      <c r="D57" s="228"/>
-      <c r="E57" s="228"/>
-      <c r="F57" s="228"/>
-      <c r="G57" s="228"/>
-      <c r="H57" s="228"/>
-      <c r="I57" s="228"/>
-      <c r="J57" s="228"/>
-      <c r="K57" s="228"/>
-      <c r="L57" s="228"/>
-      <c r="M57" s="228"/>
-      <c r="N57" s="228"/>
-      <c r="O57" s="228"/>
-      <c r="P57" s="228"/>
-      <c r="Q57" s="228"/>
-      <c r="R57" s="228"/>
-      <c r="S57" s="228"/>
-      <c r="T57" s="228"/>
-      <c r="U57" s="228"/>
+      <c r="C57" s="227"/>
+      <c r="D57" s="227"/>
+      <c r="E57" s="227"/>
+      <c r="F57" s="227"/>
+      <c r="G57" s="227"/>
+      <c r="H57" s="227"/>
+      <c r="I57" s="227"/>
+      <c r="J57" s="227"/>
+      <c r="K57" s="227"/>
+      <c r="L57" s="227"/>
+      <c r="M57" s="227"/>
+      <c r="N57" s="227"/>
+      <c r="O57" s="227"/>
+      <c r="P57" s="227"/>
+      <c r="Q57" s="227"/>
+      <c r="R57" s="227"/>
+      <c r="S57" s="227"/>
+      <c r="T57" s="227"/>
+      <c r="U57" s="227"/>
     </row>
     <row r="58" spans="2:21" ht="14.250000">
       <c r="B58" s="27"/>
@@ -39624,81 +39504,81 @@
       <c r="I58" s="4"/>
     </row>
     <row r="59" spans="2:21" ht="24.950000" customHeight="1">
-      <c r="B59" s="225" t="s">
+      <c r="B59" s="224" t="s">
         <v>222</v>
       </c>
-      <c r="C59" s="225"/>
-      <c r="D59" s="225"/>
-      <c r="E59" s="225"/>
-      <c r="F59" s="225"/>
-      <c r="G59" s="225"/>
-      <c r="H59" s="225"/>
-      <c r="I59" s="225"/>
-      <c r="J59" s="225"/>
-      <c r="K59" s="225"/>
-      <c r="L59" s="225"/>
-      <c r="M59" s="225"/>
-      <c r="N59" s="225"/>
-      <c r="O59" s="225"/>
-      <c r="P59" s="225"/>
-      <c r="Q59" s="225"/>
-      <c r="R59" s="225"/>
-      <c r="S59" s="225"/>
-      <c r="T59" s="225"/>
-      <c r="U59" s="225"/>
+      <c r="C59" s="224"/>
+      <c r="D59" s="224"/>
+      <c r="E59" s="224"/>
+      <c r="F59" s="224"/>
+      <c r="G59" s="224"/>
+      <c r="H59" s="224"/>
+      <c r="I59" s="224"/>
+      <c r="J59" s="224"/>
+      <c r="K59" s="224"/>
+      <c r="L59" s="224"/>
+      <c r="M59" s="224"/>
+      <c r="N59" s="224"/>
+      <c r="O59" s="224"/>
+      <c r="P59" s="224"/>
+      <c r="Q59" s="224"/>
+      <c r="R59" s="224"/>
+      <c r="S59" s="224"/>
+      <c r="T59" s="224"/>
+      <c r="U59" s="224"/>
     </row>
     <row r="60" spans="2:21" ht="28.500000" customHeight="1">
-      <c r="B60" s="239" t="s">
+      <c r="B60" s="238" t="s">
         <v>224</v>
       </c>
-      <c r="C60" s="239"/>
-      <c r="D60" s="239"/>
-      <c r="E60" s="239"/>
-      <c r="F60" s="239"/>
-      <c r="G60" s="239"/>
-      <c r="H60" s="239"/>
-      <c r="I60" s="239"/>
-      <c r="J60" s="240" t="str">
+      <c r="C60" s="238"/>
+      <c r="D60" s="238"/>
+      <c r="E60" s="238"/>
+      <c r="F60" s="238"/>
+      <c r="G60" s="238"/>
+      <c r="H60" s="238"/>
+      <c r="I60" s="238"/>
+      <c r="J60" s="239" t="str">
         <f>B9</f>
         <v>효성뉴서울5차아파트</v>
       </c>
-      <c r="K60" s="240"/>
-      <c r="L60" s="240"/>
-      <c r="M60" s="240"/>
-      <c r="N60" s="240"/>
-      <c r="O60" s="240"/>
-      <c r="P60" s="239" t="s">
+      <c r="K60" s="239"/>
+      <c r="L60" s="239"/>
+      <c r="M60" s="239"/>
+      <c r="N60" s="239"/>
+      <c r="O60" s="239"/>
+      <c r="P60" s="238" t="s">
         <v>225</v>
       </c>
-      <c r="Q60" s="239"/>
-      <c r="R60" s="239"/>
-      <c r="S60" s="239"/>
-      <c r="T60" s="239"/>
-      <c r="U60" s="239"/>
+      <c r="Q60" s="238"/>
+      <c r="R60" s="238"/>
+      <c r="S60" s="238"/>
+      <c r="T60" s="238"/>
+      <c r="U60" s="238"/>
     </row>
     <row r="61" spans="2:21" ht="24.950000" customHeight="1">
-      <c r="B61" s="225" t="s">
+      <c r="B61" s="224" t="s">
         <v>226</v>
       </c>
-      <c r="C61" s="225"/>
-      <c r="D61" s="225"/>
-      <c r="E61" s="225"/>
-      <c r="F61" s="225"/>
-      <c r="G61" s="225"/>
-      <c r="H61" s="225"/>
-      <c r="I61" s="225"/>
-      <c r="J61" s="225"/>
-      <c r="K61" s="225"/>
-      <c r="L61" s="225"/>
-      <c r="M61" s="225"/>
-      <c r="N61" s="225"/>
-      <c r="O61" s="225"/>
-      <c r="P61" s="225"/>
-      <c r="Q61" s="225"/>
-      <c r="R61" s="225"/>
-      <c r="S61" s="225"/>
-      <c r="T61" s="225"/>
-      <c r="U61" s="225"/>
+      <c r="C61" s="224"/>
+      <c r="D61" s="224"/>
+      <c r="E61" s="224"/>
+      <c r="F61" s="224"/>
+      <c r="G61" s="224"/>
+      <c r="H61" s="224"/>
+      <c r="I61" s="224"/>
+      <c r="J61" s="224"/>
+      <c r="K61" s="224"/>
+      <c r="L61" s="224"/>
+      <c r="M61" s="224"/>
+      <c r="N61" s="224"/>
+      <c r="O61" s="224"/>
+      <c r="P61" s="224"/>
+      <c r="Q61" s="224"/>
+      <c r="R61" s="224"/>
+      <c r="S61" s="224"/>
+      <c r="T61" s="224"/>
+      <c r="U61" s="224"/>
     </row>
     <row r="62" spans="2:21" ht="20.000000" customHeight="1">
       <c r="B62" s="22"/>
@@ -39803,7 +39683,7 @@
     </row>
     <row r="68" spans="2:21" ht="20.000000" customHeight="1">
       <c r="C68" s="31" t="str">
-        <f>"② 위      치 : "&amp;E54</f>
+        <f>"② 위      치 : "&amp;갑지!L22</f>
         <v>② 위      치 : 인천 계양구 아나지로 199 (효성동)</v>
       </c>
       <c r="D68" s="31"/>
@@ -40518,99 +40398,99 @@
     </row>
     <row r="109" spans="2:21" ht="20.000000" customHeight="1">
       <c r="B109" s="34"/>
-      <c r="C109" s="225" t="s">
+      <c r="C109" s="224" t="s">
         <v>213</v>
       </c>
-      <c r="D109" s="225"/>
-      <c r="E109" s="225"/>
-      <c r="F109" s="225"/>
-      <c r="G109" s="225"/>
-      <c r="H109" s="225"/>
-      <c r="I109" s="225"/>
-      <c r="J109" s="225"/>
-      <c r="K109" s="225"/>
-      <c r="L109" s="225"/>
-      <c r="M109" s="225"/>
-      <c r="N109" s="225"/>
-      <c r="O109" s="225"/>
-      <c r="P109" s="225"/>
-      <c r="Q109" s="225"/>
-      <c r="R109" s="225"/>
-      <c r="S109" s="225"/>
-      <c r="T109" s="225"/>
-      <c r="U109" s="225"/>
+      <c r="D109" s="224"/>
+      <c r="E109" s="224"/>
+      <c r="F109" s="224"/>
+      <c r="G109" s="224"/>
+      <c r="H109" s="224"/>
+      <c r="I109" s="224"/>
+      <c r="J109" s="224"/>
+      <c r="K109" s="224"/>
+      <c r="L109" s="224"/>
+      <c r="M109" s="224"/>
+      <c r="N109" s="224"/>
+      <c r="O109" s="224"/>
+      <c r="P109" s="224"/>
+      <c r="Q109" s="224"/>
+      <c r="R109" s="224"/>
+      <c r="S109" s="224"/>
+      <c r="T109" s="224"/>
+      <c r="U109" s="224"/>
     </row>
     <row r="110" spans="2:21" ht="20.000000" customHeight="1">
       <c r="B110" s="34"/>
-      <c r="C110" s="225" t="s">
+      <c r="C110" s="224" t="s">
         <v>212</v>
       </c>
-      <c r="D110" s="225"/>
-      <c r="E110" s="225"/>
-      <c r="F110" s="225"/>
-      <c r="G110" s="225"/>
-      <c r="H110" s="225"/>
-      <c r="I110" s="225"/>
-      <c r="J110" s="225"/>
-      <c r="K110" s="225"/>
-      <c r="L110" s="225"/>
-      <c r="M110" s="225"/>
-      <c r="N110" s="225"/>
-      <c r="O110" s="225"/>
-      <c r="P110" s="225"/>
-      <c r="Q110" s="225"/>
-      <c r="R110" s="225"/>
-      <c r="S110" s="225"/>
-      <c r="T110" s="225"/>
-      <c r="U110" s="225"/>
+      <c r="D110" s="224"/>
+      <c r="E110" s="224"/>
+      <c r="F110" s="224"/>
+      <c r="G110" s="224"/>
+      <c r="H110" s="224"/>
+      <c r="I110" s="224"/>
+      <c r="J110" s="224"/>
+      <c r="K110" s="224"/>
+      <c r="L110" s="224"/>
+      <c r="M110" s="224"/>
+      <c r="N110" s="224"/>
+      <c r="O110" s="224"/>
+      <c r="P110" s="224"/>
+      <c r="Q110" s="224"/>
+      <c r="R110" s="224"/>
+      <c r="S110" s="224"/>
+      <c r="T110" s="224"/>
+      <c r="U110" s="224"/>
     </row>
     <row r="111" spans="2:21" ht="20.000000" customHeight="1">
       <c r="B111" s="34"/>
-      <c r="C111" s="225" t="s">
+      <c r="C111" s="224" t="s">
         <v>214</v>
       </c>
-      <c r="D111" s="225"/>
-      <c r="E111" s="225"/>
-      <c r="F111" s="225"/>
-      <c r="G111" s="225"/>
-      <c r="H111" s="225"/>
-      <c r="I111" s="225"/>
-      <c r="J111" s="225"/>
-      <c r="K111" s="225"/>
-      <c r="L111" s="225"/>
-      <c r="M111" s="225"/>
-      <c r="N111" s="225"/>
-      <c r="O111" s="225"/>
-      <c r="P111" s="225"/>
-      <c r="Q111" s="225"/>
-      <c r="R111" s="225"/>
-      <c r="S111" s="225"/>
-      <c r="T111" s="225"/>
-      <c r="U111" s="225"/>
+      <c r="D111" s="224"/>
+      <c r="E111" s="224"/>
+      <c r="F111" s="224"/>
+      <c r="G111" s="224"/>
+      <c r="H111" s="224"/>
+      <c r="I111" s="224"/>
+      <c r="J111" s="224"/>
+      <c r="K111" s="224"/>
+      <c r="L111" s="224"/>
+      <c r="M111" s="224"/>
+      <c r="N111" s="224"/>
+      <c r="O111" s="224"/>
+      <c r="P111" s="224"/>
+      <c r="Q111" s="224"/>
+      <c r="R111" s="224"/>
+      <c r="S111" s="224"/>
+      <c r="T111" s="224"/>
+      <c r="U111" s="224"/>
     </row>
     <row r="112" spans="2:21" ht="20.000000" customHeight="1">
       <c r="B112" s="34"/>
-      <c r="C112" s="225" t="s">
+      <c r="C112" s="224" t="s">
         <v>215</v>
       </c>
-      <c r="D112" s="225"/>
-      <c r="E112" s="225"/>
-      <c r="F112" s="225"/>
-      <c r="G112" s="225"/>
-      <c r="H112" s="225"/>
-      <c r="I112" s="225"/>
-      <c r="J112" s="225"/>
-      <c r="K112" s="225"/>
-      <c r="L112" s="225"/>
-      <c r="M112" s="225"/>
-      <c r="N112" s="225"/>
-      <c r="O112" s="225"/>
-      <c r="P112" s="225"/>
-      <c r="Q112" s="225"/>
-      <c r="R112" s="225"/>
-      <c r="S112" s="225"/>
-      <c r="T112" s="225"/>
-      <c r="U112" s="225"/>
+      <c r="D112" s="224"/>
+      <c r="E112" s="224"/>
+      <c r="F112" s="224"/>
+      <c r="G112" s="224"/>
+      <c r="H112" s="224"/>
+      <c r="I112" s="224"/>
+      <c r="J112" s="224"/>
+      <c r="K112" s="224"/>
+      <c r="L112" s="224"/>
+      <c r="M112" s="224"/>
+      <c r="N112" s="224"/>
+      <c r="O112" s="224"/>
+      <c r="P112" s="224"/>
+      <c r="Q112" s="224"/>
+      <c r="R112" s="224"/>
+      <c r="S112" s="224"/>
+      <c r="T112" s="224"/>
+      <c r="U112" s="224"/>
     </row>
     <row r="113" spans="2:21" ht="20.000000" customHeight="1">
       <c r="B113" s="29"/>
@@ -40674,543 +40554,543 @@
       <c r="J117" s="28"/>
     </row>
     <row r="118" spans="2:21" ht="129.000000" customHeight="1">
-      <c r="C118" s="226" t="s">
+      <c r="C118" s="225" t="s">
         <v>75</v>
       </c>
-      <c r="D118" s="226"/>
-      <c r="E118" s="226"/>
-      <c r="F118" s="226"/>
-      <c r="G118" s="226"/>
-      <c r="H118" s="226"/>
-      <c r="I118" s="226"/>
-      <c r="J118" s="226"/>
-      <c r="K118" s="226"/>
-      <c r="L118" s="226"/>
-      <c r="M118" s="226"/>
-      <c r="N118" s="226"/>
-      <c r="O118" s="226"/>
-      <c r="P118" s="226"/>
-      <c r="Q118" s="226"/>
-      <c r="R118" s="226"/>
-      <c r="S118" s="226"/>
-      <c r="T118" s="226"/>
-      <c r="U118" s="226"/>
+      <c r="D118" s="225"/>
+      <c r="E118" s="225"/>
+      <c r="F118" s="225"/>
+      <c r="G118" s="225"/>
+      <c r="H118" s="225"/>
+      <c r="I118" s="225"/>
+      <c r="J118" s="225"/>
+      <c r="K118" s="225"/>
+      <c r="L118" s="225"/>
+      <c r="M118" s="225"/>
+      <c r="N118" s="225"/>
+      <c r="O118" s="225"/>
+      <c r="P118" s="225"/>
+      <c r="Q118" s="225"/>
+      <c r="R118" s="225"/>
+      <c r="S118" s="225"/>
+      <c r="T118" s="225"/>
+      <c r="U118" s="225"/>
     </row>
     <row r="119" ht="408.950000" customHeight="1"/>
     <row r="120" spans="2:21" ht="16.000000" customHeight="1">
-      <c r="B120" s="208" t="s">
+      <c r="B120" s="207" t="s">
         <v>76</v>
       </c>
-      <c r="C120" s="208"/>
-      <c r="D120" s="208"/>
-      <c r="E120" s="208"/>
-      <c r="F120" s="208"/>
-      <c r="G120" s="208"/>
-      <c r="H120" s="208"/>
-      <c r="I120" s="208"/>
+      <c r="C120" s="207"/>
+      <c r="D120" s="207"/>
+      <c r="E120" s="207"/>
+      <c r="F120" s="207"/>
+      <c r="G120" s="207"/>
+      <c r="H120" s="207"/>
+      <c r="I120" s="207"/>
     </row>
     <row r="121" spans="2:21" ht="33.750000" customHeight="1">
-      <c r="B121" s="209" t="s">
+      <c r="B121" s="208" t="s">
         <v>187</v>
       </c>
-      <c r="C121" s="209"/>
-      <c r="D121" s="209"/>
-      <c r="E121" s="209"/>
-      <c r="F121" s="209"/>
-      <c r="G121" s="209"/>
-      <c r="H121" s="209"/>
-      <c r="I121" s="209"/>
-      <c r="J121" s="209"/>
-      <c r="K121" s="209"/>
-      <c r="L121" s="209"/>
-      <c r="M121" s="209"/>
-      <c r="N121" s="209"/>
-      <c r="O121" s="209"/>
-      <c r="P121" s="209"/>
-      <c r="Q121" s="209"/>
-      <c r="R121" s="209"/>
-      <c r="S121" s="209"/>
-      <c r="T121" s="209"/>
-      <c r="U121" s="209"/>
+      <c r="C121" s="208"/>
+      <c r="D121" s="208"/>
+      <c r="E121" s="208"/>
+      <c r="F121" s="208"/>
+      <c r="G121" s="208"/>
+      <c r="H121" s="208"/>
+      <c r="I121" s="208"/>
+      <c r="J121" s="208"/>
+      <c r="K121" s="208"/>
+      <c r="L121" s="208"/>
+      <c r="M121" s="208"/>
+      <c r="N121" s="208"/>
+      <c r="O121" s="208"/>
+      <c r="P121" s="208"/>
+      <c r="Q121" s="208"/>
+      <c r="R121" s="208"/>
+      <c r="S121" s="208"/>
+      <c r="T121" s="208"/>
+      <c r="U121" s="208"/>
     </row>
     <row r="122" spans="2:21" ht="55.000000" customHeight="1">
-      <c r="B122" s="220" t="s">
+      <c r="B122" s="219" t="s">
         <v>77</v>
       </c>
-      <c r="C122" s="221"/>
-      <c r="D122" s="221"/>
-      <c r="E122" s="221"/>
-      <c r="F122" s="222" t="s">
+      <c r="C122" s="220"/>
+      <c r="D122" s="220"/>
+      <c r="E122" s="220"/>
+      <c r="F122" s="221" t="s">
         <v>78</v>
       </c>
-      <c r="G122" s="223"/>
-      <c r="H122" s="223"/>
-      <c r="I122" s="223"/>
-      <c r="J122" s="223"/>
-      <c r="K122" s="223"/>
-      <c r="L122" s="223"/>
-      <c r="M122" s="223"/>
-      <c r="N122" s="223"/>
-      <c r="O122" s="223"/>
-      <c r="P122" s="223"/>
-      <c r="Q122" s="223"/>
-      <c r="R122" s="223"/>
-      <c r="S122" s="223"/>
-      <c r="T122" s="223"/>
-      <c r="U122" s="224"/>
+      <c r="G122" s="222"/>
+      <c r="H122" s="222"/>
+      <c r="I122" s="222"/>
+      <c r="J122" s="222"/>
+      <c r="K122" s="222"/>
+      <c r="L122" s="222"/>
+      <c r="M122" s="222"/>
+      <c r="N122" s="222"/>
+      <c r="O122" s="222"/>
+      <c r="P122" s="222"/>
+      <c r="Q122" s="222"/>
+      <c r="R122" s="222"/>
+      <c r="S122" s="222"/>
+      <c r="T122" s="222"/>
+      <c r="U122" s="223"/>
     </row>
     <row r="123" spans="2:21" ht="55.000000" customHeight="1">
-      <c r="B123" s="198" t="s">
+      <c r="B123" s="197" t="s">
         <v>79</v>
       </c>
-      <c r="C123" s="199"/>
-      <c r="D123" s="199"/>
-      <c r="E123" s="199"/>
-      <c r="F123" s="202" t="s">
+      <c r="C123" s="198"/>
+      <c r="D123" s="198"/>
+      <c r="E123" s="198"/>
+      <c r="F123" s="201" t="s">
         <v>80</v>
       </c>
-      <c r="G123" s="203"/>
-      <c r="H123" s="203"/>
-      <c r="I123" s="203"/>
-      <c r="J123" s="203"/>
-      <c r="K123" s="203"/>
-      <c r="L123" s="203"/>
-      <c r="M123" s="203"/>
-      <c r="N123" s="203"/>
-      <c r="O123" s="203"/>
-      <c r="P123" s="203"/>
-      <c r="Q123" s="203"/>
-      <c r="R123" s="203"/>
-      <c r="S123" s="203"/>
-      <c r="T123" s="203"/>
-      <c r="U123" s="204"/>
+      <c r="G123" s="202"/>
+      <c r="H123" s="202"/>
+      <c r="I123" s="202"/>
+      <c r="J123" s="202"/>
+      <c r="K123" s="202"/>
+      <c r="L123" s="202"/>
+      <c r="M123" s="202"/>
+      <c r="N123" s="202"/>
+      <c r="O123" s="202"/>
+      <c r="P123" s="202"/>
+      <c r="Q123" s="202"/>
+      <c r="R123" s="202"/>
+      <c r="S123" s="202"/>
+      <c r="T123" s="202"/>
+      <c r="U123" s="203"/>
     </row>
     <row r="124" spans="2:21" ht="55.000000" customHeight="1">
-      <c r="B124" s="198" t="s">
+      <c r="B124" s="197" t="s">
         <v>81</v>
       </c>
-      <c r="C124" s="199"/>
-      <c r="D124" s="199"/>
-      <c r="E124" s="199"/>
-      <c r="F124" s="202" t="s">
+      <c r="C124" s="198"/>
+      <c r="D124" s="198"/>
+      <c r="E124" s="198"/>
+      <c r="F124" s="201" t="s">
         <v>82</v>
       </c>
-      <c r="G124" s="203"/>
-      <c r="H124" s="203"/>
-      <c r="I124" s="203"/>
-      <c r="J124" s="203"/>
-      <c r="K124" s="203"/>
-      <c r="L124" s="203"/>
-      <c r="M124" s="203"/>
-      <c r="N124" s="203"/>
-      <c r="O124" s="203"/>
-      <c r="P124" s="203"/>
-      <c r="Q124" s="203"/>
-      <c r="R124" s="203"/>
-      <c r="S124" s="203"/>
-      <c r="T124" s="203"/>
-      <c r="U124" s="204"/>
+      <c r="G124" s="202"/>
+      <c r="H124" s="202"/>
+      <c r="I124" s="202"/>
+      <c r="J124" s="202"/>
+      <c r="K124" s="202"/>
+      <c r="L124" s="202"/>
+      <c r="M124" s="202"/>
+      <c r="N124" s="202"/>
+      <c r="O124" s="202"/>
+      <c r="P124" s="202"/>
+      <c r="Q124" s="202"/>
+      <c r="R124" s="202"/>
+      <c r="S124" s="202"/>
+      <c r="T124" s="202"/>
+      <c r="U124" s="203"/>
     </row>
     <row r="125" spans="2:21" ht="55.000000" customHeight="1">
-      <c r="B125" s="198"/>
-      <c r="C125" s="199"/>
-      <c r="D125" s="199"/>
-      <c r="E125" s="199"/>
-      <c r="F125" s="202" t="s">
+      <c r="B125" s="197"/>
+      <c r="C125" s="198"/>
+      <c r="D125" s="198"/>
+      <c r="E125" s="198"/>
+      <c r="F125" s="201" t="s">
         <v>83</v>
       </c>
-      <c r="G125" s="203"/>
-      <c r="H125" s="203"/>
-      <c r="I125" s="203"/>
-      <c r="J125" s="203"/>
-      <c r="K125" s="203"/>
-      <c r="L125" s="203"/>
-      <c r="M125" s="203"/>
-      <c r="N125" s="203"/>
-      <c r="O125" s="203"/>
-      <c r="P125" s="203"/>
-      <c r="Q125" s="203"/>
-      <c r="R125" s="203"/>
-      <c r="S125" s="203"/>
-      <c r="T125" s="203"/>
-      <c r="U125" s="204"/>
+      <c r="G125" s="202"/>
+      <c r="H125" s="202"/>
+      <c r="I125" s="202"/>
+      <c r="J125" s="202"/>
+      <c r="K125" s="202"/>
+      <c r="L125" s="202"/>
+      <c r="M125" s="202"/>
+      <c r="N125" s="202"/>
+      <c r="O125" s="202"/>
+      <c r="P125" s="202"/>
+      <c r="Q125" s="202"/>
+      <c r="R125" s="202"/>
+      <c r="S125" s="202"/>
+      <c r="T125" s="202"/>
+      <c r="U125" s="203"/>
     </row>
     <row r="126" spans="2:21" ht="55.000000" customHeight="1">
-      <c r="B126" s="198"/>
-      <c r="C126" s="199"/>
-      <c r="D126" s="199"/>
-      <c r="E126" s="199"/>
-      <c r="F126" s="202" t="s">
+      <c r="B126" s="197"/>
+      <c r="C126" s="198"/>
+      <c r="D126" s="198"/>
+      <c r="E126" s="198"/>
+      <c r="F126" s="201" t="s">
         <v>84</v>
       </c>
-      <c r="G126" s="203"/>
-      <c r="H126" s="203"/>
-      <c r="I126" s="203"/>
-      <c r="J126" s="203"/>
-      <c r="K126" s="203"/>
-      <c r="L126" s="203"/>
-      <c r="M126" s="203"/>
-      <c r="N126" s="203"/>
-      <c r="O126" s="203"/>
-      <c r="P126" s="203"/>
-      <c r="Q126" s="203"/>
-      <c r="R126" s="203"/>
-      <c r="S126" s="203"/>
-      <c r="T126" s="203"/>
-      <c r="U126" s="204"/>
+      <c r="G126" s="202"/>
+      <c r="H126" s="202"/>
+      <c r="I126" s="202"/>
+      <c r="J126" s="202"/>
+      <c r="K126" s="202"/>
+      <c r="L126" s="202"/>
+      <c r="M126" s="202"/>
+      <c r="N126" s="202"/>
+      <c r="O126" s="202"/>
+      <c r="P126" s="202"/>
+      <c r="Q126" s="202"/>
+      <c r="R126" s="202"/>
+      <c r="S126" s="202"/>
+      <c r="T126" s="202"/>
+      <c r="U126" s="203"/>
     </row>
     <row r="127" spans="2:21" ht="55.000000" customHeight="1">
-      <c r="B127" s="198" t="s">
+      <c r="B127" s="197" t="s">
         <v>85</v>
       </c>
-      <c r="C127" s="199"/>
-      <c r="D127" s="199"/>
-      <c r="E127" s="199"/>
-      <c r="F127" s="210" t="s">
+      <c r="C127" s="198"/>
+      <c r="D127" s="198"/>
+      <c r="E127" s="198"/>
+      <c r="F127" s="209" t="s">
         <v>86</v>
       </c>
-      <c r="G127" s="211"/>
-      <c r="H127" s="211"/>
-      <c r="I127" s="211"/>
-      <c r="J127" s="211"/>
-      <c r="K127" s="211"/>
-      <c r="L127" s="211"/>
-      <c r="M127" s="211"/>
-      <c r="N127" s="211"/>
-      <c r="O127" s="211"/>
-      <c r="P127" s="211"/>
-      <c r="Q127" s="211"/>
-      <c r="R127" s="211"/>
-      <c r="S127" s="211"/>
-      <c r="T127" s="211"/>
-      <c r="U127" s="212"/>
+      <c r="G127" s="210"/>
+      <c r="H127" s="210"/>
+      <c r="I127" s="210"/>
+      <c r="J127" s="210"/>
+      <c r="K127" s="210"/>
+      <c r="L127" s="210"/>
+      <c r="M127" s="210"/>
+      <c r="N127" s="210"/>
+      <c r="O127" s="210"/>
+      <c r="P127" s="210"/>
+      <c r="Q127" s="210"/>
+      <c r="R127" s="210"/>
+      <c r="S127" s="210"/>
+      <c r="T127" s="210"/>
+      <c r="U127" s="211"/>
     </row>
     <row r="128" spans="2:21" ht="55.000000" hidden="1" customHeight="1">
-      <c r="B128" s="198"/>
-      <c r="C128" s="199"/>
-      <c r="D128" s="199"/>
-      <c r="E128" s="199"/>
-      <c r="F128" s="213"/>
-      <c r="G128" s="214"/>
-      <c r="H128" s="214"/>
-      <c r="I128" s="214"/>
-      <c r="J128" s="214"/>
-      <c r="K128" s="214"/>
-      <c r="L128" s="214"/>
-      <c r="M128" s="214"/>
-      <c r="N128" s="214"/>
-      <c r="O128" s="214"/>
-      <c r="P128" s="214"/>
-      <c r="Q128" s="214"/>
-      <c r="R128" s="214"/>
-      <c r="S128" s="214"/>
-      <c r="T128" s="214"/>
-      <c r="U128" s="215"/>
+      <c r="B128" s="197"/>
+      <c r="C128" s="198"/>
+      <c r="D128" s="198"/>
+      <c r="E128" s="198"/>
+      <c r="F128" s="212"/>
+      <c r="G128" s="213"/>
+      <c r="H128" s="213"/>
+      <c r="I128" s="213"/>
+      <c r="J128" s="213"/>
+      <c r="K128" s="213"/>
+      <c r="L128" s="213"/>
+      <c r="M128" s="213"/>
+      <c r="N128" s="213"/>
+      <c r="O128" s="213"/>
+      <c r="P128" s="213"/>
+      <c r="Q128" s="213"/>
+      <c r="R128" s="213"/>
+      <c r="S128" s="213"/>
+      <c r="T128" s="213"/>
+      <c r="U128" s="214"/>
     </row>
     <row r="129" spans="2:21" ht="55.000000" hidden="1" customHeight="1">
-      <c r="B129" s="198"/>
-      <c r="C129" s="199"/>
-      <c r="D129" s="199"/>
-      <c r="E129" s="199"/>
-      <c r="F129" s="216"/>
-      <c r="G129" s="217"/>
-      <c r="H129" s="217"/>
-      <c r="I129" s="217"/>
-      <c r="J129" s="217"/>
-      <c r="K129" s="217"/>
-      <c r="L129" s="217"/>
-      <c r="M129" s="217"/>
-      <c r="N129" s="217"/>
-      <c r="O129" s="217"/>
-      <c r="P129" s="217"/>
-      <c r="Q129" s="217"/>
-      <c r="R129" s="217"/>
-      <c r="S129" s="217"/>
-      <c r="T129" s="217"/>
-      <c r="U129" s="218"/>
+      <c r="B129" s="197"/>
+      <c r="C129" s="198"/>
+      <c r="D129" s="198"/>
+      <c r="E129" s="198"/>
+      <c r="F129" s="215"/>
+      <c r="G129" s="216"/>
+      <c r="H129" s="216"/>
+      <c r="I129" s="216"/>
+      <c r="J129" s="216"/>
+      <c r="K129" s="216"/>
+      <c r="L129" s="216"/>
+      <c r="M129" s="216"/>
+      <c r="N129" s="216"/>
+      <c r="O129" s="216"/>
+      <c r="P129" s="216"/>
+      <c r="Q129" s="216"/>
+      <c r="R129" s="216"/>
+      <c r="S129" s="216"/>
+      <c r="T129" s="216"/>
+      <c r="U129" s="217"/>
     </row>
     <row r="130" spans="2:21" ht="55.000000" customHeight="1">
-      <c r="B130" s="198" t="s">
+      <c r="B130" s="197" t="s">
         <v>87</v>
       </c>
-      <c r="C130" s="199"/>
-      <c r="D130" s="219" t="s">
+      <c r="C130" s="198"/>
+      <c r="D130" s="218" t="s">
         <v>88</v>
       </c>
-      <c r="E130" s="219"/>
-      <c r="F130" s="202" t="s">
+      <c r="E130" s="218"/>
+      <c r="F130" s="201" t="s">
         <v>89</v>
       </c>
-      <c r="G130" s="203"/>
-      <c r="H130" s="203"/>
-      <c r="I130" s="203"/>
-      <c r="J130" s="203"/>
-      <c r="K130" s="203"/>
-      <c r="L130" s="203"/>
-      <c r="M130" s="203"/>
-      <c r="N130" s="203"/>
-      <c r="O130" s="203"/>
-      <c r="P130" s="203"/>
-      <c r="Q130" s="203"/>
-      <c r="R130" s="203"/>
-      <c r="S130" s="203"/>
-      <c r="T130" s="203"/>
-      <c r="U130" s="204"/>
+      <c r="G130" s="202"/>
+      <c r="H130" s="202"/>
+      <c r="I130" s="202"/>
+      <c r="J130" s="202"/>
+      <c r="K130" s="202"/>
+      <c r="L130" s="202"/>
+      <c r="M130" s="202"/>
+      <c r="N130" s="202"/>
+      <c r="O130" s="202"/>
+      <c r="P130" s="202"/>
+      <c r="Q130" s="202"/>
+      <c r="R130" s="202"/>
+      <c r="S130" s="202"/>
+      <c r="T130" s="202"/>
+      <c r="U130" s="203"/>
     </row>
     <row r="131" spans="2:21" ht="55.000000" customHeight="1">
-      <c r="B131" s="198"/>
-      <c r="C131" s="199"/>
-      <c r="D131" s="219"/>
-      <c r="E131" s="219"/>
-      <c r="F131" s="202" t="s">
+      <c r="B131" s="197"/>
+      <c r="C131" s="198"/>
+      <c r="D131" s="218"/>
+      <c r="E131" s="218"/>
+      <c r="F131" s="201" t="s">
         <v>90</v>
       </c>
-      <c r="G131" s="203"/>
-      <c r="H131" s="203"/>
-      <c r="I131" s="203"/>
-      <c r="J131" s="203"/>
-      <c r="K131" s="203"/>
-      <c r="L131" s="203"/>
-      <c r="M131" s="203"/>
-      <c r="N131" s="203"/>
-      <c r="O131" s="203"/>
-      <c r="P131" s="203"/>
-      <c r="Q131" s="203"/>
-      <c r="R131" s="203"/>
-      <c r="S131" s="203"/>
-      <c r="T131" s="203"/>
-      <c r="U131" s="204"/>
+      <c r="G131" s="202"/>
+      <c r="H131" s="202"/>
+      <c r="I131" s="202"/>
+      <c r="J131" s="202"/>
+      <c r="K131" s="202"/>
+      <c r="L131" s="202"/>
+      <c r="M131" s="202"/>
+      <c r="N131" s="202"/>
+      <c r="O131" s="202"/>
+      <c r="P131" s="202"/>
+      <c r="Q131" s="202"/>
+      <c r="R131" s="202"/>
+      <c r="S131" s="202"/>
+      <c r="T131" s="202"/>
+      <c r="U131" s="203"/>
     </row>
     <row r="132" spans="2:21" ht="55.000000" customHeight="1">
-      <c r="B132" s="198"/>
-      <c r="C132" s="199"/>
-      <c r="D132" s="219"/>
-      <c r="E132" s="219"/>
-      <c r="F132" s="202" t="s">
+      <c r="B132" s="197"/>
+      <c r="C132" s="198"/>
+      <c r="D132" s="218"/>
+      <c r="E132" s="218"/>
+      <c r="F132" s="201" t="s">
         <v>91</v>
       </c>
-      <c r="G132" s="203"/>
-      <c r="H132" s="203"/>
-      <c r="I132" s="203"/>
-      <c r="J132" s="203"/>
-      <c r="K132" s="203"/>
-      <c r="L132" s="203"/>
-      <c r="M132" s="203"/>
-      <c r="N132" s="203"/>
-      <c r="O132" s="203"/>
-      <c r="P132" s="203"/>
-      <c r="Q132" s="203"/>
-      <c r="R132" s="203"/>
-      <c r="S132" s="203"/>
-      <c r="T132" s="203"/>
-      <c r="U132" s="204"/>
+      <c r="G132" s="202"/>
+      <c r="H132" s="202"/>
+      <c r="I132" s="202"/>
+      <c r="J132" s="202"/>
+      <c r="K132" s="202"/>
+      <c r="L132" s="202"/>
+      <c r="M132" s="202"/>
+      <c r="N132" s="202"/>
+      <c r="O132" s="202"/>
+      <c r="P132" s="202"/>
+      <c r="Q132" s="202"/>
+      <c r="R132" s="202"/>
+      <c r="S132" s="202"/>
+      <c r="T132" s="202"/>
+      <c r="U132" s="203"/>
     </row>
     <row r="133" spans="2:21" ht="55.000000" customHeight="1">
-      <c r="B133" s="198"/>
-      <c r="C133" s="199"/>
-      <c r="D133" s="219" t="s">
+      <c r="B133" s="197"/>
+      <c r="C133" s="198"/>
+      <c r="D133" s="218" t="s">
         <v>92</v>
       </c>
-      <c r="E133" s="219"/>
-      <c r="F133" s="210" t="s">
+      <c r="E133" s="218"/>
+      <c r="F133" s="209" t="s">
         <v>93</v>
       </c>
-      <c r="G133" s="211"/>
-      <c r="H133" s="211"/>
-      <c r="I133" s="211"/>
-      <c r="J133" s="211"/>
-      <c r="K133" s="211"/>
-      <c r="L133" s="211"/>
-      <c r="M133" s="211"/>
-      <c r="N133" s="211"/>
-      <c r="O133" s="211"/>
-      <c r="P133" s="211"/>
-      <c r="Q133" s="211"/>
-      <c r="R133" s="211"/>
-      <c r="S133" s="211"/>
-      <c r="T133" s="211"/>
-      <c r="U133" s="212"/>
+      <c r="G133" s="210"/>
+      <c r="H133" s="210"/>
+      <c r="I133" s="210"/>
+      <c r="J133" s="210"/>
+      <c r="K133" s="210"/>
+      <c r="L133" s="210"/>
+      <c r="M133" s="210"/>
+      <c r="N133" s="210"/>
+      <c r="O133" s="210"/>
+      <c r="P133" s="210"/>
+      <c r="Q133" s="210"/>
+      <c r="R133" s="210"/>
+      <c r="S133" s="210"/>
+      <c r="T133" s="210"/>
+      <c r="U133" s="211"/>
     </row>
     <row r="134" spans="2:21" ht="55.000000" hidden="1" customHeight="1">
-      <c r="B134" s="198"/>
-      <c r="C134" s="199"/>
-      <c r="D134" s="219"/>
-      <c r="E134" s="219"/>
-      <c r="F134" s="213"/>
-      <c r="G134" s="214"/>
-      <c r="H134" s="214"/>
-      <c r="I134" s="214"/>
-      <c r="J134" s="214"/>
-      <c r="K134" s="214"/>
-      <c r="L134" s="214"/>
-      <c r="M134" s="214"/>
-      <c r="N134" s="214"/>
-      <c r="O134" s="214"/>
-      <c r="P134" s="214"/>
-      <c r="Q134" s="214"/>
-      <c r="R134" s="214"/>
-      <c r="S134" s="214"/>
-      <c r="T134" s="214"/>
-      <c r="U134" s="215"/>
+      <c r="B134" s="197"/>
+      <c r="C134" s="198"/>
+      <c r="D134" s="218"/>
+      <c r="E134" s="218"/>
+      <c r="F134" s="212"/>
+      <c r="G134" s="213"/>
+      <c r="H134" s="213"/>
+      <c r="I134" s="213"/>
+      <c r="J134" s="213"/>
+      <c r="K134" s="213"/>
+      <c r="L134" s="213"/>
+      <c r="M134" s="213"/>
+      <c r="N134" s="213"/>
+      <c r="O134" s="213"/>
+      <c r="P134" s="213"/>
+      <c r="Q134" s="213"/>
+      <c r="R134" s="213"/>
+      <c r="S134" s="213"/>
+      <c r="T134" s="213"/>
+      <c r="U134" s="214"/>
     </row>
     <row r="135" spans="2:21" ht="55.000000" hidden="1" customHeight="1">
-      <c r="B135" s="198"/>
-      <c r="C135" s="199"/>
-      <c r="D135" s="219"/>
-      <c r="E135" s="219"/>
-      <c r="F135" s="216"/>
-      <c r="G135" s="217"/>
-      <c r="H135" s="217"/>
-      <c r="I135" s="217"/>
-      <c r="J135" s="217"/>
-      <c r="K135" s="217"/>
-      <c r="L135" s="217"/>
-      <c r="M135" s="217"/>
-      <c r="N135" s="217"/>
-      <c r="O135" s="217"/>
-      <c r="P135" s="217"/>
-      <c r="Q135" s="217"/>
-      <c r="R135" s="217"/>
-      <c r="S135" s="217"/>
-      <c r="T135" s="217"/>
-      <c r="U135" s="218"/>
+      <c r="B135" s="197"/>
+      <c r="C135" s="198"/>
+      <c r="D135" s="218"/>
+      <c r="E135" s="218"/>
+      <c r="F135" s="215"/>
+      <c r="G135" s="216"/>
+      <c r="H135" s="216"/>
+      <c r="I135" s="216"/>
+      <c r="J135" s="216"/>
+      <c r="K135" s="216"/>
+      <c r="L135" s="216"/>
+      <c r="M135" s="216"/>
+      <c r="N135" s="216"/>
+      <c r="O135" s="216"/>
+      <c r="P135" s="216"/>
+      <c r="Q135" s="216"/>
+      <c r="R135" s="216"/>
+      <c r="S135" s="216"/>
+      <c r="T135" s="216"/>
+      <c r="U135" s="217"/>
     </row>
     <row r="136" spans="2:21" ht="55.000000" customHeight="1">
-      <c r="B136" s="198" t="s">
+      <c r="B136" s="197" t="s">
         <v>94</v>
       </c>
-      <c r="C136" s="199"/>
-      <c r="D136" s="199"/>
-      <c r="E136" s="199"/>
-      <c r="F136" s="202" t="s">
+      <c r="C136" s="198"/>
+      <c r="D136" s="198"/>
+      <c r="E136" s="198"/>
+      <c r="F136" s="201" t="s">
         <v>82</v>
       </c>
-      <c r="G136" s="203"/>
-      <c r="H136" s="203"/>
-      <c r="I136" s="203"/>
-      <c r="J136" s="203"/>
-      <c r="K136" s="203"/>
-      <c r="L136" s="203"/>
-      <c r="M136" s="203"/>
-      <c r="N136" s="203"/>
-      <c r="O136" s="203"/>
-      <c r="P136" s="203"/>
-      <c r="Q136" s="203"/>
-      <c r="R136" s="203"/>
-      <c r="S136" s="203"/>
-      <c r="T136" s="203"/>
-      <c r="U136" s="204"/>
+      <c r="G136" s="202"/>
+      <c r="H136" s="202"/>
+      <c r="I136" s="202"/>
+      <c r="J136" s="202"/>
+      <c r="K136" s="202"/>
+      <c r="L136" s="202"/>
+      <c r="M136" s="202"/>
+      <c r="N136" s="202"/>
+      <c r="O136" s="202"/>
+      <c r="P136" s="202"/>
+      <c r="Q136" s="202"/>
+      <c r="R136" s="202"/>
+      <c r="S136" s="202"/>
+      <c r="T136" s="202"/>
+      <c r="U136" s="203"/>
     </row>
     <row r="137" spans="2:21" ht="55.000000" customHeight="1">
-      <c r="B137" s="198"/>
-      <c r="C137" s="199"/>
-      <c r="D137" s="199"/>
-      <c r="E137" s="199"/>
-      <c r="F137" s="202" t="s">
+      <c r="B137" s="197"/>
+      <c r="C137" s="198"/>
+      <c r="D137" s="198"/>
+      <c r="E137" s="198"/>
+      <c r="F137" s="201" t="s">
         <v>83</v>
       </c>
-      <c r="G137" s="203"/>
-      <c r="H137" s="203"/>
-      <c r="I137" s="203"/>
-      <c r="J137" s="203"/>
-      <c r="K137" s="203"/>
-      <c r="L137" s="203"/>
-      <c r="M137" s="203"/>
-      <c r="N137" s="203"/>
-      <c r="O137" s="203"/>
-      <c r="P137" s="203"/>
-      <c r="Q137" s="203"/>
-      <c r="R137" s="203"/>
-      <c r="S137" s="203"/>
-      <c r="T137" s="203"/>
-      <c r="U137" s="204"/>
+      <c r="G137" s="202"/>
+      <c r="H137" s="202"/>
+      <c r="I137" s="202"/>
+      <c r="J137" s="202"/>
+      <c r="K137" s="202"/>
+      <c r="L137" s="202"/>
+      <c r="M137" s="202"/>
+      <c r="N137" s="202"/>
+      <c r="O137" s="202"/>
+      <c r="P137" s="202"/>
+      <c r="Q137" s="202"/>
+      <c r="R137" s="202"/>
+      <c r="S137" s="202"/>
+      <c r="T137" s="202"/>
+      <c r="U137" s="203"/>
     </row>
     <row r="138" spans="2:21" ht="55.000000" customHeight="1">
-      <c r="B138" s="200"/>
-      <c r="C138" s="201"/>
-      <c r="D138" s="201"/>
-      <c r="E138" s="201"/>
-      <c r="F138" s="205" t="s">
+      <c r="B138" s="199"/>
+      <c r="C138" s="200"/>
+      <c r="D138" s="200"/>
+      <c r="E138" s="200"/>
+      <c r="F138" s="204" t="s">
         <v>91</v>
       </c>
-      <c r="G138" s="206"/>
-      <c r="H138" s="206"/>
-      <c r="I138" s="206"/>
-      <c r="J138" s="206"/>
-      <c r="K138" s="206"/>
-      <c r="L138" s="206"/>
-      <c r="M138" s="206"/>
-      <c r="N138" s="206"/>
-      <c r="O138" s="206"/>
-      <c r="P138" s="206"/>
-      <c r="Q138" s="206"/>
-      <c r="R138" s="206"/>
-      <c r="S138" s="206"/>
-      <c r="T138" s="206"/>
-      <c r="U138" s="207"/>
+      <c r="G138" s="205"/>
+      <c r="H138" s="205"/>
+      <c r="I138" s="205"/>
+      <c r="J138" s="205"/>
+      <c r="K138" s="205"/>
+      <c r="L138" s="205"/>
+      <c r="M138" s="205"/>
+      <c r="N138" s="205"/>
+      <c r="O138" s="205"/>
+      <c r="P138" s="205"/>
+      <c r="Q138" s="205"/>
+      <c r="R138" s="205"/>
+      <c r="S138" s="205"/>
+      <c r="T138" s="205"/>
+      <c r="U138" s="206"/>
     </row>
     <row r="139" spans="2:21" ht="16.000000" customHeight="1">
-      <c r="B139" s="208" t="s">
+      <c r="B139" s="207" t="s">
         <v>95</v>
       </c>
-      <c r="C139" s="208"/>
-      <c r="D139" s="208"/>
-      <c r="E139" s="208"/>
-      <c r="F139" s="208"/>
-      <c r="G139" s="208"/>
-      <c r="H139" s="208"/>
-      <c r="I139" s="208"/>
-      <c r="J139" s="208"/>
-      <c r="K139" s="208"/>
-      <c r="L139" s="208"/>
-      <c r="M139" s="208"/>
-      <c r="N139" s="208"/>
-      <c r="O139" s="208"/>
-      <c r="P139" s="208"/>
-      <c r="Q139" s="208"/>
-      <c r="R139" s="208"/>
-      <c r="S139" s="208"/>
-      <c r="T139" s="208"/>
-      <c r="U139" s="208"/>
+      <c r="C139" s="207"/>
+      <c r="D139" s="207"/>
+      <c r="E139" s="207"/>
+      <c r="F139" s="207"/>
+      <c r="G139" s="207"/>
+      <c r="H139" s="207"/>
+      <c r="I139" s="207"/>
+      <c r="J139" s="207"/>
+      <c r="K139" s="207"/>
+      <c r="L139" s="207"/>
+      <c r="M139" s="207"/>
+      <c r="N139" s="207"/>
+      <c r="O139" s="207"/>
+      <c r="P139" s="207"/>
+      <c r="Q139" s="207"/>
+      <c r="R139" s="207"/>
+      <c r="S139" s="207"/>
+      <c r="T139" s="207"/>
+      <c r="U139" s="207"/>
     </row>
     <row r="140" spans="2:21" ht="42.000000" customHeight="1">
-      <c r="B140" s="209" t="s">
+      <c r="B140" s="208" t="s">
         <v>188</v>
       </c>
-      <c r="C140" s="209"/>
-      <c r="D140" s="209"/>
-      <c r="E140" s="209"/>
-      <c r="F140" s="209"/>
-      <c r="G140" s="209"/>
-      <c r="H140" s="209"/>
-      <c r="I140" s="209"/>
-      <c r="J140" s="209"/>
-      <c r="K140" s="209"/>
-      <c r="L140" s="209"/>
-      <c r="M140" s="209"/>
-      <c r="N140" s="209"/>
-      <c r="O140" s="209"/>
-      <c r="P140" s="209"/>
-      <c r="Q140" s="209"/>
-      <c r="R140" s="209"/>
-      <c r="S140" s="209"/>
-      <c r="T140" s="209"/>
-      <c r="U140" s="209"/>
+      <c r="C140" s="208"/>
+      <c r="D140" s="208"/>
+      <c r="E140" s="208"/>
+      <c r="F140" s="208"/>
+      <c r="G140" s="208"/>
+      <c r="H140" s="208"/>
+      <c r="I140" s="208"/>
+      <c r="J140" s="208"/>
+      <c r="K140" s="208"/>
+      <c r="L140" s="208"/>
+      <c r="M140" s="208"/>
+      <c r="N140" s="208"/>
+      <c r="O140" s="208"/>
+      <c r="P140" s="208"/>
+      <c r="Q140" s="208"/>
+      <c r="R140" s="208"/>
+      <c r="S140" s="208"/>
+      <c r="T140" s="208"/>
+      <c r="U140" s="208"/>
     </row>
     <row r="141" spans="2:21" ht="30.000000" customHeight="1">
-      <c r="B141" s="193" t="s">
+      <c r="B141" s="192" t="s">
         <v>13</v>
       </c>
-      <c r="C141" s="194"/>
-      <c r="D141" s="194"/>
-      <c r="E141" s="194"/>
-      <c r="F141" s="194"/>
-      <c r="G141" s="194"/>
-      <c r="H141" s="194"/>
-      <c r="I141" s="195"/>
-      <c r="J141" s="195"/>
-      <c r="K141" s="195"/>
-      <c r="L141" s="195"/>
+      <c r="C141" s="193"/>
+      <c r="D141" s="193"/>
+      <c r="E141" s="193"/>
+      <c r="F141" s="193"/>
+      <c r="G141" s="193"/>
+      <c r="H141" s="193"/>
+      <c r="I141" s="194"/>
+      <c r="J141" s="194"/>
+      <c r="K141" s="194"/>
+      <c r="L141" s="194"/>
       <c r="M141" s="35" t="s">
         <v>96</v>
       </c>
@@ -41220,13 +41100,13 @@
         <v>97</v>
       </c>
       <c r="Q141" s="36"/>
-      <c r="R141" s="196">
+      <c r="R141" s="195">
         <f>INT(SUM(R142,R143,R144,R145,R146,R147,R148,R149))</f>
         <v>1092686</v>
       </c>
-      <c r="S141" s="196"/>
-      <c r="T141" s="196"/>
-      <c r="U141" s="197"/>
+      <c r="S141" s="195"/>
+      <c r="T141" s="195"/>
+      <c r="U141" s="196"/>
     </row>
     <row r="142" spans="2:21" ht="30.000000" customHeight="1">
       <c r="B142" s="37"/>
@@ -41240,13 +41120,13 @@
       </c>
       <c r="G142" s="6"/>
       <c r="H142" s="6"/>
-      <c r="I142" s="188">
+      <c r="I142" s="187">
         <f>대가산출!G9</f>
         <v>373353</v>
       </c>
-      <c r="J142" s="188"/>
-      <c r="K142" s="188"/>
-      <c r="L142" s="188"/>
+      <c r="J142" s="187"/>
+      <c r="K142" s="187"/>
+      <c r="L142" s="187"/>
       <c r="M142" s="6" t="s">
         <v>98</v>
       </c>
@@ -41275,13 +41155,13 @@
       </c>
       <c r="G143" s="6"/>
       <c r="H143" s="6"/>
-      <c r="I143" s="188">
+      <c r="I143" s="187">
         <f>대가산출!G10</f>
         <v>310884</v>
       </c>
-      <c r="J143" s="188"/>
-      <c r="K143" s="188"/>
-      <c r="L143" s="188"/>
+      <c r="J143" s="187"/>
+      <c r="K143" s="187"/>
+      <c r="L143" s="187"/>
       <c r="M143" s="6" t="s">
         <v>98</v>
       </c>
@@ -41310,13 +41190,13 @@
       </c>
       <c r="G144" s="6"/>
       <c r="H144" s="6"/>
-      <c r="I144" s="188">
+      <c r="I144" s="187">
         <f>대가산출!G11</f>
         <v>295138</v>
       </c>
-      <c r="J144" s="188"/>
-      <c r="K144" s="188"/>
-      <c r="L144" s="188"/>
+      <c r="J144" s="187"/>
+      <c r="K144" s="187"/>
+      <c r="L144" s="187"/>
       <c r="M144" s="6" t="s">
         <v>100</v>
       </c>
@@ -41345,13 +41225,13 @@
       </c>
       <c r="G145" s="6"/>
       <c r="H145" s="6"/>
-      <c r="I145" s="188">
+      <c r="I145" s="187">
         <f>대가산출!G12</f>
         <v>235459</v>
       </c>
-      <c r="J145" s="188"/>
-      <c r="K145" s="188"/>
-      <c r="L145" s="188"/>
+      <c r="J145" s="187"/>
+      <c r="K145" s="187"/>
+      <c r="L145" s="187"/>
       <c r="M145" s="6" t="s">
         <v>100</v>
       </c>
@@ -41374,23 +41254,23 @@
     </row>
     <row r="146" spans="2:21" ht="30.000000" customHeight="1">
       <c r="B146" s="39"/>
-      <c r="C146" s="189" t="s">
+      <c r="C146" s="188" t="s">
         <v>5</v>
       </c>
-      <c r="D146" s="189"/>
-      <c r="E146" s="189"/>
+      <c r="D146" s="188"/>
+      <c r="E146" s="188"/>
       <c r="F146" s="40" t="s">
         <v>104</v>
       </c>
       <c r="G146" s="40"/>
       <c r="H146" s="40"/>
-      <c r="I146" s="190">
+      <c r="I146" s="189">
         <f>I142</f>
         <v>373353</v>
       </c>
-      <c r="J146" s="190"/>
-      <c r="K146" s="190"/>
-      <c r="L146" s="190"/>
+      <c r="J146" s="189"/>
+      <c r="K146" s="189"/>
+      <c r="L146" s="189"/>
       <c r="M146" s="40" t="s">
         <v>100</v>
       </c>
@@ -41403,13 +41283,13 @@
         <v>0</v>
       </c>
       <c r="Q146" s="41"/>
-      <c r="R146" s="191">
+      <c r="R146" s="190">
         <f>P146*I146</f>
         <v>0</v>
       </c>
-      <c r="S146" s="191"/>
-      <c r="T146" s="191"/>
-      <c r="U146" s="192"/>
+      <c r="S146" s="190"/>
+      <c r="T146" s="190"/>
+      <c r="U146" s="191"/>
     </row>
     <row r="147" spans="2:21" ht="30.000000" customHeight="1">
       <c r="B147" s="37"/>
@@ -41419,13 +41299,13 @@
       </c>
       <c r="G147" s="6"/>
       <c r="H147" s="6"/>
-      <c r="I147" s="188">
+      <c r="I147" s="187">
         <f>I143</f>
         <v>310884</v>
       </c>
-      <c r="J147" s="188"/>
-      <c r="K147" s="188"/>
-      <c r="L147" s="188"/>
+      <c r="J147" s="187"/>
+      <c r="K147" s="187"/>
+      <c r="L147" s="187"/>
       <c r="M147" s="6" t="s">
         <v>100</v>
       </c>
@@ -41454,13 +41334,13 @@
       </c>
       <c r="G148" s="6"/>
       <c r="H148" s="6"/>
-      <c r="I148" s="188">
+      <c r="I148" s="187">
         <f>I144</f>
         <v>295138</v>
       </c>
-      <c r="J148" s="188"/>
-      <c r="K148" s="188"/>
-      <c r="L148" s="188"/>
+      <c r="J148" s="187"/>
+      <c r="K148" s="187"/>
+      <c r="L148" s="187"/>
       <c r="M148" s="6" t="s">
         <v>100</v>
       </c>
@@ -41491,13 +41371,13 @@
       </c>
       <c r="G149" s="45"/>
       <c r="H149" s="45"/>
-      <c r="I149" s="182">
+      <c r="I149" s="181">
         <f>I145</f>
         <v>235459</v>
       </c>
-      <c r="J149" s="182"/>
-      <c r="K149" s="182"/>
-      <c r="L149" s="182"/>
+      <c r="J149" s="181"/>
+      <c r="K149" s="181"/>
+      <c r="L149" s="181"/>
       <c r="M149" s="45" t="s">
         <v>100</v>
       </c>
@@ -41510,47 +41390,47 @@
         <v>1</v>
       </c>
       <c r="Q149" s="46"/>
-      <c r="R149" s="183">
+      <c r="R149" s="182">
         <f>P149*I149</f>
         <v>235459</v>
       </c>
-      <c r="S149" s="183"/>
-      <c r="T149" s="183"/>
-      <c r="U149" s="184"/>
+      <c r="S149" s="182"/>
+      <c r="T149" s="182"/>
+      <c r="U149" s="183"/>
     </row>
     <row r="150" spans="2:21" ht="30.000000" customHeight="1">
       <c r="B150" s="178" t="s">
         <v>1</v>
       </c>
-      <c r="C150" s="179"/>
-      <c r="D150" s="179"/>
-      <c r="E150" s="179"/>
-      <c r="F150" s="179"/>
-      <c r="G150" s="179"/>
-      <c r="H150" s="179"/>
+      <c r="C150" s="28"/>
+      <c r="D150" s="28"/>
+      <c r="E150" s="28"/>
+      <c r="F150" s="28"/>
+      <c r="G150" s="28"/>
+      <c r="H150" s="28"/>
       <c r="I150" s="47" t="s">
         <v>101</v>
       </c>
       <c r="J150" s="47"/>
       <c r="K150" s="47"/>
       <c r="L150" s="47"/>
-      <c r="M150" s="185" t="s">
+      <c r="M150" s="184" t="s">
         <v>12</v>
       </c>
-      <c r="N150" s="185"/>
+      <c r="N150" s="184"/>
       <c r="O150" s="48"/>
       <c r="P150" s="47">
         <f>대가산출!F17</f>
         <v>90</v>
       </c>
       <c r="Q150" s="48"/>
-      <c r="R150" s="186">
+      <c r="R150" s="185">
         <f>R141*P150%</f>
         <v>983417.4</v>
       </c>
-      <c r="S150" s="186"/>
-      <c r="T150" s="186"/>
-      <c r="U150" s="187"/>
+      <c r="S150" s="185"/>
+      <c r="T150" s="185"/>
+      <c r="U150" s="186"/>
     </row>
     <row r="151" spans="2:21" ht="30.000000" customHeight="1">
       <c r="B151" s="163" t="s">
@@ -41590,12 +41470,12 @@
       <c r="B152" s="178" t="s">
         <v>3</v>
       </c>
-      <c r="C152" s="179"/>
-      <c r="D152" s="179"/>
-      <c r="E152" s="179"/>
-      <c r="F152" s="179"/>
-      <c r="G152" s="179"/>
-      <c r="H152" s="179"/>
+      <c r="C152" s="28"/>
+      <c r="D152" s="28"/>
+      <c r="E152" s="28"/>
+      <c r="F152" s="28"/>
+      <c r="G152" s="28"/>
+      <c r="H152" s="28"/>
       <c r="I152" s="6"/>
       <c r="J152" s="6"/>
       <c r="K152" s="6"/>
@@ -41605,13 +41485,13 @@
       <c r="O152" s="6"/>
       <c r="P152" s="2"/>
       <c r="Q152" s="2"/>
-      <c r="R152" s="180">
+      <c r="R152" s="179">
         <f>INT(R158+R157+R156+R155+R154)</f>
         <v>219268</v>
       </c>
-      <c r="S152" s="180"/>
-      <c r="T152" s="180"/>
-      <c r="U152" s="181"/>
+      <c r="S152" s="179"/>
+      <c r="T152" s="179"/>
+      <c r="U152" s="180"/>
     </row>
     <row r="153" spans="2:21" ht="30.000000" customHeight="1">
       <c r="B153" s="52" t="s">

--- a/repair/back/doc/estimate/diagnosis.xlsx
+++ b/repair/back/doc/estimate/diagnosis.xlsx
@@ -2814,12 +2814,6 @@
       <color rgb="FF000000"/>
     </font>
     <font>
-      <b/>
-      <sz val="24.0"/>
-      <name val="바탕"/>
-      <color rgb="FF000000"/>
-    </font>
-    <font>
       <sz val="16.0"/>
       <name val="돋움"/>
       <color rgb="FF000000"/>
@@ -2832,6 +2826,12 @@
     <font>
       <sz val="11.0"/>
       <name val="돋움"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24.0"/>
+      <name val="바탕"/>
       <color rgb="FF000000"/>
     </font>
   </fonts>
@@ -41425,8 +41425,8 @@
       </c>
       <c r="Q150" s="48"/>
       <c r="R150" s="185">
-        <f>R141*P150%</f>
-        <v>983417.4</v>
+        <f>ROUND(R141*P150%,0)</f>
+        <v>983417</v>
       </c>
       <c r="S150" s="185"/>
       <c r="T150" s="185"/>
@@ -41459,8 +41459,8 @@
       </c>
       <c r="Q151" s="49"/>
       <c r="R151" s="176">
-        <f>(R141+R150)*P151%</f>
-        <v>207610.34</v>
+        <f>ROUND((R141+R150)*P151%,0)</f>
+        <v>207610</v>
       </c>
       <c r="S151" s="176"/>
       <c r="T151" s="176"/>
